--- a/models/49sectors_exiobase/materials.xlsx
+++ b/models/49sectors_exiobase/materials.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\01.Feina_CREAF\06.Git_Repos\pymedeas2_vensim\models_for_pymedeas2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4961CF08-9532-49C2-93D6-F81BC4A1C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF64D61-A017-49ED-9963-03A252C49268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28050" windowHeight="13995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,26 +16,26 @@
     <sheet name="Global" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="a_extraction_projection_minerals" localSheetId="0">Global!$T$5:$T$62</definedName>
-    <definedName name="current_mineral_reserves_mt" localSheetId="0">Global!$R$5:$R$62</definedName>
-    <definedName name="current_mineral_resources_mt" localSheetId="0">Global!$S$5:$S$62</definedName>
-    <definedName name="current_recycling_rates_minerals" localSheetId="0">Global!$Q$5:$Q$62</definedName>
-    <definedName name="energy_requirements_per_unit_of_water_consumption" localSheetId="0">Global!$M$157:$M$158</definedName>
+    <definedName name="a_extraction_projection_minerals" localSheetId="0">Global!$P$5:$P$62</definedName>
+    <definedName name="current_mineral_reserves_mt" localSheetId="0">Global!$N$5:$N$62</definedName>
+    <definedName name="current_mineral_resources_mt" localSheetId="0">Global!$O$5:$O$62</definedName>
+    <definedName name="current_recycling_rates_minerals" localSheetId="0">Global!$M$5:$M$62</definedName>
+    <definedName name="energy_requirements_per_unit_of_water_consumption" localSheetId="0">Global!$I$157:$I$158</definedName>
     <definedName name="grid_correction_factor_ev_batteries" localSheetId="0">Global!$F$64</definedName>
     <definedName name="grid_correction_factor_res_elec" localSheetId="0">Global!$B$64:$E$64</definedName>
-    <definedName name="historical_extraction_minerals_rest" localSheetId="0">Global!$V$5:$AR$62</definedName>
-    <definedName name="initial_energy_cons_per_material_recycled" comment="&quot;Initial energy cons per unit of material cons (recycled) - data&quot;" localSheetId="0">Global!$N$5:$N$62</definedName>
-    <definedName name="initial_energy_cons_per_material_virgin" comment="&quot;Initial energy cons per unit of material cons (virgin)&quot;" localSheetId="0">Global!$M$5:$M$62</definedName>
-    <definedName name="initial_minerals_extraction_rest" localSheetId="0">Global!$W$5:$W$62</definedName>
+    <definedName name="historical_extraction_minerals_rest" localSheetId="0">Global!$R$5:$AN$62</definedName>
+    <definedName name="initial_energy_cons_per_material_recycled" comment="&quot;Initial energy cons per unit of material cons (recycled) - data&quot;" localSheetId="0">Global!$J$5:$J$62</definedName>
+    <definedName name="initial_energy_cons_per_material_virgin" comment="&quot;Initial energy cons per unit of material cons (virgin)&quot;" localSheetId="0">Global!$I$5:$I$62</definedName>
+    <definedName name="initial_minerals_extraction_rest" localSheetId="0">Global!$S$5:$S$62</definedName>
     <definedName name="materials_for_om_per_capacity_installed_res_elec" localSheetId="0">Global!$B$99:$E$156</definedName>
-    <definedName name="materials_per_new_capacity_installed_ev_batteries" localSheetId="0">Global!$F$5:$J$62</definedName>
+    <definedName name="materials_per_new_capacity_installed_ev_batteries" localSheetId="0">Global!$F$5:$F$62</definedName>
     <definedName name="materials_per_new_capacity_installed_res" localSheetId="0">Global!$B$5:$E$62</definedName>
-    <definedName name="materials_per_new_res_elec_capacity_installed_hvdcs" localSheetId="0">Global!$L$5:$L$62</definedName>
-    <definedName name="materials_per_new_res_elec_capacity_installed_material_overgrid_high_power" localSheetId="0">Global!$K$5:$K$62</definedName>
+    <definedName name="materials_per_new_res_elec_capacity_installed_hvdcs" localSheetId="0">Global!$H$5:$H$62</definedName>
+    <definedName name="materials_per_new_res_elec_capacity_installed_material_overgrid_high_power" localSheetId="0">Global!$G$5:$G$62</definedName>
     <definedName name="self_electricity_consumption_res_elec" localSheetId="0">Global!$B$160:$E$160</definedName>
     <definedName name="share_energy_requirements_for_decom_ev_batteries" localSheetId="0">Global!$F$161</definedName>
     <definedName name="share_energy_requirements_for_decom_res_elec" localSheetId="0">Global!$B$161:$E$161</definedName>
-    <definedName name="time" localSheetId="0">Global!$V$3:$AR$3</definedName>
+    <definedName name="time" localSheetId="0">Global!$R$3:$AN$3</definedName>
     <definedName name="water_for_om_res_elec" localSheetId="0">Global!$B$157:$E$158</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
@@ -64,7 +64,7 @@
     <author>EM</author>
   </authors>
   <commentList>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -89,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -163,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -214,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -265,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -290,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="M19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -315,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="M23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -340,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="M29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -365,7 +365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="N39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -390,7 +390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="O39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -415,7 +415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="M57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -440,7 +440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -465,7 +465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -490,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="M60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -570,7 +570,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="96">
   <si>
     <t>Material intensity of technologies</t>
   </si>
@@ -859,21 +859,6 @@
   <si>
     <t>Decommissioning</t>
   </si>
-  <si>
-    <t>kg/kwh</t>
-  </si>
-  <si>
-    <t>LFP</t>
-  </si>
-  <si>
-    <t>NMC_LEGACY</t>
-  </si>
-  <si>
-    <t>NMC_811</t>
-  </si>
-  <si>
-    <t>NCA</t>
-  </si>
 </sst>
 </file>
 
@@ -981,7 +966,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1307,37 +1292,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1517,9 +1476,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1812,51 +1768,51 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:ANO164"/>
+  <dimension ref="A1:ANK164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.7109375" customWidth="1"/>
     <col min="2" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="16.42578125" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" customWidth="1"/>
-    <col min="13" max="13" width="31.85546875" style="62" customWidth="1"/>
-    <col min="14" max="14" width="32.5703125" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="19" width="12" customWidth="1"/>
-    <col min="20" max="20" width="12" style="63" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="63" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="31.85546875" style="62" customWidth="1"/>
+    <col min="10" max="10" width="32.5703125" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12" style="63" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1055" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1051" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="98" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="7" t="s">
+      <c r="B1" s="95" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
@@ -1875,13 +1831,9 @@
       <c r="AK1" s="5"/>
       <c r="AL1" s="5"/>
       <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="6"/>
+      <c r="AN1" s="6"/>
     </row>
-    <row r="2" spans="1:1055" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1051" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>2</v>
@@ -1898,52 +1850,44 @@
       <c r="F2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="L2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="P2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="9"/>
-      <c r="V2" s="17" t="s">
+      <c r="Q2" s="9"/>
+      <c r="R2" s="17" t="s">
         <v>17</v>
       </c>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -1961,13 +1905,9 @@
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="18"/>
+      <c r="AN2" s="18"/>
     </row>
-    <row r="3" spans="1:1055" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1051" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="19" t="s">
         <v>18</v>
@@ -1982,141 +1922,132 @@
         <v>18</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="19" t="s">
+      <c r="I3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="J3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="K3" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="L3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="M3" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="R3" s="24" t="s">
+      <c r="N3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="S3" s="23" t="s">
+      <c r="O3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="P3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>25</v>
       </c>
+      <c r="R3" s="1">
+        <v>1994</v>
+      </c>
+      <c r="S3" s="1">
+        <v>1995</v>
+      </c>
+      <c r="T3" s="1">
+        <v>1996</v>
+      </c>
+      <c r="U3" s="1">
+        <v>1997</v>
+      </c>
       <c r="V3" s="1">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="W3" s="1">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="X3" s="1">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="Y3" s="1">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="Z3" s="1">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="AA3" s="1">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="AB3" s="1">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="AC3" s="1">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="AD3" s="1">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="AE3" s="1">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="AF3" s="1">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="AG3" s="1">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="AH3" s="1">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="AI3" s="1">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="AJ3" s="1">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="AK3" s="1">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="AL3" s="1">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="AM3" s="1">
-        <v>2011</v>
-      </c>
-      <c r="AN3" s="1">
-        <v>2012</v>
-      </c>
-      <c r="AO3" s="1">
-        <v>2013</v>
-      </c>
-      <c r="AP3" s="1">
-        <v>2014</v>
-      </c>
-      <c r="AQ3" s="1">
         <v>2015</v>
       </c>
-      <c r="AR3" s="18">
+      <c r="AN3" s="18">
         <v>2016</v>
       </c>
     </row>
-    <row r="4" spans="1:1055" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1051" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="27"/>
       <c r="E4" s="29"/>
       <c r="F4" s="27"/>
-      <c r="J4" s="96"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="27"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="33"/>
-      <c r="AR4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="27"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="33"/>
+      <c r="AN4" s="29"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
       <c r="AS4"/>
       <c r="AT4"/>
       <c r="AU4"/>
@@ -3124,12 +3055,8 @@
       <c r="ANI4"/>
       <c r="ANJ4"/>
       <c r="ANK4"/>
-      <c r="ANL4"/>
-      <c r="ANM4"/>
-      <c r="ANN4"/>
-      <c r="ANO4"/>
     </row>
-    <row r="5" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>27</v>
       </c>
@@ -3148,44 +3075,44 @@
       <c r="F5" s="35">
         <v>0</v>
       </c>
-      <c r="G5" s="96">
-        <v>0</v>
-      </c>
-      <c r="H5" s="96">
-        <v>0</v>
-      </c>
-      <c r="I5" s="96">
-        <v>0</v>
-      </c>
-      <c r="J5" s="97">
-        <v>0</v>
-      </c>
-      <c r="K5" s="36">
-        <v>0</v>
-      </c>
-      <c r="L5" s="38">
-        <v>0</v>
-      </c>
-      <c r="M5" s="39">
+      <c r="G5" s="36">
+        <v>0</v>
+      </c>
+      <c r="H5" s="38">
+        <v>0</v>
+      </c>
+      <c r="I5" s="39">
         <v>100</v>
       </c>
-      <c r="N5" s="40">
-        <v>0</v>
-      </c>
-      <c r="O5" s="35"/>
-      <c r="Q5" s="38">
-        <v>0</v>
-      </c>
-      <c r="R5" s="35">
-        <v>0</v>
-      </c>
-      <c r="S5" s="38">
-        <v>0</v>
-      </c>
-      <c r="T5" s="41">
-        <v>0</v>
-      </c>
-      <c r="U5" s="42">
+      <c r="J5" s="40">
+        <v>0</v>
+      </c>
+      <c r="K5" s="35"/>
+      <c r="M5" s="38">
+        <v>0</v>
+      </c>
+      <c r="N5" s="35">
+        <v>0</v>
+      </c>
+      <c r="O5" s="38">
+        <v>0</v>
+      </c>
+      <c r="P5" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="42">
+        <v>0</v>
+      </c>
+      <c r="R5" s="36">
+        <v>0</v>
+      </c>
+      <c r="S5" s="36">
+        <v>0</v>
+      </c>
+      <c r="T5" s="36">
+        <v>0</v>
+      </c>
+      <c r="U5" s="36">
         <v>0</v>
       </c>
       <c r="V5" s="36">
@@ -3242,21 +3169,13 @@
       <c r="AM5" s="36">
         <v>0</v>
       </c>
-      <c r="AN5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN5" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
       <c r="AS5"/>
       <c r="AT5"/>
       <c r="AU5"/>
@@ -4264,12 +4183,8 @@
       <c r="ANI5"/>
       <c r="ANJ5"/>
       <c r="ANK5"/>
-      <c r="ANL5"/>
-      <c r="ANM5"/>
-      <c r="ANN5"/>
-      <c r="ANO5"/>
     </row>
-    <row r="6" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
         <v>28</v>
       </c>
@@ -4288,121 +4203,113 @@
       <c r="F6" s="35">
         <v>500</v>
       </c>
-      <c r="G6" s="96">
-        <v>0</v>
-      </c>
-      <c r="H6" s="96">
-        <v>0</v>
-      </c>
-      <c r="I6" s="96">
-        <v>0</v>
-      </c>
-      <c r="J6" s="97">
-        <v>0</v>
-      </c>
-      <c r="K6" s="36">
+      <c r="G6" s="36">
         <v>7362</v>
       </c>
-      <c r="L6" s="38">
+      <c r="H6" s="38">
         <v>100</v>
       </c>
-      <c r="M6" s="39">
+      <c r="I6" s="39">
         <v>218</v>
       </c>
-      <c r="N6" s="40">
+      <c r="J6" s="40">
         <v>29</v>
       </c>
-      <c r="O6" s="35">
+      <c r="K6" s="35">
         <v>0.42</v>
       </c>
-      <c r="P6" s="36">
+      <c r="L6" s="36">
         <v>0.7</v>
       </c>
-      <c r="Q6" s="38">
-        <f>(O6+P6)/2</f>
+      <c r="M6" s="38">
+        <f>(K6+L6)/2</f>
         <v>0.55999999999999994</v>
       </c>
-      <c r="R6" s="35">
+      <c r="N6" s="35">
         <v>28000</v>
       </c>
-      <c r="S6" s="38">
+      <c r="O6" s="38">
         <v>75000</v>
       </c>
-      <c r="T6" s="41">
+      <c r="P6" s="41">
         <v>1006851.44431989</v>
       </c>
-      <c r="U6" s="42">
+      <c r="Q6" s="42">
         <v>-24747508.840468701</v>
       </c>
+      <c r="R6" s="36">
+        <v>19100000</v>
+      </c>
+      <c r="S6" s="36">
+        <v>19393200</v>
+      </c>
+      <c r="T6" s="36">
+        <v>20694690</v>
+      </c>
+      <c r="U6" s="36">
+        <v>21392970</v>
+      </c>
       <c r="V6" s="36">
-        <v>19100000</v>
+        <v>22089700</v>
       </c>
       <c r="W6" s="36">
-        <v>19393200</v>
+        <v>23084960</v>
       </c>
       <c r="X6" s="36">
-        <v>20694690</v>
+        <v>23982470</v>
       </c>
       <c r="Y6" s="36">
-        <v>21392970</v>
+        <v>24378590</v>
       </c>
       <c r="Z6" s="36">
-        <v>22089700</v>
+        <v>25872770</v>
       </c>
       <c r="AA6" s="36">
-        <v>23084960</v>
+        <v>27662610</v>
       </c>
       <c r="AB6" s="36">
-        <v>23982470</v>
+        <v>29751750</v>
       </c>
       <c r="AC6" s="36">
-        <v>24378590</v>
+        <v>31838150</v>
       </c>
       <c r="AD6" s="36">
-        <v>25872770</v>
+        <v>33607000</v>
       </c>
       <c r="AE6" s="36">
-        <v>27662610</v>
+        <v>37851990</v>
       </c>
       <c r="AF6" s="36">
-        <v>29751750</v>
+        <v>38789070</v>
       </c>
       <c r="AG6" s="36">
-        <v>31838150</v>
+        <v>36941740</v>
       </c>
       <c r="AH6" s="36">
-        <v>33607000</v>
+        <v>40260150</v>
       </c>
       <c r="AI6" s="36">
-        <v>37851990</v>
+        <v>43814260</v>
       </c>
       <c r="AJ6" s="36">
-        <v>38789070</v>
+        <v>45233790</v>
       </c>
       <c r="AK6" s="36">
-        <v>36941740</v>
+        <v>46864630</v>
       </c>
       <c r="AL6" s="36">
-        <v>40260150</v>
+        <v>49355110</v>
       </c>
       <c r="AM6" s="36">
-        <v>43814260</v>
-      </c>
-      <c r="AN6" s="36">
-        <v>45233790</v>
-      </c>
-      <c r="AO6" s="36">
-        <v>46864630</v>
-      </c>
-      <c r="AP6" s="36">
-        <v>49355110</v>
-      </c>
-      <c r="AQ6" s="36">
         <v>55928650</v>
       </c>
-      <c r="AR6" s="38">
+      <c r="AN6" s="38">
         <v>55520790</v>
       </c>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
       <c r="AS6"/>
       <c r="AT6"/>
       <c r="AU6"/>
@@ -5410,12 +5317,8 @@
       <c r="ANI6"/>
       <c r="ANJ6"/>
       <c r="ANK6"/>
-      <c r="ANL6"/>
-      <c r="ANM6"/>
-      <c r="ANN6"/>
-      <c r="ANO6"/>
     </row>
-    <row r="7" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>29</v>
       </c>
@@ -5434,44 +5337,44 @@
       <c r="F7" s="35">
         <v>0</v>
       </c>
-      <c r="G7" s="96">
-        <v>0</v>
-      </c>
-      <c r="H7" s="96">
-        <v>0</v>
-      </c>
-      <c r="I7" s="96">
-        <v>0</v>
-      </c>
-      <c r="J7" s="97">
-        <v>0</v>
-      </c>
-      <c r="K7" s="36">
-        <v>0</v>
-      </c>
-      <c r="L7" s="38">
-        <v>0</v>
-      </c>
-      <c r="M7" s="39">
-        <v>0</v>
-      </c>
-      <c r="N7" s="40">
-        <v>0</v>
-      </c>
-      <c r="O7" s="35"/>
-      <c r="Q7" s="38">
-        <v>0</v>
-      </c>
-      <c r="R7" s="35">
-        <v>0</v>
-      </c>
-      <c r="S7" s="38">
-        <v>0</v>
-      </c>
-      <c r="T7" s="41">
-        <v>0</v>
-      </c>
-      <c r="U7" s="42">
+      <c r="G7" s="36">
+        <v>0</v>
+      </c>
+      <c r="H7" s="38">
+        <v>0</v>
+      </c>
+      <c r="I7" s="39">
+        <v>0</v>
+      </c>
+      <c r="J7" s="40">
+        <v>0</v>
+      </c>
+      <c r="K7" s="35"/>
+      <c r="M7" s="38">
+        <v>0</v>
+      </c>
+      <c r="N7" s="35">
+        <v>0</v>
+      </c>
+      <c r="O7" s="38">
+        <v>0</v>
+      </c>
+      <c r="P7" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="42">
+        <v>0</v>
+      </c>
+      <c r="R7" s="36">
+        <v>0</v>
+      </c>
+      <c r="S7" s="36">
+        <v>0</v>
+      </c>
+      <c r="T7" s="36">
+        <v>0</v>
+      </c>
+      <c r="U7" s="36">
         <v>0</v>
       </c>
       <c r="V7" s="36">
@@ -5528,21 +5431,13 @@
       <c r="AM7" s="36">
         <v>0</v>
       </c>
-      <c r="AN7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN7" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
       <c r="AS7"/>
       <c r="AT7"/>
       <c r="AU7"/>
@@ -6550,12 +6445,8 @@
       <c r="ANI7"/>
       <c r="ANJ7"/>
       <c r="ANK7"/>
-      <c r="ANL7"/>
-      <c r="ANM7"/>
-      <c r="ANN7"/>
-      <c r="ANO7"/>
     </row>
-    <row r="8" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>30</v>
       </c>
@@ -6574,115 +6465,107 @@
       <c r="F8" s="35">
         <v>0</v>
       </c>
-      <c r="G8" s="96">
-        <v>0</v>
-      </c>
-      <c r="H8" s="96">
-        <v>0</v>
-      </c>
-      <c r="I8" s="96">
-        <v>0</v>
-      </c>
-      <c r="J8" s="97">
-        <v>0</v>
-      </c>
-      <c r="K8" s="36">
-        <v>0</v>
-      </c>
-      <c r="L8" s="38">
-        <v>0</v>
-      </c>
-      <c r="M8" s="39">
+      <c r="G8" s="36">
+        <v>0</v>
+      </c>
+      <c r="H8" s="38">
+        <v>0</v>
+      </c>
+      <c r="I8" s="39">
         <v>264</v>
       </c>
-      <c r="N8" s="40">
-        <v>0</v>
-      </c>
-      <c r="O8" s="35"/>
-      <c r="Q8" s="38">
+      <c r="J8" s="40">
+        <v>0</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="M8" s="38">
         <v>0.15</v>
       </c>
-      <c r="R8" s="35">
+      <c r="N8" s="35">
         <v>0.5</v>
       </c>
-      <c r="S8" s="38">
+      <c r="O8" s="38">
         <v>6</v>
       </c>
-      <c r="T8" s="41">
+      <c r="P8" s="41">
         <v>119.692871936237</v>
       </c>
-      <c r="U8" s="42">
+      <c r="Q8" s="42">
         <v>12862.9927690069</v>
       </c>
+      <c r="R8" s="36">
+        <v>18100</v>
+      </c>
+      <c r="S8" s="36">
+        <v>18500</v>
+      </c>
+      <c r="T8" s="36">
+        <v>18900</v>
+      </c>
+      <c r="U8" s="36">
+        <v>20000</v>
+      </c>
       <c r="V8" s="36">
-        <v>18100</v>
+        <v>19600</v>
       </c>
       <c r="W8" s="36">
-        <v>18500</v>
+        <v>19100</v>
       </c>
       <c r="X8" s="36">
-        <v>18900</v>
+        <v>19700</v>
       </c>
       <c r="Y8" s="36">
-        <v>20000</v>
+        <v>18200</v>
       </c>
       <c r="Z8" s="36">
-        <v>19600</v>
+        <v>15800</v>
       </c>
       <c r="AA8" s="36">
-        <v>19100</v>
+        <v>16890</v>
       </c>
       <c r="AB8" s="36">
-        <v>19700</v>
+        <v>18790</v>
       </c>
       <c r="AC8" s="36">
-        <v>18200</v>
+        <v>19390</v>
       </c>
       <c r="AD8" s="36">
-        <v>15800</v>
+        <v>19280</v>
       </c>
       <c r="AE8" s="36">
-        <v>16890</v>
+        <v>20370</v>
       </c>
       <c r="AF8" s="36">
-        <v>18790</v>
+        <v>19550</v>
       </c>
       <c r="AG8" s="36">
-        <v>19390</v>
+        <v>18690</v>
       </c>
       <c r="AH8" s="36">
-        <v>19280</v>
+        <v>20930</v>
       </c>
       <c r="AI8" s="36">
-        <v>20370</v>
+        <v>22010</v>
       </c>
       <c r="AJ8" s="36">
-        <v>19550</v>
+        <v>22780</v>
       </c>
       <c r="AK8" s="36">
-        <v>18690</v>
+        <v>21770</v>
       </c>
       <c r="AL8" s="36">
-        <v>20930</v>
+        <v>22020</v>
       </c>
       <c r="AM8" s="36">
-        <v>22010</v>
-      </c>
-      <c r="AN8" s="36">
-        <v>22780</v>
-      </c>
-      <c r="AO8" s="36">
-        <v>21770</v>
-      </c>
-      <c r="AP8" s="36">
-        <v>22020</v>
-      </c>
-      <c r="AQ8" s="36">
         <v>22680</v>
       </c>
-      <c r="AR8" s="38">
+      <c r="AN8" s="38">
         <v>22320</v>
       </c>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
       <c r="AS8"/>
       <c r="AT8"/>
       <c r="AU8"/>
@@ -7690,12 +7573,8 @@
       <c r="ANI8"/>
       <c r="ANJ8"/>
       <c r="ANK8"/>
-      <c r="ANL8"/>
-      <c r="ANM8"/>
-      <c r="ANN8"/>
-      <c r="ANO8"/>
     </row>
-    <row r="9" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>31</v>
       </c>
@@ -7714,44 +7593,44 @@
       <c r="F9" s="35">
         <v>0</v>
       </c>
-      <c r="G9" s="96">
-        <v>0</v>
-      </c>
-      <c r="H9" s="96">
-        <v>0</v>
-      </c>
-      <c r="I9" s="96">
-        <v>0</v>
-      </c>
-      <c r="J9" s="97">
-        <v>0</v>
-      </c>
-      <c r="K9" s="36">
-        <v>0</v>
-      </c>
-      <c r="L9" s="38">
-        <v>0</v>
-      </c>
-      <c r="M9" s="39">
+      <c r="G9" s="36">
+        <v>0</v>
+      </c>
+      <c r="H9" s="38">
+        <v>0</v>
+      </c>
+      <c r="I9" s="39">
         <v>200</v>
       </c>
-      <c r="N9" s="40">
-        <v>0</v>
-      </c>
-      <c r="O9" s="35"/>
-      <c r="Q9" s="38">
-        <v>0</v>
-      </c>
-      <c r="R9" s="35">
-        <v>0</v>
-      </c>
-      <c r="S9" s="38">
-        <v>0</v>
-      </c>
-      <c r="T9" s="41">
-        <v>0</v>
-      </c>
-      <c r="U9" s="42">
+      <c r="J9" s="40">
+        <v>0</v>
+      </c>
+      <c r="K9" s="35"/>
+      <c r="M9" s="38">
+        <v>0</v>
+      </c>
+      <c r="N9" s="35">
+        <v>0</v>
+      </c>
+      <c r="O9" s="38">
+        <v>0</v>
+      </c>
+      <c r="P9" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="42">
+        <v>0</v>
+      </c>
+      <c r="R9" s="36">
+        <v>0</v>
+      </c>
+      <c r="S9" s="36">
+        <v>0</v>
+      </c>
+      <c r="T9" s="36">
+        <v>0</v>
+      </c>
+      <c r="U9" s="36">
         <v>0</v>
       </c>
       <c r="V9" s="36">
@@ -7808,21 +7687,13 @@
       <c r="AM9" s="36">
         <v>0</v>
       </c>
-      <c r="AN9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN9" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
       <c r="AS9"/>
       <c r="AT9"/>
       <c r="AU9"/>
@@ -8830,12 +8701,8 @@
       <c r="ANI9"/>
       <c r="ANJ9"/>
       <c r="ANK9"/>
-      <c r="ANL9"/>
-      <c r="ANM9"/>
-      <c r="ANN9"/>
-      <c r="ANO9"/>
     </row>
-    <row r="10" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>32</v>
       </c>
@@ -8854,44 +8721,44 @@
       <c r="F10" s="35">
         <v>0</v>
       </c>
-      <c r="G10" s="96">
-        <v>0</v>
-      </c>
-      <c r="H10" s="96">
-        <v>0</v>
-      </c>
-      <c r="I10" s="96">
-        <v>0</v>
-      </c>
-      <c r="J10" s="97">
-        <v>0</v>
-      </c>
-      <c r="K10" s="36">
+      <c r="G10" s="36">
         <v>48</v>
       </c>
-      <c r="L10" s="38">
-        <v>0</v>
-      </c>
-      <c r="M10" s="39">
+      <c r="H10" s="38">
+        <v>0</v>
+      </c>
+      <c r="I10" s="39">
         <v>4.5</v>
       </c>
-      <c r="N10" s="40">
-        <v>0</v>
-      </c>
-      <c r="O10" s="35"/>
-      <c r="Q10" s="38">
-        <v>0</v>
-      </c>
-      <c r="R10" s="35">
-        <v>0</v>
-      </c>
-      <c r="S10" s="38">
-        <v>0</v>
-      </c>
-      <c r="T10" s="41">
-        <v>0</v>
-      </c>
-      <c r="U10" s="42">
+      <c r="J10" s="40">
+        <v>0</v>
+      </c>
+      <c r="K10" s="35"/>
+      <c r="M10" s="38">
+        <v>0</v>
+      </c>
+      <c r="N10" s="35">
+        <v>0</v>
+      </c>
+      <c r="O10" s="38">
+        <v>0</v>
+      </c>
+      <c r="P10" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="42">
+        <v>0</v>
+      </c>
+      <c r="R10" s="36">
+        <v>0</v>
+      </c>
+      <c r="S10" s="36">
+        <v>0</v>
+      </c>
+      <c r="T10" s="36">
+        <v>0</v>
+      </c>
+      <c r="U10" s="36">
         <v>0</v>
       </c>
       <c r="V10" s="36">
@@ -8948,21 +8815,13 @@
       <c r="AM10" s="36">
         <v>0</v>
       </c>
-      <c r="AN10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN10" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
       <c r="AS10"/>
       <c r="AT10"/>
       <c r="AU10"/>
@@ -9970,12 +9829,8 @@
       <c r="ANI10"/>
       <c r="ANJ10"/>
       <c r="ANK10"/>
-      <c r="ANL10"/>
-      <c r="ANM10"/>
-      <c r="ANN10"/>
-      <c r="ANO10"/>
     </row>
-    <row r="11" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>33</v>
       </c>
@@ -9995,121 +9850,113 @@
       <c r="F11" s="35">
         <v>0</v>
       </c>
-      <c r="G11" s="96">
-        <v>0</v>
-      </c>
-      <c r="H11" s="96">
-        <v>0</v>
-      </c>
-      <c r="I11" s="96">
-        <v>0</v>
-      </c>
-      <c r="J11" s="97">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36">
-        <v>0</v>
-      </c>
-      <c r="L11" s="38">
-        <v>0</v>
-      </c>
-      <c r="M11" s="39">
+      <c r="G11" s="36">
+        <v>0</v>
+      </c>
+      <c r="H11" s="38">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39">
         <v>83</v>
       </c>
-      <c r="N11" s="40">
-        <v>0</v>
-      </c>
-      <c r="O11" s="35">
+      <c r="J11" s="40">
+        <v>0</v>
+      </c>
+      <c r="K11" s="35">
         <v>0.87</v>
       </c>
-      <c r="P11" s="36">
+      <c r="L11" s="36">
         <v>0.93</v>
       </c>
-      <c r="Q11" s="38">
-        <f>(O11+P11)/2</f>
+      <c r="M11" s="38">
+        <f>(K11+L11)/2</f>
         <v>0.9</v>
       </c>
-      <c r="R11" s="35">
+      <c r="N11" s="35">
         <v>480</v>
       </c>
-      <c r="S11" s="38">
+      <c r="O11" s="38">
         <v>12000</v>
       </c>
-      <c r="T11" s="41">
+      <c r="P11" s="41">
         <v>561172.97577377898</v>
       </c>
-      <c r="U11" s="42">
+      <c r="Q11" s="42">
         <v>-13481662.071520699</v>
       </c>
+      <c r="R11" s="36">
+        <v>9570000</v>
+      </c>
+      <c r="S11" s="36">
+        <v>11999960</v>
+      </c>
+      <c r="T11" s="36">
+        <v>12189960</v>
+      </c>
+      <c r="U11" s="36">
+        <v>12499930</v>
+      </c>
       <c r="V11" s="36">
-        <v>9570000</v>
+        <v>12699880</v>
       </c>
       <c r="W11" s="36">
-        <v>11999960</v>
+        <v>13499820</v>
       </c>
       <c r="X11" s="36">
-        <v>12189960</v>
+        <v>14399830</v>
       </c>
       <c r="Y11" s="36">
-        <v>12499930</v>
+        <v>12099800</v>
       </c>
       <c r="Z11" s="36">
-        <v>12699880</v>
+        <v>13499670</v>
       </c>
       <c r="AA11" s="36">
-        <v>13499820</v>
+        <v>15499420</v>
       </c>
       <c r="AB11" s="36">
-        <v>14399830</v>
+        <v>17499230</v>
       </c>
       <c r="AC11" s="36">
-        <v>12099800</v>
+        <v>19298990</v>
       </c>
       <c r="AD11" s="36">
-        <v>13499670</v>
+        <v>19598220</v>
       </c>
       <c r="AE11" s="36">
-        <v>15499420</v>
+        <v>21496500</v>
       </c>
       <c r="AF11" s="36">
-        <v>17499230</v>
+        <v>23794450</v>
       </c>
       <c r="AG11" s="36">
-        <v>19298990</v>
+        <v>19289490</v>
       </c>
       <c r="AH11" s="36">
-        <v>19598220</v>
+        <v>23683310</v>
       </c>
       <c r="AI11" s="36">
-        <v>21496500</v>
+        <v>23281570</v>
       </c>
       <c r="AJ11" s="36">
-        <v>23794450</v>
+        <v>25578710</v>
       </c>
       <c r="AK11" s="36">
-        <v>19289490</v>
+        <v>28777200</v>
       </c>
       <c r="AL11" s="36">
-        <v>23683310</v>
+        <v>26364160</v>
       </c>
       <c r="AM11" s="36">
-        <v>23281570</v>
-      </c>
-      <c r="AN11" s="36">
-        <v>25578710</v>
-      </c>
-      <c r="AO11" s="36">
-        <v>28777200</v>
-      </c>
-      <c r="AP11" s="36">
-        <v>26364160</v>
-      </c>
-      <c r="AQ11" s="36">
         <v>30350300</v>
       </c>
-      <c r="AR11" s="38">
+      <c r="AN11" s="38">
         <v>30335910</v>
       </c>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
       <c r="AS11"/>
       <c r="AT11"/>
       <c r="AU11"/>
@@ -11117,12 +10964,8 @@
       <c r="ANI11"/>
       <c r="ANJ11"/>
       <c r="ANK11"/>
-      <c r="ANL11"/>
-      <c r="ANM11"/>
-      <c r="ANN11"/>
-      <c r="ANO11"/>
     </row>
-    <row r="12" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
         <v>34</v>
       </c>
@@ -11141,121 +10984,113 @@
       <c r="F12" s="35">
         <v>289</v>
       </c>
-      <c r="G12" s="96">
-        <v>0</v>
-      </c>
-      <c r="H12" s="96">
-        <v>0</v>
-      </c>
-      <c r="I12" s="96">
-        <v>0</v>
-      </c>
-      <c r="J12" s="97">
-        <v>0</v>
-      </c>
-      <c r="K12" s="36">
+      <c r="G12" s="36">
         <v>2044</v>
       </c>
-      <c r="L12" s="38">
+      <c r="H12" s="38">
         <v>125</v>
       </c>
-      <c r="M12" s="39">
+      <c r="I12" s="39">
         <v>57</v>
       </c>
-      <c r="N12" s="40">
+      <c r="J12" s="40">
         <v>16.5</v>
       </c>
-      <c r="O12" s="35">
+      <c r="K12" s="35">
         <v>0.43</v>
       </c>
-      <c r="P12" s="36">
+      <c r="L12" s="36">
         <v>0.53</v>
       </c>
-      <c r="Q12" s="38">
-        <f>(O12+P12)/2</f>
+      <c r="M12" s="38">
+        <f>(K12+L12)/2</f>
         <v>0.48</v>
       </c>
-      <c r="R12" s="35">
-        <v>720</v>
-      </c>
-      <c r="S12" s="38">
+      <c r="N12" s="35">
+        <v>980</v>
+      </c>
+      <c r="O12" s="38">
         <v>2100</v>
       </c>
-      <c r="T12" s="41">
+      <c r="P12" s="41">
         <v>230741.487187447</v>
       </c>
-      <c r="U12" s="42">
+      <c r="Q12" s="42">
         <v>1147112.83580538</v>
       </c>
+      <c r="R12" s="36">
+        <v>9430000</v>
+      </c>
+      <c r="S12" s="36">
+        <v>9992170</v>
+      </c>
+      <c r="T12" s="36">
+        <v>10994390</v>
+      </c>
+      <c r="U12" s="36">
+        <v>11392880</v>
+      </c>
       <c r="V12" s="36">
-        <v>9430000</v>
+        <v>12190320</v>
       </c>
       <c r="W12" s="36">
-        <v>9992170</v>
+        <v>12586080</v>
       </c>
       <c r="X12" s="36">
-        <v>10994390</v>
+        <v>13182150</v>
       </c>
       <c r="Y12" s="36">
-        <v>11392880</v>
+        <v>13677330</v>
       </c>
       <c r="Z12" s="36">
-        <v>12190320</v>
+        <v>13573660</v>
       </c>
       <c r="AA12" s="36">
-        <v>12586080</v>
+        <v>13569730</v>
       </c>
       <c r="AB12" s="36">
-        <v>13182150</v>
+        <v>14561920</v>
       </c>
       <c r="AC12" s="36">
-        <v>13677330</v>
+        <v>14949450</v>
       </c>
       <c r="AD12" s="36">
-        <v>13573660</v>
+        <v>15032000</v>
       </c>
       <c r="AE12" s="36">
-        <v>13569730</v>
+        <v>15309050</v>
       </c>
       <c r="AF12" s="36">
-        <v>14561920</v>
+        <v>15285180</v>
       </c>
       <c r="AG12" s="36">
-        <v>14949450</v>
+        <v>15750700</v>
       </c>
       <c r="AH12" s="36">
-        <v>15032000</v>
+        <v>15707320</v>
       </c>
       <c r="AI12" s="36">
-        <v>15309050</v>
+        <v>15891470</v>
       </c>
       <c r="AJ12" s="36">
-        <v>15285180</v>
+        <v>16672810</v>
       </c>
       <c r="AK12" s="36">
-        <v>15750700</v>
+        <v>18037090</v>
       </c>
       <c r="AL12" s="36">
-        <v>15707320</v>
+        <v>18126070</v>
       </c>
       <c r="AM12" s="36">
-        <v>15891470</v>
-      </c>
-      <c r="AN12" s="36">
-        <v>16672810</v>
-      </c>
-      <c r="AO12" s="36">
-        <v>18037090</v>
-      </c>
-      <c r="AP12" s="36">
-        <v>18126070</v>
-      </c>
-      <c r="AQ12" s="36">
         <v>18615350</v>
       </c>
-      <c r="AR12" s="38">
+      <c r="AN12" s="38">
         <v>18700270</v>
       </c>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
       <c r="AS12"/>
       <c r="AT12"/>
       <c r="AU12"/>
@@ -12263,12 +12098,8 @@
       <c r="ANI12"/>
       <c r="ANJ12"/>
       <c r="ANK12"/>
-      <c r="ANL12"/>
-      <c r="ANM12"/>
-      <c r="ANN12"/>
-      <c r="ANO12"/>
     </row>
-    <row r="13" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>35</v>
       </c>
@@ -12288,44 +12119,44 @@
       <c r="F13" s="35">
         <v>0</v>
       </c>
-      <c r="G13" s="96">
-        <v>0</v>
-      </c>
-      <c r="H13" s="96">
-        <v>0</v>
-      </c>
-      <c r="I13" s="96">
-        <v>0</v>
-      </c>
-      <c r="J13" s="97">
-        <v>0</v>
-      </c>
-      <c r="K13" s="36">
+      <c r="G13" s="36">
         <v>6200</v>
       </c>
-      <c r="L13" s="38">
-        <v>0</v>
-      </c>
-      <c r="M13" s="39">
+      <c r="H13" s="38">
+        <v>0</v>
+      </c>
+      <c r="I13" s="39">
         <v>38.5</v>
       </c>
-      <c r="N13" s="40">
-        <v>0</v>
-      </c>
-      <c r="O13" s="35"/>
-      <c r="Q13" s="38">
-        <v>0</v>
-      </c>
-      <c r="R13" s="35">
-        <v>0</v>
-      </c>
-      <c r="S13" s="38">
-        <v>0</v>
-      </c>
-      <c r="T13" s="41">
-        <v>0</v>
-      </c>
-      <c r="U13" s="42">
+      <c r="J13" s="40">
+        <v>0</v>
+      </c>
+      <c r="K13" s="35"/>
+      <c r="M13" s="38">
+        <v>0</v>
+      </c>
+      <c r="N13" s="35">
+        <v>0</v>
+      </c>
+      <c r="O13" s="38">
+        <v>0</v>
+      </c>
+      <c r="P13" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="42">
+        <v>0</v>
+      </c>
+      <c r="R13" s="36">
+        <v>0</v>
+      </c>
+      <c r="S13" s="36">
+        <v>0</v>
+      </c>
+      <c r="T13" s="36">
+        <v>0</v>
+      </c>
+      <c r="U13" s="36">
         <v>0</v>
       </c>
       <c r="V13" s="36">
@@ -12382,21 +12213,13 @@
       <c r="AM13" s="36">
         <v>0</v>
       </c>
-      <c r="AN13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN13" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
       <c r="AS13"/>
       <c r="AT13"/>
       <c r="AU13"/>
@@ -13404,12 +13227,8 @@
       <c r="ANI13"/>
       <c r="ANJ13"/>
       <c r="ANK13"/>
-      <c r="ANL13"/>
-      <c r="ANM13"/>
-      <c r="ANN13"/>
-      <c r="ANO13"/>
     </row>
-    <row r="14" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>36</v>
       </c>
@@ -13428,44 +13247,44 @@
       <c r="F14" s="35">
         <v>0</v>
       </c>
-      <c r="G14" s="96">
-        <v>0</v>
-      </c>
-      <c r="H14" s="96">
-        <v>0</v>
-      </c>
-      <c r="I14" s="96">
-        <v>0</v>
-      </c>
-      <c r="J14" s="97">
-        <v>0</v>
-      </c>
-      <c r="K14" s="36">
-        <v>0</v>
-      </c>
-      <c r="L14" s="38">
-        <v>0</v>
-      </c>
-      <c r="M14" s="39">
+      <c r="G14" s="36">
+        <v>0</v>
+      </c>
+      <c r="H14" s="38">
+        <v>0</v>
+      </c>
+      <c r="I14" s="39">
         <v>384.2</v>
       </c>
-      <c r="N14" s="40">
-        <v>0</v>
-      </c>
-      <c r="O14" s="35"/>
-      <c r="Q14" s="38">
-        <v>0</v>
-      </c>
-      <c r="R14" s="35">
-        <v>0</v>
-      </c>
-      <c r="S14" s="38">
-        <v>0</v>
-      </c>
-      <c r="T14" s="41">
-        <v>0</v>
-      </c>
-      <c r="U14" s="42">
+      <c r="J14" s="40">
+        <v>0</v>
+      </c>
+      <c r="K14" s="35"/>
+      <c r="M14" s="38">
+        <v>0</v>
+      </c>
+      <c r="N14" s="35">
+        <v>0</v>
+      </c>
+      <c r="O14" s="38">
+        <v>0</v>
+      </c>
+      <c r="P14" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="42">
+        <v>0</v>
+      </c>
+      <c r="R14" s="36">
+        <v>0</v>
+      </c>
+      <c r="S14" s="36">
+        <v>0</v>
+      </c>
+      <c r="T14" s="36">
+        <v>0</v>
+      </c>
+      <c r="U14" s="36">
         <v>0</v>
       </c>
       <c r="V14" s="36">
@@ -13522,21 +13341,13 @@
       <c r="AM14" s="36">
         <v>0</v>
       </c>
-      <c r="AN14" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN14" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14"/>
       <c r="AS14"/>
       <c r="AT14"/>
       <c r="AU14"/>
@@ -14544,12 +14355,8 @@
       <c r="ANI14"/>
       <c r="ANJ14"/>
       <c r="ANK14"/>
-      <c r="ANL14"/>
-      <c r="ANM14"/>
-      <c r="ANN14"/>
-      <c r="ANO14"/>
     </row>
-    <row r="15" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>37</v>
       </c>
@@ -14568,44 +14375,44 @@
       <c r="F15" s="35">
         <v>0</v>
       </c>
-      <c r="G15" s="96">
-        <v>0</v>
-      </c>
-      <c r="H15" s="96">
-        <v>0</v>
-      </c>
-      <c r="I15" s="96">
-        <v>0</v>
-      </c>
-      <c r="J15" s="97">
-        <v>0</v>
-      </c>
-      <c r="K15" s="36">
-        <v>0</v>
-      </c>
-      <c r="L15" s="38">
-        <v>0</v>
-      </c>
-      <c r="M15" s="39">
+      <c r="G15" s="36">
+        <v>0</v>
+      </c>
+      <c r="H15" s="38">
+        <v>0</v>
+      </c>
+      <c r="I15" s="39">
         <v>2000</v>
       </c>
-      <c r="N15" s="40">
-        <v>0</v>
-      </c>
-      <c r="O15" s="35"/>
-      <c r="Q15" s="38">
-        <v>0</v>
-      </c>
-      <c r="R15" s="35">
-        <v>0</v>
-      </c>
-      <c r="S15" s="38">
-        <v>0</v>
-      </c>
-      <c r="T15" s="41">
-        <v>0</v>
-      </c>
-      <c r="U15" s="42">
+      <c r="J15" s="40">
+        <v>0</v>
+      </c>
+      <c r="K15" s="35"/>
+      <c r="M15" s="38">
+        <v>0</v>
+      </c>
+      <c r="N15" s="35">
+        <v>0</v>
+      </c>
+      <c r="O15" s="38">
+        <v>0</v>
+      </c>
+      <c r="P15" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="42">
+        <v>0</v>
+      </c>
+      <c r="R15" s="36">
+        <v>0</v>
+      </c>
+      <c r="S15" s="36">
+        <v>0</v>
+      </c>
+      <c r="T15" s="36">
+        <v>0</v>
+      </c>
+      <c r="U15" s="36">
         <v>0</v>
       </c>
       <c r="V15" s="36">
@@ -14662,21 +14469,13 @@
       <c r="AM15" s="36">
         <v>0</v>
       </c>
-      <c r="AN15" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN15" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
       <c r="AS15"/>
       <c r="AT15"/>
       <c r="AU15"/>
@@ -15684,12 +15483,8 @@
       <c r="ANI15"/>
       <c r="ANJ15"/>
       <c r="ANK15"/>
-      <c r="ANL15"/>
-      <c r="ANM15"/>
-      <c r="ANN15"/>
-      <c r="ANO15"/>
     </row>
-    <row r="16" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
         <v>38</v>
       </c>
@@ -15708,44 +15503,44 @@
       <c r="F16" s="35">
         <v>0</v>
       </c>
-      <c r="G16" s="96">
-        <v>0</v>
-      </c>
-      <c r="H16" s="96">
-        <v>0</v>
-      </c>
-      <c r="I16" s="96">
-        <v>0</v>
-      </c>
-      <c r="J16" s="97">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36">
-        <v>0</v>
-      </c>
-      <c r="L16" s="38">
-        <v>0</v>
-      </c>
-      <c r="M16" s="39">
+      <c r="G16" s="36">
+        <v>0</v>
+      </c>
+      <c r="H16" s="38">
+        <v>0</v>
+      </c>
+      <c r="I16" s="39">
         <v>120</v>
       </c>
-      <c r="N16" s="40">
-        <v>0</v>
-      </c>
-      <c r="O16" s="35"/>
-      <c r="Q16" s="38">
-        <v>0</v>
-      </c>
-      <c r="R16" s="35">
-        <v>0</v>
-      </c>
-      <c r="S16" s="38">
-        <v>0</v>
-      </c>
-      <c r="T16" s="41">
-        <v>0</v>
-      </c>
-      <c r="U16" s="42">
+      <c r="J16" s="40">
+        <v>0</v>
+      </c>
+      <c r="K16" s="35"/>
+      <c r="M16" s="38">
+        <v>0</v>
+      </c>
+      <c r="N16" s="35">
+        <v>0</v>
+      </c>
+      <c r="O16" s="38">
+        <v>0</v>
+      </c>
+      <c r="P16" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="42">
+        <v>0</v>
+      </c>
+      <c r="R16" s="36">
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
+        <v>0</v>
+      </c>
+      <c r="T16" s="36">
+        <v>0</v>
+      </c>
+      <c r="U16" s="36">
         <v>0</v>
       </c>
       <c r="V16" s="36">
@@ -15802,21 +15597,13 @@
       <c r="AM16" s="36">
         <v>0</v>
       </c>
-      <c r="AN16" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN16" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO16"/>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16"/>
       <c r="AS16"/>
       <c r="AT16"/>
       <c r="AU16"/>
@@ -16824,12 +16611,8 @@
       <c r="ANI16"/>
       <c r="ANJ16"/>
       <c r="ANK16"/>
-      <c r="ANL16"/>
-      <c r="ANM16"/>
-      <c r="ANN16"/>
-      <c r="ANO16"/>
     </row>
-    <row r="17" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>39</v>
       </c>
@@ -16848,44 +16631,44 @@
       <c r="F17" s="35">
         <v>0</v>
       </c>
-      <c r="G17" s="96">
-        <v>0</v>
-      </c>
-      <c r="H17" s="96">
-        <v>0</v>
-      </c>
-      <c r="I17" s="96">
-        <v>0</v>
-      </c>
-      <c r="J17" s="97">
-        <v>0</v>
-      </c>
-      <c r="K17" s="36">
+      <c r="G17" s="36">
         <v>1140</v>
       </c>
-      <c r="L17" s="38">
-        <v>0</v>
-      </c>
-      <c r="M17" s="39">
+      <c r="H17" s="38">
+        <v>0</v>
+      </c>
+      <c r="I17" s="39">
         <v>28</v>
       </c>
-      <c r="N17" s="40">
-        <v>0</v>
-      </c>
-      <c r="O17" s="35"/>
-      <c r="Q17" s="38">
-        <v>0</v>
-      </c>
-      <c r="R17" s="35">
-        <v>0</v>
-      </c>
-      <c r="S17" s="38">
-        <v>0</v>
-      </c>
-      <c r="T17" s="41">
-        <v>0</v>
-      </c>
-      <c r="U17" s="42">
+      <c r="J17" s="40">
+        <v>0</v>
+      </c>
+      <c r="K17" s="35"/>
+      <c r="M17" s="38">
+        <v>0</v>
+      </c>
+      <c r="N17" s="35">
+        <v>0</v>
+      </c>
+      <c r="O17" s="38">
+        <v>0</v>
+      </c>
+      <c r="P17" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="42">
+        <v>0</v>
+      </c>
+      <c r="R17" s="36">
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
+        <v>0</v>
+      </c>
+      <c r="T17" s="36">
+        <v>0</v>
+      </c>
+      <c r="U17" s="36">
         <v>0</v>
       </c>
       <c r="V17" s="36">
@@ -16942,21 +16725,13 @@
       <c r="AM17" s="36">
         <v>0</v>
       </c>
-      <c r="AN17" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN17" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO17"/>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+      <c r="AR17"/>
       <c r="AS17"/>
       <c r="AT17"/>
       <c r="AU17"/>
@@ -17964,12 +17739,8 @@
       <c r="ANI17"/>
       <c r="ANJ17"/>
       <c r="ANK17"/>
-      <c r="ANL17"/>
-      <c r="ANM17"/>
-      <c r="ANN17"/>
-      <c r="ANO17"/>
     </row>
-    <row r="18" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
         <v>40</v>
       </c>
@@ -17988,44 +17759,44 @@
       <c r="F18" s="35">
         <v>0</v>
       </c>
-      <c r="G18" s="96">
-        <v>0</v>
-      </c>
-      <c r="H18" s="96">
-        <v>0</v>
-      </c>
-      <c r="I18" s="96">
-        <v>0</v>
-      </c>
-      <c r="J18" s="97">
-        <v>0</v>
-      </c>
-      <c r="K18" s="36">
-        <v>0</v>
-      </c>
-      <c r="L18" s="38">
-        <v>0</v>
-      </c>
-      <c r="M18" s="39">
+      <c r="G18" s="36">
+        <v>0</v>
+      </c>
+      <c r="H18" s="38">
+        <v>0</v>
+      </c>
+      <c r="I18" s="39">
         <v>28</v>
       </c>
-      <c r="N18" s="40">
-        <v>0</v>
-      </c>
-      <c r="O18" s="35"/>
-      <c r="Q18" s="38">
-        <v>0</v>
-      </c>
-      <c r="R18" s="35">
-        <v>0</v>
-      </c>
-      <c r="S18" s="38">
-        <v>0</v>
-      </c>
-      <c r="T18" s="41">
-        <v>0</v>
-      </c>
-      <c r="U18" s="42">
+      <c r="J18" s="40">
+        <v>0</v>
+      </c>
+      <c r="K18" s="35"/>
+      <c r="M18" s="38">
+        <v>0</v>
+      </c>
+      <c r="N18" s="35">
+        <v>0</v>
+      </c>
+      <c r="O18" s="38">
+        <v>0</v>
+      </c>
+      <c r="P18" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="42">
+        <v>0</v>
+      </c>
+      <c r="R18" s="36">
+        <v>0</v>
+      </c>
+      <c r="S18" s="36">
+        <v>0</v>
+      </c>
+      <c r="T18" s="36">
+        <v>0</v>
+      </c>
+      <c r="U18" s="36">
         <v>0</v>
       </c>
       <c r="V18" s="36">
@@ -18082,21 +17853,13 @@
       <c r="AM18" s="36">
         <v>0</v>
       </c>
-      <c r="AN18" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN18" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18"/>
       <c r="AS18"/>
       <c r="AT18"/>
       <c r="AU18"/>
@@ -19104,12 +18867,8 @@
       <c r="ANI18"/>
       <c r="ANJ18"/>
       <c r="ANK18"/>
-      <c r="ANL18"/>
-      <c r="ANM18"/>
-      <c r="ANN18"/>
-      <c r="ANO18"/>
     </row>
-    <row r="19" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>41</v>
       </c>
@@ -19128,115 +18887,107 @@
       <c r="F19" s="35">
         <v>0</v>
       </c>
-      <c r="G19" s="96">
-        <v>0</v>
-      </c>
-      <c r="H19" s="96">
-        <v>0</v>
-      </c>
-      <c r="I19" s="96">
-        <v>0</v>
-      </c>
-      <c r="J19" s="97">
-        <v>0</v>
-      </c>
-      <c r="K19" s="36">
-        <v>0</v>
-      </c>
-      <c r="L19" s="38">
-        <v>0</v>
-      </c>
-      <c r="M19" s="39">
+      <c r="G19" s="36">
+        <v>0</v>
+      </c>
+      <c r="H19" s="38">
+        <v>0</v>
+      </c>
+      <c r="I19" s="39">
         <v>218</v>
       </c>
-      <c r="N19" s="40">
-        <v>0</v>
-      </c>
-      <c r="O19" s="35"/>
-      <c r="Q19" s="38">
+      <c r="J19" s="40">
+        <v>0</v>
+      </c>
+      <c r="K19" s="35"/>
+      <c r="M19" s="38">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R19" s="35">
+      <c r="N19" s="35">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="S19" s="38">
+      <c r="O19" s="38">
         <v>1</v>
       </c>
-      <c r="T19" s="41">
+      <c r="P19" s="41">
         <v>10.1109898130647</v>
       </c>
-      <c r="U19" s="42">
+      <c r="Q19" s="42">
         <v>-434.34489379048</v>
       </c>
+      <c r="R19" s="36">
+        <v>35</v>
+      </c>
+      <c r="S19" s="36">
+        <v>35</v>
+      </c>
+      <c r="T19" s="36">
+        <v>63</v>
+      </c>
+      <c r="U19" s="36">
+        <v>54</v>
+      </c>
       <c r="V19" s="36">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="W19" s="36">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="X19" s="36">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="Y19" s="36">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="Z19" s="36">
+        <v>64</v>
+      </c>
+      <c r="AA19" s="36">
+        <v>69</v>
+      </c>
+      <c r="AB19" s="36">
         <v>60</v>
       </c>
-      <c r="AA19" s="36">
-        <v>75</v>
-      </c>
-      <c r="AB19" s="36">
-        <v>100</v>
-      </c>
       <c r="AC19" s="36">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="AD19" s="36">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="AE19" s="36">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AF19" s="36">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="AG19" s="36">
         <v>69</v>
       </c>
       <c r="AH19" s="36">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="AI19" s="36">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AJ19" s="36">
-        <v>111</v>
+        <v>373</v>
       </c>
       <c r="AK19" s="36">
-        <v>69</v>
+        <v>340</v>
       </c>
       <c r="AL19" s="36">
-        <v>172</v>
+        <v>415</v>
       </c>
       <c r="AM19" s="36">
-        <v>282</v>
-      </c>
-      <c r="AN19" s="36">
-        <v>373</v>
-      </c>
-      <c r="AO19" s="36">
-        <v>340</v>
-      </c>
-      <c r="AP19" s="36">
-        <v>415</v>
-      </c>
-      <c r="AQ19" s="36">
         <v>440</v>
       </c>
-      <c r="AR19" s="38">
+      <c r="AN19" s="38">
         <v>345</v>
       </c>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19"/>
       <c r="AS19"/>
       <c r="AT19"/>
       <c r="AU19"/>
@@ -20244,12 +19995,8 @@
       <c r="ANI19"/>
       <c r="ANJ19"/>
       <c r="ANK19"/>
-      <c r="ANL19"/>
-      <c r="ANM19"/>
-      <c r="ANN19"/>
-      <c r="ANO19"/>
     </row>
-    <row r="20" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
         <v>42</v>
       </c>
@@ -20268,44 +20015,44 @@
       <c r="F20" s="35">
         <v>0</v>
       </c>
-      <c r="G20" s="96">
-        <v>0</v>
-      </c>
-      <c r="H20" s="96">
-        <v>0</v>
-      </c>
-      <c r="I20" s="96">
-        <v>0</v>
-      </c>
-      <c r="J20" s="97">
-        <v>0</v>
-      </c>
-      <c r="K20" s="36">
+      <c r="G20" s="36">
         <v>562</v>
       </c>
-      <c r="L20" s="38">
-        <v>0</v>
-      </c>
-      <c r="M20" s="39">
+      <c r="H20" s="38">
+        <v>0</v>
+      </c>
+      <c r="I20" s="39">
         <v>23.5</v>
       </c>
-      <c r="N20" s="40">
-        <v>0</v>
-      </c>
-      <c r="O20" s="35"/>
-      <c r="Q20" s="38">
-        <v>0</v>
-      </c>
-      <c r="R20" s="35">
-        <v>0</v>
-      </c>
-      <c r="S20" s="38">
-        <v>0</v>
-      </c>
-      <c r="T20" s="41">
-        <v>0</v>
-      </c>
-      <c r="U20" s="42">
+      <c r="J20" s="40">
+        <v>0</v>
+      </c>
+      <c r="K20" s="35"/>
+      <c r="M20" s="38">
+        <v>0</v>
+      </c>
+      <c r="N20" s="35">
+        <v>0</v>
+      </c>
+      <c r="O20" s="38">
+        <v>0</v>
+      </c>
+      <c r="P20" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="42">
+        <v>0</v>
+      </c>
+      <c r="R20" s="36">
+        <v>0</v>
+      </c>
+      <c r="S20" s="36">
+        <v>0</v>
+      </c>
+      <c r="T20" s="36">
+        <v>0</v>
+      </c>
+      <c r="U20" s="36">
         <v>0</v>
       </c>
       <c r="V20" s="36">
@@ -20362,21 +20109,13 @@
       <c r="AM20" s="36">
         <v>0</v>
       </c>
-      <c r="AN20" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR20" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN20" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO20"/>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20"/>
       <c r="AS20"/>
       <c r="AT20"/>
       <c r="AU20"/>
@@ -21384,12 +21123,8 @@
       <c r="ANI20"/>
       <c r="ANJ20"/>
       <c r="ANK20"/>
-      <c r="ANL20"/>
-      <c r="ANM20"/>
-      <c r="ANN20"/>
-      <c r="ANO20"/>
     </row>
-    <row r="21" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>43</v>
       </c>
@@ -21408,44 +21143,44 @@
       <c r="F21" s="35">
         <v>0</v>
       </c>
-      <c r="G21" s="96">
-        <v>0</v>
-      </c>
-      <c r="H21" s="96">
-        <v>0</v>
-      </c>
-      <c r="I21" s="96">
-        <v>0</v>
-      </c>
-      <c r="J21" s="97">
-        <v>0</v>
-      </c>
-      <c r="K21" s="36">
-        <v>0</v>
-      </c>
-      <c r="L21" s="38">
-        <v>0</v>
-      </c>
-      <c r="M21" s="39">
+      <c r="G21" s="36">
+        <v>0</v>
+      </c>
+      <c r="H21" s="38">
+        <v>0</v>
+      </c>
+      <c r="I21" s="39">
         <v>100</v>
       </c>
-      <c r="N21" s="40">
-        <v>0</v>
-      </c>
-      <c r="O21" s="35"/>
-      <c r="Q21" s="38">
-        <v>0</v>
-      </c>
-      <c r="R21" s="35">
-        <v>0</v>
-      </c>
-      <c r="S21" s="38">
-        <v>0</v>
-      </c>
-      <c r="T21" s="41">
-        <v>0</v>
-      </c>
-      <c r="U21" s="42">
+      <c r="J21" s="40">
+        <v>0</v>
+      </c>
+      <c r="K21" s="35"/>
+      <c r="M21" s="38">
+        <v>0</v>
+      </c>
+      <c r="N21" s="35">
+        <v>0</v>
+      </c>
+      <c r="O21" s="38">
+        <v>0</v>
+      </c>
+      <c r="P21" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="42">
+        <v>0</v>
+      </c>
+      <c r="R21" s="36">
+        <v>0</v>
+      </c>
+      <c r="S21" s="36">
+        <v>0</v>
+      </c>
+      <c r="T21" s="36">
+        <v>0</v>
+      </c>
+      <c r="U21" s="36">
         <v>0</v>
       </c>
       <c r="V21" s="36">
@@ -21502,21 +21237,13 @@
       <c r="AM21" s="36">
         <v>0</v>
       </c>
-      <c r="AN21" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN21" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO21"/>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21"/>
       <c r="AS21"/>
       <c r="AT21"/>
       <c r="AU21"/>
@@ -22524,12 +22251,8 @@
       <c r="ANI21"/>
       <c r="ANJ21"/>
       <c r="ANK21"/>
-      <c r="ANL21"/>
-      <c r="ANM21"/>
-      <c r="ANN21"/>
-      <c r="ANO21"/>
     </row>
-    <row r="22" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>44</v>
       </c>
@@ -22548,44 +22271,44 @@
       <c r="F22" s="35">
         <v>0</v>
       </c>
-      <c r="G22" s="96">
-        <v>0</v>
-      </c>
-      <c r="H22" s="96">
-        <v>0</v>
-      </c>
-      <c r="I22" s="96">
-        <v>0</v>
-      </c>
-      <c r="J22" s="97">
-        <v>0</v>
-      </c>
-      <c r="K22" s="36">
-        <v>0</v>
-      </c>
-      <c r="L22" s="38">
-        <v>0</v>
-      </c>
-      <c r="M22" s="39">
+      <c r="G22" s="36">
+        <v>0</v>
+      </c>
+      <c r="H22" s="38">
+        <v>0</v>
+      </c>
+      <c r="I22" s="39">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="N22" s="40">
-        <v>0</v>
-      </c>
-      <c r="O22" s="35"/>
-      <c r="Q22" s="38">
-        <v>0</v>
-      </c>
-      <c r="R22" s="35">
-        <v>0</v>
-      </c>
-      <c r="S22" s="38">
-        <v>0</v>
-      </c>
-      <c r="T22" s="41">
-        <v>0</v>
-      </c>
-      <c r="U22" s="42">
+      <c r="J22" s="40">
+        <v>0</v>
+      </c>
+      <c r="K22" s="35"/>
+      <c r="M22" s="38">
+        <v>0</v>
+      </c>
+      <c r="N22" s="35">
+        <v>0</v>
+      </c>
+      <c r="O22" s="38">
+        <v>0</v>
+      </c>
+      <c r="P22" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="42">
+        <v>0</v>
+      </c>
+      <c r="R22" s="36">
+        <v>0</v>
+      </c>
+      <c r="S22" s="36">
+        <v>0</v>
+      </c>
+      <c r="T22" s="36">
+        <v>0</v>
+      </c>
+      <c r="U22" s="36">
         <v>0</v>
       </c>
       <c r="V22" s="36">
@@ -22642,21 +22365,13 @@
       <c r="AM22" s="36">
         <v>0</v>
       </c>
-      <c r="AN22" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN22" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
       <c r="AS22"/>
       <c r="AT22"/>
       <c r="AU22"/>
@@ -23664,12 +23379,8 @@
       <c r="ANI22"/>
       <c r="ANJ22"/>
       <c r="ANK22"/>
-      <c r="ANL22"/>
-      <c r="ANM22"/>
-      <c r="ANN22"/>
-      <c r="ANO22"/>
     </row>
-    <row r="23" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>45</v>
       </c>
@@ -23688,115 +23399,107 @@
       <c r="F23" s="35">
         <v>0</v>
       </c>
-      <c r="G23" s="96">
-        <v>0</v>
-      </c>
-      <c r="H23" s="96">
-        <v>0</v>
-      </c>
-      <c r="I23" s="96">
-        <v>0</v>
-      </c>
-      <c r="J23" s="97">
-        <v>0</v>
-      </c>
-      <c r="K23" s="36">
-        <v>0</v>
-      </c>
-      <c r="L23" s="38">
-        <v>0</v>
-      </c>
-      <c r="M23" s="39">
+      <c r="G23" s="36">
+        <v>0</v>
+      </c>
+      <c r="H23" s="38">
+        <v>0</v>
+      </c>
+      <c r="I23" s="39">
         <v>3320</v>
       </c>
-      <c r="N23" s="40">
-        <v>0</v>
-      </c>
-      <c r="O23" s="35"/>
-      <c r="Q23" s="38">
+      <c r="J23" s="40">
+        <v>0</v>
+      </c>
+      <c r="K23" s="35"/>
+      <c r="M23" s="38">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R23" s="35">
+      <c r="N23" s="35">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="S23" s="38">
+      <c r="O23" s="38">
         <v>4.7100000000000003E-2</v>
       </c>
-      <c r="T23" s="41">
+      <c r="P23" s="41">
         <v>12.0529021132057</v>
       </c>
-      <c r="U23" s="42">
+      <c r="Q23" s="42">
         <v>-286.28398042464499</v>
       </c>
+      <c r="R23" s="36">
+        <v>145</v>
+      </c>
+      <c r="S23" s="36">
+        <v>239</v>
+      </c>
+      <c r="T23" s="36">
+        <v>200</v>
+      </c>
+      <c r="U23" s="36">
+        <v>230</v>
+      </c>
       <c r="V23" s="36">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="W23" s="36">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="X23" s="36">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="Y23" s="36">
-        <v>230</v>
+        <v>345</v>
       </c>
       <c r="Z23" s="36">
-        <v>230</v>
+        <v>335</v>
       </c>
       <c r="AA23" s="36">
-        <v>215</v>
+        <v>370</v>
       </c>
       <c r="AB23" s="36">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="AC23" s="36">
-        <v>345</v>
+        <v>490</v>
       </c>
       <c r="AD23" s="36">
-        <v>335</v>
+        <v>570</v>
       </c>
       <c r="AE23" s="36">
-        <v>370</v>
+        <v>533</v>
       </c>
       <c r="AF23" s="36">
-        <v>395</v>
+        <v>530</v>
       </c>
       <c r="AG23" s="36">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="AH23" s="36">
-        <v>570</v>
+        <v>479</v>
       </c>
       <c r="AI23" s="36">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="AJ23" s="36">
-        <v>530</v>
+        <v>622</v>
       </c>
       <c r="AK23" s="36">
-        <v>466</v>
+        <v>629</v>
       </c>
       <c r="AL23" s="36">
-        <v>479</v>
+        <v>564</v>
       </c>
       <c r="AM23" s="36">
-        <v>522</v>
-      </c>
-      <c r="AN23" s="36">
-        <v>622</v>
-      </c>
-      <c r="AO23" s="36">
-        <v>629</v>
-      </c>
-      <c r="AP23" s="36">
-        <v>564</v>
-      </c>
-      <c r="AQ23" s="36">
         <v>369</v>
       </c>
-      <c r="AR23" s="38">
+      <c r="AN23" s="38">
         <v>155</v>
       </c>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
       <c r="AS23"/>
       <c r="AT23"/>
       <c r="AU23"/>
@@ -24804,12 +24507,8 @@
       <c r="ANI23"/>
       <c r="ANJ23"/>
       <c r="ANK23"/>
-      <c r="ANL23"/>
-      <c r="ANM23"/>
-      <c r="ANN23"/>
-      <c r="ANO23"/>
     </row>
-    <row r="24" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
         <v>46</v>
       </c>
@@ -24829,121 +24528,113 @@
       <c r="F24" s="35">
         <v>0</v>
       </c>
-      <c r="G24" s="96">
-        <v>0</v>
-      </c>
-      <c r="H24" s="96">
-        <v>0</v>
-      </c>
-      <c r="I24" s="96">
-        <v>0</v>
-      </c>
-      <c r="J24" s="97">
-        <v>0</v>
-      </c>
-      <c r="K24" s="36">
+      <c r="G24" s="36">
         <v>29683</v>
       </c>
-      <c r="L24" s="38">
+      <c r="H24" s="38">
         <v>435</v>
       </c>
-      <c r="M24" s="39">
+      <c r="I24" s="39">
         <v>25</v>
       </c>
-      <c r="N24" s="40">
+      <c r="J24" s="40">
         <v>9.4</v>
       </c>
-      <c r="O24" s="35">
+      <c r="K24" s="35">
         <v>0.52</v>
       </c>
-      <c r="P24" s="36">
+      <c r="L24" s="36">
         <v>0.9</v>
       </c>
-      <c r="Q24" s="38">
-        <f>(O24+P24)/2</f>
+      <c r="M24" s="38">
+        <f>(K24+L24)/2</f>
         <v>0.71</v>
       </c>
-      <c r="R24" s="35">
+      <c r="N24" s="35">
         <v>160000</v>
       </c>
-      <c r="S24" s="38">
+      <c r="O24" s="38">
         <v>800000</v>
       </c>
-      <c r="T24" s="41">
+      <c r="P24" s="41">
         <v>80787194.164979905</v>
       </c>
-      <c r="U24" s="42">
+      <c r="Q24" s="42">
         <v>-2777690174.63939</v>
       </c>
+      <c r="R24" s="36">
+        <v>1000000000</v>
+      </c>
+      <c r="S24" s="36">
+        <v>999928230</v>
+      </c>
+      <c r="T24" s="36">
+        <v>1019944840</v>
+      </c>
+      <c r="U24" s="36">
+        <v>1039927180</v>
+      </c>
       <c r="V24" s="36">
-        <v>1000000000</v>
+        <v>1019893920</v>
       </c>
       <c r="W24" s="36">
-        <v>999928230</v>
+        <v>993844440</v>
       </c>
       <c r="X24" s="36">
-        <v>1019944840</v>
+        <v>1059821110</v>
       </c>
       <c r="Y24" s="36">
-        <v>1039927180</v>
+        <v>1059791350</v>
       </c>
       <c r="Z24" s="36">
-        <v>1019893920</v>
+        <v>1079735210</v>
       </c>
       <c r="AA24" s="36">
-        <v>993844440</v>
+        <v>1159623830</v>
       </c>
       <c r="AB24" s="36">
-        <v>1059821110</v>
+        <v>1339511300</v>
       </c>
       <c r="AC24" s="36">
-        <v>1059791350</v>
+        <v>1539358150</v>
       </c>
       <c r="AD24" s="36">
-        <v>1079735210</v>
+        <v>1799023770</v>
       </c>
       <c r="AE24" s="36">
-        <v>1159623830</v>
+        <v>1998410780</v>
       </c>
       <c r="AF24" s="36">
-        <v>1339511300</v>
+        <v>2217726110</v>
       </c>
       <c r="AG24" s="36">
-        <v>1539358150</v>
+        <v>2236160950</v>
       </c>
       <c r="AH24" s="36">
-        <v>1799023770</v>
+        <v>2584196110</v>
       </c>
       <c r="AI24" s="36">
-        <v>1998410780</v>
+        <v>2933714900</v>
       </c>
       <c r="AJ24" s="36">
-        <v>2217726110</v>
+        <v>2922833710</v>
       </c>
       <c r="AK24" s="36">
-        <v>2236160950</v>
+        <v>3102160850</v>
       </c>
       <c r="AL24" s="36">
-        <v>2584196110</v>
+        <v>3408008320</v>
       </c>
       <c r="AM24" s="36">
-        <v>2933714900</v>
-      </c>
-      <c r="AN24" s="36">
-        <v>2922833710</v>
-      </c>
-      <c r="AO24" s="36">
-        <v>3102160850</v>
-      </c>
-      <c r="AP24" s="36">
-        <v>3408008320</v>
-      </c>
-      <c r="AQ24" s="36">
         <v>3663619920</v>
       </c>
-      <c r="AR24" s="38">
+      <c r="AN24" s="38">
         <v>3568372660</v>
       </c>
+      <c r="AO24"/>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24"/>
       <c r="AS24"/>
       <c r="AT24"/>
       <c r="AU24"/>
@@ -25951,12 +25642,8 @@
       <c r="ANI24"/>
       <c r="ANJ24"/>
       <c r="ANK24"/>
-      <c r="ANL24"/>
-      <c r="ANM24"/>
-      <c r="ANN24"/>
-      <c r="ANO24"/>
     </row>
-    <row r="25" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>47</v>
       </c>
@@ -25975,44 +25662,44 @@
       <c r="F25" s="35">
         <v>0</v>
       </c>
-      <c r="G25" s="96">
-        <v>0</v>
-      </c>
-      <c r="H25" s="96">
-        <v>0</v>
-      </c>
-      <c r="I25" s="96">
-        <v>0</v>
-      </c>
-      <c r="J25" s="97">
-        <v>0</v>
-      </c>
-      <c r="K25" s="36">
-        <v>0</v>
-      </c>
-      <c r="L25" s="38">
-        <v>0</v>
-      </c>
-      <c r="M25" s="39">
+      <c r="G25" s="36">
+        <v>0</v>
+      </c>
+      <c r="H25" s="38">
+        <v>0</v>
+      </c>
+      <c r="I25" s="39">
         <v>21.5</v>
       </c>
-      <c r="N25" s="40">
-        <v>0</v>
-      </c>
-      <c r="O25" s="35"/>
-      <c r="Q25" s="38">
-        <v>0</v>
-      </c>
-      <c r="R25" s="35">
-        <v>0</v>
-      </c>
-      <c r="S25" s="38">
-        <v>0</v>
-      </c>
-      <c r="T25" s="41">
-        <v>0</v>
-      </c>
-      <c r="U25" s="42">
+      <c r="J25" s="40">
+        <v>0</v>
+      </c>
+      <c r="K25" s="35"/>
+      <c r="M25" s="38">
+        <v>0</v>
+      </c>
+      <c r="N25" s="35">
+        <v>0</v>
+      </c>
+      <c r="O25" s="38">
+        <v>0</v>
+      </c>
+      <c r="P25" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="42">
+        <v>0</v>
+      </c>
+      <c r="R25" s="36">
+        <v>0</v>
+      </c>
+      <c r="S25" s="36">
+        <v>0</v>
+      </c>
+      <c r="T25" s="36">
+        <v>0</v>
+      </c>
+      <c r="U25" s="36">
         <v>0</v>
       </c>
       <c r="V25" s="36">
@@ -26069,21 +25756,13 @@
       <c r="AM25" s="36">
         <v>0</v>
       </c>
-      <c r="AN25" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP25" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR25" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN25" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO25"/>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25"/>
       <c r="AS25"/>
       <c r="AT25"/>
       <c r="AU25"/>
@@ -27091,12 +26770,8 @@
       <c r="ANI25"/>
       <c r="ANJ25"/>
       <c r="ANK25"/>
-      <c r="ANL25"/>
-      <c r="ANM25"/>
-      <c r="ANN25"/>
-      <c r="ANO25"/>
     </row>
-    <row r="26" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
         <v>48</v>
       </c>
@@ -27115,44 +26790,44 @@
       <c r="F26" s="35">
         <v>0</v>
       </c>
-      <c r="G26" s="96">
-        <v>0</v>
-      </c>
-      <c r="H26" s="96">
-        <v>0</v>
-      </c>
-      <c r="I26" s="96">
-        <v>0</v>
-      </c>
-      <c r="J26" s="97">
-        <v>0</v>
-      </c>
-      <c r="K26" s="36">
+      <c r="G26" s="36">
         <v>7500</v>
       </c>
-      <c r="L26" s="38">
-        <v>0</v>
-      </c>
-      <c r="M26" s="39">
+      <c r="H26" s="38">
+        <v>0</v>
+      </c>
+      <c r="I26" s="39">
         <v>3</v>
       </c>
-      <c r="N26" s="40">
-        <v>0</v>
-      </c>
-      <c r="O26" s="35"/>
-      <c r="Q26" s="38">
-        <v>0</v>
-      </c>
-      <c r="R26" s="35">
-        <v>0</v>
-      </c>
-      <c r="S26" s="38">
-        <v>0</v>
-      </c>
-      <c r="T26" s="41">
-        <v>0</v>
-      </c>
-      <c r="U26" s="42">
+      <c r="J26" s="40">
+        <v>0</v>
+      </c>
+      <c r="K26" s="35"/>
+      <c r="M26" s="38">
+        <v>0</v>
+      </c>
+      <c r="N26" s="35">
+        <v>0</v>
+      </c>
+      <c r="O26" s="38">
+        <v>0</v>
+      </c>
+      <c r="P26" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="42">
+        <v>0</v>
+      </c>
+      <c r="R26" s="36">
+        <v>0</v>
+      </c>
+      <c r="S26" s="36">
+        <v>0</v>
+      </c>
+      <c r="T26" s="36">
+        <v>0</v>
+      </c>
+      <c r="U26" s="36">
         <v>0</v>
       </c>
       <c r="V26" s="36">
@@ -27209,21 +26884,13 @@
       <c r="AM26" s="36">
         <v>0</v>
       </c>
-      <c r="AN26" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN26" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO26"/>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+      <c r="AR26"/>
       <c r="AS26"/>
       <c r="AT26"/>
       <c r="AU26"/>
@@ -28231,12 +27898,8 @@
       <c r="ANI26"/>
       <c r="ANJ26"/>
       <c r="ANK26"/>
-      <c r="ANL26"/>
-      <c r="ANM26"/>
-      <c r="ANN26"/>
-      <c r="ANO26"/>
     </row>
-    <row r="27" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
         <v>49</v>
       </c>
@@ -28255,44 +27918,44 @@
       <c r="F27" s="35">
         <v>0</v>
       </c>
-      <c r="G27" s="96">
-        <v>0</v>
-      </c>
-      <c r="H27" s="96">
-        <v>0</v>
-      </c>
-      <c r="I27" s="96">
-        <v>0</v>
-      </c>
-      <c r="J27" s="97">
-        <v>0</v>
-      </c>
-      <c r="K27" s="36">
-        <v>0</v>
-      </c>
-      <c r="L27" s="38">
-        <v>0</v>
-      </c>
-      <c r="M27" s="39">
+      <c r="G27" s="36">
+        <v>0</v>
+      </c>
+      <c r="H27" s="38">
+        <v>0</v>
+      </c>
+      <c r="I27" s="39">
         <v>5.3</v>
       </c>
-      <c r="N27" s="40">
-        <v>0</v>
-      </c>
-      <c r="O27" s="35"/>
-      <c r="Q27" s="38">
-        <v>0</v>
-      </c>
-      <c r="R27" s="35">
-        <v>0</v>
-      </c>
-      <c r="S27" s="38">
-        <v>0</v>
-      </c>
-      <c r="T27" s="41">
-        <v>0</v>
-      </c>
-      <c r="U27" s="42">
+      <c r="J27" s="40">
+        <v>0</v>
+      </c>
+      <c r="K27" s="35"/>
+      <c r="M27" s="38">
+        <v>0</v>
+      </c>
+      <c r="N27" s="35">
+        <v>0</v>
+      </c>
+      <c r="O27" s="38">
+        <v>0</v>
+      </c>
+      <c r="P27" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="42">
+        <v>0</v>
+      </c>
+      <c r="R27" s="36">
+        <v>0</v>
+      </c>
+      <c r="S27" s="36">
+        <v>0</v>
+      </c>
+      <c r="T27" s="36">
+        <v>0</v>
+      </c>
+      <c r="U27" s="36">
         <v>0</v>
       </c>
       <c r="V27" s="36">
@@ -28349,21 +28012,13 @@
       <c r="AM27" s="36">
         <v>0</v>
       </c>
-      <c r="AN27" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN27" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO27"/>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+      <c r="AR27"/>
       <c r="AS27"/>
       <c r="AT27"/>
       <c r="AU27"/>
@@ -29371,12 +29026,8 @@
       <c r="ANI27"/>
       <c r="ANJ27"/>
       <c r="ANK27"/>
-      <c r="ANL27"/>
-      <c r="ANM27"/>
-      <c r="ANN27"/>
-      <c r="ANO27"/>
     </row>
-    <row r="28" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
         <v>50</v>
       </c>
@@ -29395,44 +29046,44 @@
       <c r="F28" s="35">
         <v>0</v>
       </c>
-      <c r="G28" s="96">
-        <v>0</v>
-      </c>
-      <c r="H28" s="96">
-        <v>0</v>
-      </c>
-      <c r="I28" s="96">
-        <v>0</v>
-      </c>
-      <c r="J28" s="97">
-        <v>0</v>
-      </c>
-      <c r="K28" s="36">
-        <v>0</v>
-      </c>
-      <c r="L28" s="38">
-        <v>0</v>
-      </c>
-      <c r="M28" s="39">
+      <c r="G28" s="36">
+        <v>0</v>
+      </c>
+      <c r="H28" s="38">
+        <v>0</v>
+      </c>
+      <c r="I28" s="39">
         <v>0.85</v>
       </c>
-      <c r="N28" s="40">
-        <v>0</v>
-      </c>
-      <c r="O28" s="35"/>
-      <c r="Q28" s="38">
-        <v>0</v>
-      </c>
-      <c r="R28" s="35">
-        <v>0</v>
-      </c>
-      <c r="S28" s="38">
-        <v>0</v>
-      </c>
-      <c r="T28" s="41">
-        <v>0</v>
-      </c>
-      <c r="U28" s="42">
+      <c r="J28" s="40">
+        <v>0</v>
+      </c>
+      <c r="K28" s="35"/>
+      <c r="M28" s="38">
+        <v>0</v>
+      </c>
+      <c r="N28" s="35">
+        <v>0</v>
+      </c>
+      <c r="O28" s="38">
+        <v>0</v>
+      </c>
+      <c r="P28" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="42">
+        <v>0</v>
+      </c>
+      <c r="R28" s="36">
+        <v>0</v>
+      </c>
+      <c r="S28" s="36">
+        <v>0</v>
+      </c>
+      <c r="T28" s="36">
+        <v>0</v>
+      </c>
+      <c r="U28" s="36">
         <v>0</v>
       </c>
       <c r="V28" s="36">
@@ -29489,21 +29140,13 @@
       <c r="AM28" s="36">
         <v>0</v>
       </c>
-      <c r="AN28" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN28" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO28"/>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28"/>
       <c r="AS28"/>
       <c r="AT28"/>
       <c r="AU28"/>
@@ -30511,12 +30154,8 @@
       <c r="ANI28"/>
       <c r="ANJ28"/>
       <c r="ANK28"/>
-      <c r="ANL28"/>
-      <c r="ANM28"/>
-      <c r="ANN28"/>
-      <c r="ANO28"/>
     </row>
-    <row r="29" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
         <v>51</v>
       </c>
@@ -30535,115 +30174,107 @@
       <c r="F29" s="35">
         <v>34.4</v>
       </c>
-      <c r="G29" s="97">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="97">
-        <v>0.12</v>
-      </c>
-      <c r="I29" s="97">
-        <v>0.67400000000000004</v>
-      </c>
-      <c r="J29" s="97">
-        <v>0.67</v>
-      </c>
-      <c r="K29" s="36">
-        <v>0</v>
-      </c>
-      <c r="L29" s="38">
-        <v>0</v>
-      </c>
-      <c r="M29" s="39">
+      <c r="G29" s="36">
+        <v>0</v>
+      </c>
+      <c r="H29" s="38">
+        <v>0</v>
+      </c>
+      <c r="I29" s="39">
         <v>853</v>
       </c>
-      <c r="N29" s="40">
-        <v>0</v>
-      </c>
-      <c r="O29" s="35"/>
-      <c r="Q29" s="38">
+      <c r="J29" s="40">
+        <v>0</v>
+      </c>
+      <c r="K29" s="35"/>
+      <c r="M29" s="38">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R29" s="35">
+      <c r="N29" s="35">
         <v>13.5</v>
       </c>
-      <c r="S29" s="38">
+      <c r="O29" s="38">
         <v>39.5</v>
       </c>
-      <c r="T29" s="41">
+      <c r="P29" s="41">
         <v>804.07748378876397</v>
       </c>
-      <c r="U29" s="42">
+      <c r="Q29" s="42">
         <v>-25209.405062563001</v>
       </c>
+      <c r="R29" s="36">
+        <v>6100</v>
+      </c>
+      <c r="S29" s="36">
+        <v>6300</v>
+      </c>
+      <c r="T29" s="36">
+        <v>11000</v>
+      </c>
+      <c r="U29" s="36">
+        <v>14000</v>
+      </c>
       <c r="V29" s="36">
-        <v>6100</v>
+        <v>15000</v>
       </c>
       <c r="W29" s="36">
-        <v>6300</v>
+        <v>14000</v>
       </c>
       <c r="X29" s="36">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="Y29" s="36">
-        <v>14000</v>
+        <v>15100</v>
       </c>
       <c r="Z29" s="36">
-        <v>15000</v>
+        <v>14200</v>
       </c>
       <c r="AA29" s="36">
-        <v>14000</v>
+        <v>15100</v>
       </c>
       <c r="AB29" s="36">
-        <v>14000</v>
+        <v>20200</v>
       </c>
       <c r="AC29" s="36">
-        <v>15100</v>
+        <v>20600</v>
       </c>
       <c r="AD29" s="36">
-        <v>14200</v>
+        <v>23500</v>
       </c>
       <c r="AE29" s="36">
-        <v>15100</v>
+        <v>25800</v>
       </c>
       <c r="AF29" s="36">
-        <v>20200</v>
+        <v>25400</v>
       </c>
       <c r="AG29" s="36">
-        <v>20600</v>
+        <v>18800</v>
       </c>
       <c r="AH29" s="36">
-        <v>23500</v>
+        <v>28100</v>
       </c>
       <c r="AI29" s="36">
-        <v>25800</v>
+        <v>34100</v>
       </c>
       <c r="AJ29" s="36">
-        <v>25400</v>
+        <v>35000</v>
       </c>
       <c r="AK29" s="36">
-        <v>18800</v>
+        <v>34000</v>
       </c>
       <c r="AL29" s="36">
-        <v>28100</v>
+        <v>31700</v>
       </c>
       <c r="AM29" s="36">
-        <v>34100</v>
-      </c>
-      <c r="AN29" s="36">
+        <v>31500</v>
+      </c>
+      <c r="AN29" s="38">
         <v>35000</v>
       </c>
-      <c r="AO29" s="36">
-        <v>34000</v>
-      </c>
-      <c r="AP29" s="36">
-        <v>31700</v>
-      </c>
-      <c r="AQ29" s="36">
-        <v>31500</v>
-      </c>
-      <c r="AR29" s="38">
-        <v>35000</v>
-      </c>
+      <c r="AO29"/>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+      <c r="AR29"/>
       <c r="AS29"/>
       <c r="AT29"/>
       <c r="AU29"/>
@@ -31651,12 +31282,8 @@
       <c r="ANI29"/>
       <c r="ANJ29"/>
       <c r="ANK29"/>
-      <c r="ANL29"/>
-      <c r="ANM29"/>
-      <c r="ANN29"/>
-      <c r="ANO29"/>
     </row>
-    <row r="30" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
         <v>52</v>
       </c>
@@ -31675,44 +31302,44 @@
       <c r="F30" s="35">
         <v>0</v>
       </c>
-      <c r="G30" s="97">
-        <v>0</v>
-      </c>
-      <c r="H30" s="97">
-        <v>0</v>
-      </c>
-      <c r="I30" s="97">
-        <v>0</v>
-      </c>
-      <c r="J30" s="97">
-        <v>0</v>
-      </c>
-      <c r="K30" s="36">
-        <v>0</v>
-      </c>
-      <c r="L30" s="38">
-        <v>0</v>
-      </c>
-      <c r="M30" s="39">
+      <c r="G30" s="36">
+        <v>0</v>
+      </c>
+      <c r="H30" s="38">
+        <v>0</v>
+      </c>
+      <c r="I30" s="39">
         <v>100</v>
       </c>
-      <c r="N30" s="40">
-        <v>0</v>
-      </c>
-      <c r="O30" s="35"/>
-      <c r="Q30" s="38">
-        <v>0</v>
-      </c>
-      <c r="R30" s="35">
-        <v>0</v>
-      </c>
-      <c r="S30" s="38">
-        <v>0</v>
-      </c>
-      <c r="T30" s="41">
-        <v>0</v>
-      </c>
-      <c r="U30" s="42">
+      <c r="J30" s="40">
+        <v>0</v>
+      </c>
+      <c r="K30" s="35"/>
+      <c r="M30" s="38">
+        <v>0</v>
+      </c>
+      <c r="N30" s="35">
+        <v>0</v>
+      </c>
+      <c r="O30" s="38">
+        <v>0</v>
+      </c>
+      <c r="P30" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="42">
+        <v>0</v>
+      </c>
+      <c r="R30" s="36">
+        <v>0</v>
+      </c>
+      <c r="S30" s="36">
+        <v>0</v>
+      </c>
+      <c r="T30" s="36">
+        <v>0</v>
+      </c>
+      <c r="U30" s="36">
         <v>0</v>
       </c>
       <c r="V30" s="36">
@@ -31769,21 +31396,13 @@
       <c r="AM30" s="36">
         <v>0</v>
       </c>
-      <c r="AN30" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP30" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN30" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+      <c r="AR30"/>
       <c r="AS30"/>
       <c r="AT30"/>
       <c r="AU30"/>
@@ -32791,12 +32410,8 @@
       <c r="ANI30"/>
       <c r="ANJ30"/>
       <c r="ANK30"/>
-      <c r="ANL30"/>
-      <c r="ANM30"/>
-      <c r="ANN30"/>
-      <c r="ANO30"/>
     </row>
-    <row r="31" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
         <v>53</v>
       </c>
@@ -32818,112 +32433,104 @@
       <c r="G31" s="36">
         <v>0</v>
       </c>
-      <c r="H31" s="36">
-        <v>0</v>
-      </c>
-      <c r="I31" s="36">
-        <v>0</v>
-      </c>
-      <c r="J31" s="36">
-        <v>0</v>
-      </c>
-      <c r="K31" s="36">
-        <v>0</v>
-      </c>
-      <c r="L31" s="38">
-        <v>0</v>
-      </c>
-      <c r="M31" s="39">
+      <c r="H31" s="38">
+        <v>0</v>
+      </c>
+      <c r="I31" s="39">
         <v>220</v>
       </c>
-      <c r="N31" s="40">
-        <v>0</v>
-      </c>
-      <c r="O31" s="35"/>
-      <c r="Q31" s="38">
+      <c r="J31" s="40">
+        <v>0</v>
+      </c>
+      <c r="K31" s="35"/>
+      <c r="M31" s="38">
         <v>0.39</v>
       </c>
-      <c r="R31" s="35">
+      <c r="N31" s="35">
         <v>2400</v>
       </c>
-      <c r="S31" s="38">
+      <c r="O31" s="38">
         <v>12000</v>
       </c>
-      <c r="T31" s="41">
+      <c r="P31" s="41">
         <v>302664.460642363</v>
       </c>
-      <c r="U31" s="42">
+      <c r="Q31" s="42">
         <v>-11844018.973561</v>
       </c>
+      <c r="R31" s="36">
+        <v>2460000</v>
+      </c>
+      <c r="S31" s="36">
+        <v>2640000</v>
+      </c>
+      <c r="T31" s="36">
+        <v>2639990</v>
+      </c>
+      <c r="U31" s="36">
+        <v>3029990</v>
+      </c>
       <c r="V31" s="36">
-        <v>2460000</v>
+        <v>3089990</v>
       </c>
       <c r="W31" s="36">
-        <v>2640000</v>
+        <v>3089980</v>
       </c>
       <c r="X31" s="36">
-        <v>2639990</v>
+        <v>3089980</v>
       </c>
       <c r="Y31" s="36">
-        <v>3029990</v>
+        <v>3169980</v>
       </c>
       <c r="Z31" s="36">
-        <v>3089990</v>
+        <v>3319970</v>
       </c>
       <c r="AA31" s="36">
-        <v>3089980</v>
+        <v>3459940</v>
       </c>
       <c r="AB31" s="36">
-        <v>3089980</v>
+        <v>4269920</v>
       </c>
       <c r="AC31" s="36">
-        <v>3169980</v>
+        <v>4209830</v>
       </c>
       <c r="AD31" s="36">
-        <v>3319970</v>
+        <v>4059670</v>
       </c>
       <c r="AE31" s="36">
-        <v>3459940</v>
+        <v>4389210</v>
       </c>
       <c r="AF31" s="36">
-        <v>4269920</v>
+        <v>5428700</v>
       </c>
       <c r="AG31" s="36">
-        <v>4209830</v>
+        <v>5507890</v>
       </c>
       <c r="AH31" s="36">
-        <v>4059670</v>
+        <v>5756730</v>
       </c>
       <c r="AI31" s="36">
-        <v>4389210</v>
+        <v>5926210</v>
       </c>
       <c r="AJ31" s="36">
-        <v>5428700</v>
+        <v>6345590</v>
       </c>
       <c r="AK31" s="36">
-        <v>5507890</v>
+        <v>6905580</v>
       </c>
       <c r="AL31" s="36">
-        <v>5756730</v>
+        <v>8413980</v>
       </c>
       <c r="AM31" s="36">
-        <v>5926210</v>
-      </c>
-      <c r="AN31" s="36">
-        <v>6345590</v>
-      </c>
-      <c r="AO31" s="36">
-        <v>6905580</v>
-      </c>
-      <c r="AP31" s="36">
-        <v>8413980</v>
-      </c>
-      <c r="AQ31" s="36">
         <v>27692050</v>
       </c>
-      <c r="AR31" s="38">
+      <c r="AN31" s="38">
         <v>27689810</v>
       </c>
+      <c r="AO31"/>
+      <c r="AP31"/>
+      <c r="AQ31"/>
+      <c r="AR31"/>
       <c r="AS31"/>
       <c r="AT31"/>
       <c r="AU31"/>
@@ -33931,12 +33538,8 @@
       <c r="ANI31"/>
       <c r="ANJ31"/>
       <c r="ANK31"/>
-      <c r="ANL31"/>
-      <c r="ANM31"/>
-      <c r="ANN31"/>
-      <c r="ANO31"/>
     </row>
-    <row r="32" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
         <v>54</v>
       </c>
@@ -33956,115 +33559,107 @@
       <c r="F32" s="35">
         <v>1631</v>
       </c>
-      <c r="G32" s="97">
-        <v>0</v>
-      </c>
-      <c r="H32" s="97">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="I32" s="97">
-        <v>7.8E-2</v>
-      </c>
-      <c r="J32" s="97">
-        <v>0</v>
-      </c>
-      <c r="K32" s="36">
-        <v>0</v>
-      </c>
-      <c r="L32" s="38">
-        <v>0</v>
-      </c>
-      <c r="M32" s="39">
+      <c r="G32" s="36">
+        <v>0</v>
+      </c>
+      <c r="H32" s="38">
+        <v>0</v>
+      </c>
+      <c r="I32" s="39">
         <v>57.6</v>
       </c>
-      <c r="N32" s="40">
-        <v>0</v>
-      </c>
-      <c r="O32" s="35"/>
-      <c r="Q32" s="38">
+      <c r="J32" s="40">
+        <v>0</v>
+      </c>
+      <c r="K32" s="35"/>
+      <c r="M32" s="38">
         <v>0.53</v>
       </c>
-      <c r="R32" s="35">
-        <v>570</v>
-      </c>
-      <c r="S32" s="38">
-        <v>1030</v>
-      </c>
-      <c r="T32" s="41">
+      <c r="N32" s="35">
+        <v>1700</v>
+      </c>
+      <c r="O32" s="38">
+        <v>1700</v>
+      </c>
+      <c r="P32" s="41">
         <v>343350.03530150698</v>
       </c>
-      <c r="U32" s="42">
+      <c r="Q32" s="42">
         <v>-8586601.9007070903</v>
       </c>
+      <c r="R32" s="36">
+        <v>7190000</v>
+      </c>
+      <c r="S32" s="36">
+        <v>7579970</v>
+      </c>
+      <c r="T32" s="36">
+        <v>7729960</v>
+      </c>
+      <c r="U32" s="36">
+        <v>7679940</v>
+      </c>
       <c r="V32" s="36">
-        <v>7190000</v>
+        <v>7039890</v>
       </c>
       <c r="W32" s="36">
-        <v>7579970</v>
+        <v>6989840</v>
       </c>
       <c r="X32" s="36">
-        <v>7729960</v>
+        <v>7279850</v>
       </c>
       <c r="Y32" s="36">
-        <v>7679940</v>
+        <v>7599810</v>
       </c>
       <c r="Z32" s="36">
-        <v>7039890</v>
+        <v>8099700</v>
       </c>
       <c r="AA32" s="36">
-        <v>6989840</v>
+        <v>8199470</v>
       </c>
       <c r="AB32" s="36">
-        <v>7279850</v>
+        <v>9349300</v>
       </c>
       <c r="AC32" s="36">
-        <v>7599810</v>
+        <v>10499090</v>
       </c>
       <c r="AD32" s="36">
-        <v>8099700</v>
+        <v>11898380</v>
       </c>
       <c r="AE32" s="36">
-        <v>8199470</v>
+        <v>12596810</v>
       </c>
       <c r="AF32" s="36">
-        <v>9349300</v>
+        <v>13294950</v>
       </c>
       <c r="AG32" s="36">
-        <v>10499090</v>
+        <v>10790450</v>
       </c>
       <c r="AH32" s="36">
-        <v>11898380</v>
+        <v>13884820</v>
       </c>
       <c r="AI32" s="36">
-        <v>12596810</v>
+        <v>15983240</v>
       </c>
       <c r="AJ32" s="36">
-        <v>13294950</v>
+        <v>15780650</v>
       </c>
       <c r="AK32" s="36">
-        <v>10790450</v>
+        <v>16879270</v>
       </c>
       <c r="AL32" s="36">
-        <v>13884820</v>
+        <v>17767420</v>
       </c>
       <c r="AM32" s="36">
-        <v>15983240</v>
-      </c>
-      <c r="AN32" s="36">
-        <v>15780650</v>
-      </c>
-      <c r="AO32" s="36">
-        <v>16879270</v>
-      </c>
-      <c r="AP32" s="36">
-        <v>17767420</v>
-      </c>
-      <c r="AQ32" s="36">
         <v>17454820</v>
       </c>
-      <c r="AR32" s="38">
+      <c r="AN32" s="38">
         <v>15941730</v>
       </c>
+      <c r="AO32"/>
+      <c r="AP32"/>
+      <c r="AQ32"/>
+      <c r="AR32"/>
       <c r="AS32"/>
       <c r="AT32"/>
       <c r="AU32"/>
@@ -35072,12 +34667,8 @@
       <c r="ANI32"/>
       <c r="ANJ32"/>
       <c r="ANK32"/>
-      <c r="ANL32"/>
-      <c r="ANM32"/>
-      <c r="ANN32"/>
-      <c r="ANO32"/>
     </row>
-    <row r="33" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>55</v>
       </c>
@@ -35098,44 +34689,44 @@
       <c r="F33" s="35">
         <v>0</v>
       </c>
-      <c r="G33" s="96">
-        <v>0</v>
-      </c>
-      <c r="H33" s="96">
-        <v>0</v>
-      </c>
-      <c r="I33" s="96">
-        <v>0</v>
-      </c>
-      <c r="J33" s="97">
-        <v>0</v>
-      </c>
-      <c r="K33" s="36">
+      <c r="G33" s="36">
         <v>40</v>
       </c>
-      <c r="L33" s="38">
-        <v>0</v>
-      </c>
-      <c r="M33" s="39">
+      <c r="H33" s="38">
+        <v>0</v>
+      </c>
+      <c r="I33" s="39">
         <v>2000</v>
       </c>
-      <c r="N33" s="40">
-        <v>0</v>
-      </c>
-      <c r="O33" s="35"/>
-      <c r="Q33" s="38">
-        <v>0</v>
-      </c>
-      <c r="R33" s="35">
-        <v>0</v>
-      </c>
-      <c r="S33" s="38">
-        <v>0</v>
-      </c>
-      <c r="T33" s="41">
-        <v>0</v>
-      </c>
-      <c r="U33" s="42">
+      <c r="J33" s="40">
+        <v>0</v>
+      </c>
+      <c r="K33" s="35"/>
+      <c r="M33" s="38">
+        <v>0</v>
+      </c>
+      <c r="N33" s="35">
+        <v>0</v>
+      </c>
+      <c r="O33" s="38">
+        <v>0</v>
+      </c>
+      <c r="P33" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="42">
+        <v>0</v>
+      </c>
+      <c r="R33" s="36">
+        <v>0</v>
+      </c>
+      <c r="S33" s="36">
+        <v>0</v>
+      </c>
+      <c r="T33" s="36">
+        <v>0</v>
+      </c>
+      <c r="U33" s="36">
         <v>0</v>
       </c>
       <c r="V33" s="36">
@@ -35192,21 +34783,13 @@
       <c r="AM33" s="36">
         <v>0</v>
       </c>
-      <c r="AN33" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP33" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ33" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR33" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN33" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO33"/>
+      <c r="AP33"/>
+      <c r="AQ33"/>
+      <c r="AR33"/>
       <c r="AS33"/>
       <c r="AT33"/>
       <c r="AU33"/>
@@ -36214,12 +35797,8 @@
       <c r="ANI33"/>
       <c r="ANJ33"/>
       <c r="ANK33"/>
-      <c r="ANL33"/>
-      <c r="ANM33"/>
-      <c r="ANN33"/>
-      <c r="ANO33"/>
     </row>
-    <row r="34" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
         <v>56</v>
       </c>
@@ -36238,44 +35817,44 @@
       <c r="F34" s="35">
         <v>0</v>
       </c>
-      <c r="G34" s="96">
-        <v>0</v>
-      </c>
-      <c r="H34" s="96">
-        <v>0</v>
-      </c>
-      <c r="I34" s="96">
-        <v>0</v>
-      </c>
-      <c r="J34" s="97">
-        <v>0</v>
-      </c>
-      <c r="K34" s="36">
+      <c r="G34" s="36">
         <v>130000</v>
       </c>
-      <c r="L34" s="38">
+      <c r="H34" s="38">
         <v>1160</v>
       </c>
-      <c r="M34" s="39">
+      <c r="I34" s="39">
         <v>0.95</v>
       </c>
-      <c r="N34" s="40">
-        <v>0</v>
-      </c>
-      <c r="O34" s="35"/>
-      <c r="Q34" s="38">
-        <v>0</v>
-      </c>
-      <c r="R34" s="35">
-        <v>0</v>
-      </c>
-      <c r="S34" s="38">
-        <v>0</v>
-      </c>
-      <c r="T34" s="41">
-        <v>0</v>
-      </c>
-      <c r="U34" s="42">
+      <c r="J34" s="40">
+        <v>0</v>
+      </c>
+      <c r="K34" s="35"/>
+      <c r="M34" s="38">
+        <v>0</v>
+      </c>
+      <c r="N34" s="35">
+        <v>0</v>
+      </c>
+      <c r="O34" s="38">
+        <v>0</v>
+      </c>
+      <c r="P34" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="42">
+        <v>0</v>
+      </c>
+      <c r="R34" s="36">
+        <v>0</v>
+      </c>
+      <c r="S34" s="36">
+        <v>0</v>
+      </c>
+      <c r="T34" s="36">
+        <v>0</v>
+      </c>
+      <c r="U34" s="36">
         <v>0</v>
       </c>
       <c r="V34" s="36">
@@ -36332,21 +35911,13 @@
       <c r="AM34" s="36">
         <v>0</v>
       </c>
-      <c r="AN34" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN34" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO34"/>
+      <c r="AP34"/>
+      <c r="AQ34"/>
+      <c r="AR34"/>
       <c r="AS34"/>
       <c r="AT34"/>
       <c r="AU34"/>
@@ -37354,12 +36925,8 @@
       <c r="ANI34"/>
       <c r="ANJ34"/>
       <c r="ANK34"/>
-      <c r="ANL34"/>
-      <c r="ANM34"/>
-      <c r="ANN34"/>
-      <c r="ANO34"/>
     </row>
-    <row r="35" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
         <v>57</v>
       </c>
@@ -37379,115 +36946,107 @@
       <c r="F35" s="35">
         <v>0</v>
       </c>
-      <c r="G35" s="96">
-        <v>0</v>
-      </c>
-      <c r="H35" s="96">
-        <v>0</v>
-      </c>
-      <c r="I35" s="96">
-        <v>0</v>
-      </c>
-      <c r="J35" s="97">
-        <v>0</v>
-      </c>
-      <c r="K35" s="36">
-        <v>0</v>
-      </c>
-      <c r="L35" s="38">
-        <v>0</v>
-      </c>
-      <c r="M35" s="39">
+      <c r="G35" s="36">
+        <v>0</v>
+      </c>
+      <c r="H35" s="38">
+        <v>0</v>
+      </c>
+      <c r="I35" s="39">
         <v>378</v>
       </c>
-      <c r="N35" s="40">
-        <v>0</v>
-      </c>
-      <c r="O35" s="35"/>
-      <c r="Q35" s="38">
+      <c r="J35" s="40">
+        <v>0</v>
+      </c>
+      <c r="K35" s="35"/>
+      <c r="M35" s="38">
         <v>0.3</v>
       </c>
-      <c r="R35" s="35">
+      <c r="N35" s="35">
         <v>11</v>
       </c>
-      <c r="S35" s="38">
+      <c r="O35" s="38">
         <v>14</v>
       </c>
-      <c r="T35" s="41">
+      <c r="P35" s="41">
         <v>5023.5108697014803</v>
       </c>
-      <c r="U35" s="42">
+      <c r="Q35" s="42">
         <v>-107292.911532271</v>
       </c>
+      <c r="R35" s="36">
+        <v>104000</v>
+      </c>
+      <c r="S35" s="36">
+        <v>126000</v>
+      </c>
+      <c r="T35" s="36">
+        <v>128000</v>
+      </c>
+      <c r="U35" s="36">
+        <v>139990</v>
+      </c>
       <c r="V35" s="36">
-        <v>104000</v>
+        <v>134990</v>
       </c>
       <c r="W35" s="36">
-        <v>126000</v>
+        <v>121980</v>
       </c>
       <c r="X35" s="36">
-        <v>128000</v>
+        <v>128980</v>
       </c>
       <c r="Y35" s="36">
-        <v>139990</v>
+        <v>129980</v>
       </c>
       <c r="Z35" s="36">
-        <v>134990</v>
+        <v>122970</v>
       </c>
       <c r="AA35" s="36">
-        <v>121980</v>
+        <v>124950</v>
       </c>
       <c r="AB35" s="36">
-        <v>128980</v>
+        <v>140930</v>
       </c>
       <c r="AC35" s="36">
-        <v>129980</v>
+        <v>184910</v>
       </c>
       <c r="AD35" s="36">
-        <v>122970</v>
+        <v>183840</v>
       </c>
       <c r="AE35" s="36">
-        <v>124950</v>
+        <v>204680</v>
       </c>
       <c r="AF35" s="36">
-        <v>140930</v>
+        <v>217500</v>
       </c>
       <c r="AG35" s="36">
-        <v>184910</v>
+        <v>220040</v>
       </c>
       <c r="AH35" s="36">
-        <v>183840</v>
+        <v>240480</v>
       </c>
       <c r="AI35" s="36">
-        <v>204680</v>
+        <v>262320</v>
       </c>
       <c r="AJ35" s="36">
-        <v>217500</v>
+        <v>257060</v>
       </c>
       <c r="AK35" s="36">
-        <v>220040</v>
+        <v>255930</v>
       </c>
       <c r="AL35" s="36">
-        <v>240480</v>
+        <v>277740</v>
       </c>
       <c r="AM35" s="36">
-        <v>262320</v>
-      </c>
-      <c r="AN35" s="36">
-        <v>257060</v>
-      </c>
-      <c r="AO35" s="36">
-        <v>255930</v>
-      </c>
-      <c r="AP35" s="36">
-        <v>277740</v>
-      </c>
-      <c r="AQ35" s="36">
         <v>230480</v>
       </c>
-      <c r="AR35" s="38">
+      <c r="AN35" s="38">
         <v>221170</v>
       </c>
+      <c r="AO35"/>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+      <c r="AR35"/>
       <c r="AS35"/>
       <c r="AT35"/>
       <c r="AU35"/>
@@ -38495,12 +38054,8 @@
       <c r="ANI35"/>
       <c r="ANJ35"/>
       <c r="ANK35"/>
-      <c r="ANL35"/>
-      <c r="ANM35"/>
-      <c r="ANN35"/>
-      <c r="ANO35"/>
     </row>
-    <row r="36" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
         <v>58</v>
       </c>
@@ -38519,44 +38074,44 @@
       <c r="F36" s="35">
         <v>0</v>
       </c>
-      <c r="G36" s="96">
-        <v>0</v>
-      </c>
-      <c r="H36" s="96">
-        <v>0</v>
-      </c>
-      <c r="I36" s="96">
-        <v>0</v>
-      </c>
-      <c r="J36" s="97">
-        <v>0</v>
-      </c>
-      <c r="K36" s="36">
-        <v>0</v>
-      </c>
-      <c r="L36" s="38">
-        <v>0</v>
-      </c>
-      <c r="M36" s="39">
+      <c r="G36" s="36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="38">
+        <v>0</v>
+      </c>
+      <c r="I36" s="39">
         <v>21.5</v>
       </c>
-      <c r="N36" s="40">
-        <v>0</v>
-      </c>
-      <c r="O36" s="35"/>
-      <c r="Q36" s="38">
-        <v>0</v>
-      </c>
-      <c r="R36" s="35">
-        <v>0</v>
-      </c>
-      <c r="S36" s="38">
-        <v>0</v>
-      </c>
-      <c r="T36" s="41">
-        <v>0</v>
-      </c>
-      <c r="U36" s="42">
+      <c r="J36" s="40">
+        <v>0</v>
+      </c>
+      <c r="K36" s="35"/>
+      <c r="M36" s="38">
+        <v>0</v>
+      </c>
+      <c r="N36" s="35">
+        <v>0</v>
+      </c>
+      <c r="O36" s="38">
+        <v>0</v>
+      </c>
+      <c r="P36" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="42">
+        <v>0</v>
+      </c>
+      <c r="R36" s="36">
+        <v>0</v>
+      </c>
+      <c r="S36" s="36">
+        <v>0</v>
+      </c>
+      <c r="T36" s="36">
+        <v>0</v>
+      </c>
+      <c r="U36" s="36">
         <v>0</v>
       </c>
       <c r="V36" s="36">
@@ -38613,21 +38168,13 @@
       <c r="AM36" s="36">
         <v>0</v>
       </c>
-      <c r="AN36" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP36" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR36" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN36" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO36"/>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+      <c r="AR36"/>
       <c r="AS36"/>
       <c r="AT36"/>
       <c r="AU36"/>
@@ -39635,12 +39182,8 @@
       <c r="ANI36"/>
       <c r="ANJ36"/>
       <c r="ANK36"/>
-      <c r="ANL36"/>
-      <c r="ANM36"/>
-      <c r="ANN36"/>
-      <c r="ANO36"/>
     </row>
-    <row r="37" spans="1:1055" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
         <v>59</v>
       </c>
@@ -39659,44 +39202,44 @@
       <c r="F37" s="35">
         <v>0</v>
       </c>
-      <c r="G37" s="96">
-        <v>0</v>
-      </c>
-      <c r="H37" s="96">
-        <v>0</v>
-      </c>
-      <c r="I37" s="96">
-        <v>0</v>
-      </c>
-      <c r="J37" s="97">
-        <v>0</v>
-      </c>
-      <c r="K37" s="36">
-        <v>0</v>
-      </c>
-      <c r="L37" s="38">
-        <v>0</v>
-      </c>
-      <c r="M37" s="39">
-        <v>0</v>
-      </c>
-      <c r="N37" s="40">
-        <v>0</v>
-      </c>
-      <c r="O37" s="35"/>
-      <c r="Q37" s="38">
-        <v>0</v>
-      </c>
-      <c r="R37" s="35">
-        <v>0</v>
-      </c>
-      <c r="S37" s="38">
-        <v>0</v>
-      </c>
-      <c r="T37" s="41">
-        <v>0</v>
-      </c>
-      <c r="U37" s="42">
+      <c r="G37" s="36">
+        <v>0</v>
+      </c>
+      <c r="H37" s="38">
+        <v>0</v>
+      </c>
+      <c r="I37" s="39">
+        <v>0</v>
+      </c>
+      <c r="J37" s="40">
+        <v>0</v>
+      </c>
+      <c r="K37" s="35"/>
+      <c r="M37" s="38">
+        <v>0</v>
+      </c>
+      <c r="N37" s="35">
+        <v>0</v>
+      </c>
+      <c r="O37" s="38">
+        <v>0</v>
+      </c>
+      <c r="P37" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="42">
+        <v>0</v>
+      </c>
+      <c r="R37" s="36">
+        <v>0</v>
+      </c>
+      <c r="S37" s="36">
+        <v>0</v>
+      </c>
+      <c r="T37" s="36">
+        <v>0</v>
+      </c>
+      <c r="U37" s="36">
         <v>0</v>
       </c>
       <c r="V37" s="36">
@@ -39753,21 +39296,13 @@
       <c r="AM37" s="36">
         <v>0</v>
       </c>
-      <c r="AN37" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP37" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN37" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO37"/>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+      <c r="AR37"/>
       <c r="AS37"/>
       <c r="AT37"/>
       <c r="AU37"/>
@@ -40775,12 +40310,8 @@
       <c r="ANI37"/>
       <c r="ANJ37"/>
       <c r="ANK37"/>
-      <c r="ANL37"/>
-      <c r="ANM37"/>
-      <c r="ANN37"/>
-      <c r="ANO37"/>
     </row>
-    <row r="38" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
         <v>60</v>
       </c>
@@ -40799,44 +40330,44 @@
       <c r="F38" s="35">
         <v>0</v>
       </c>
-      <c r="G38" s="96">
-        <v>0</v>
-      </c>
-      <c r="H38" s="96">
-        <v>0</v>
-      </c>
-      <c r="I38" s="96">
-        <v>0</v>
-      </c>
-      <c r="J38" s="97">
-        <v>0</v>
-      </c>
-      <c r="K38" s="36">
-        <v>0</v>
-      </c>
-      <c r="L38" s="38">
-        <v>0</v>
-      </c>
-      <c r="M38" s="39">
+      <c r="G38" s="36">
+        <v>0</v>
+      </c>
+      <c r="H38" s="38">
+        <v>0</v>
+      </c>
+      <c r="I38" s="39">
         <v>384.2</v>
       </c>
-      <c r="N38" s="40">
-        <v>0</v>
-      </c>
-      <c r="O38" s="35"/>
-      <c r="Q38" s="38">
-        <v>0</v>
-      </c>
-      <c r="R38" s="45">
-        <v>0</v>
-      </c>
-      <c r="S38" s="46">
-        <v>0</v>
-      </c>
-      <c r="T38" s="41">
-        <v>0</v>
-      </c>
-      <c r="U38" s="42">
+      <c r="J38" s="40">
+        <v>0</v>
+      </c>
+      <c r="K38" s="35"/>
+      <c r="M38" s="38">
+        <v>0</v>
+      </c>
+      <c r="N38" s="45">
+        <v>0</v>
+      </c>
+      <c r="O38" s="46">
+        <v>0</v>
+      </c>
+      <c r="P38" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="42">
+        <v>0</v>
+      </c>
+      <c r="R38" s="36">
+        <v>0</v>
+      </c>
+      <c r="S38" s="36">
+        <v>0</v>
+      </c>
+      <c r="T38" s="36">
+        <v>0</v>
+      </c>
+      <c r="U38" s="36">
         <v>0</v>
       </c>
       <c r="V38" s="36">
@@ -40893,21 +40424,13 @@
       <c r="AM38" s="36">
         <v>0</v>
       </c>
-      <c r="AN38" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN38" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO38"/>
+      <c r="AP38"/>
+      <c r="AQ38"/>
+      <c r="AR38"/>
       <c r="AS38"/>
       <c r="AT38"/>
       <c r="AU38"/>
@@ -41915,12 +41438,8 @@
       <c r="ANI38"/>
       <c r="ANJ38"/>
       <c r="ANK38"/>
-      <c r="ANL38"/>
-      <c r="ANM38"/>
-      <c r="ANN38"/>
-      <c r="ANO38"/>
     </row>
-    <row r="39" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="34" t="s">
         <v>61</v>
       </c>
@@ -41940,121 +41459,113 @@
       <c r="F39" s="35">
         <v>0</v>
       </c>
-      <c r="G39" s="97">
-        <v>0</v>
-      </c>
-      <c r="H39" s="97">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="I39" s="97">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="J39" s="97">
-        <v>0.126</v>
-      </c>
-      <c r="K39" s="36">
-        <v>0</v>
-      </c>
-      <c r="L39" s="38">
-        <v>0</v>
-      </c>
-      <c r="M39" s="39">
+      <c r="G39" s="36">
+        <v>0</v>
+      </c>
+      <c r="H39" s="38">
+        <v>0</v>
+      </c>
+      <c r="I39" s="39">
         <v>164</v>
       </c>
-      <c r="N39" s="40">
-        <v>0</v>
-      </c>
-      <c r="O39" s="35">
+      <c r="J39" s="40">
+        <v>0</v>
+      </c>
+      <c r="K39" s="35">
         <v>0.56999999999999995</v>
       </c>
-      <c r="P39" s="36">
+      <c r="L39" s="36">
         <v>0.63</v>
       </c>
-      <c r="Q39" s="38">
-        <f>(O39+P39)/2</f>
+      <c r="M39" s="38">
+        <f>(K39+L39)/2</f>
         <v>0.6</v>
       </c>
-      <c r="R39" s="35">
+      <c r="N39" s="35">
         <v>81</v>
       </c>
-      <c r="S39" s="38">
+      <c r="O39" s="38">
         <v>130</v>
       </c>
-      <c r="T39" s="41">
+      <c r="P39" s="41">
         <v>40510.958042173501</v>
       </c>
-      <c r="U39" s="42">
+      <c r="Q39" s="42">
         <v>-772331.36137760605</v>
       </c>
+      <c r="R39" s="36">
+        <v>906000</v>
+      </c>
+      <c r="S39" s="36">
+        <v>1039680</v>
+      </c>
+      <c r="T39" s="36">
+        <v>1079770</v>
+      </c>
+      <c r="U39" s="36">
+        <v>1119700</v>
+      </c>
       <c r="V39" s="36">
-        <v>906000</v>
+        <v>1139590</v>
       </c>
       <c r="W39" s="36">
-        <v>1039680</v>
+        <v>1119400</v>
       </c>
       <c r="X39" s="36">
-        <v>1079770</v>
+        <v>1249270</v>
       </c>
       <c r="Y39" s="36">
-        <v>1119700</v>
+        <v>1329150</v>
       </c>
       <c r="Z39" s="36">
-        <v>1139590</v>
+        <v>1338990</v>
       </c>
       <c r="AA39" s="36">
-        <v>1119400</v>
+        <v>1398710</v>
       </c>
       <c r="AB39" s="36">
-        <v>1249270</v>
+        <v>1398340</v>
       </c>
       <c r="AC39" s="36">
-        <v>1329150</v>
+        <v>1487810</v>
       </c>
       <c r="AD39" s="36">
-        <v>1338990</v>
+        <v>1576940</v>
       </c>
       <c r="AE39" s="36">
-        <v>1398710</v>
+        <v>1655660</v>
       </c>
       <c r="AF39" s="36">
-        <v>1398340</v>
+        <v>1564350</v>
       </c>
       <c r="AG39" s="36">
-        <v>1487810</v>
+        <v>1391710</v>
       </c>
       <c r="AH39" s="36">
-        <v>1576940</v>
+        <v>1578370</v>
       </c>
       <c r="AI39" s="36">
-        <v>1655660</v>
+        <v>1927720</v>
       </c>
       <c r="AJ39" s="36">
-        <v>1564350</v>
+        <v>2206300</v>
       </c>
       <c r="AK39" s="36">
-        <v>1391710</v>
+        <v>2614500</v>
       </c>
       <c r="AL39" s="36">
-        <v>1578370</v>
+        <v>2427300</v>
       </c>
       <c r="AM39" s="36">
-        <v>1927720</v>
-      </c>
-      <c r="AN39" s="36">
-        <v>2206300</v>
-      </c>
-      <c r="AO39" s="36">
-        <v>2614500</v>
-      </c>
-      <c r="AP39" s="36">
-        <v>2427300</v>
-      </c>
-      <c r="AQ39" s="36">
         <v>2249800</v>
       </c>
-      <c r="AR39" s="38">
+      <c r="AN39" s="38">
         <v>2208450</v>
       </c>
+      <c r="AO39"/>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+      <c r="AR39"/>
       <c r="AS39"/>
       <c r="AT39"/>
       <c r="AU39"/>
@@ -43062,12 +42573,8 @@
       <c r="ANI39"/>
       <c r="ANJ39"/>
       <c r="ANK39"/>
-      <c r="ANL39"/>
-      <c r="ANM39"/>
-      <c r="ANN39"/>
-      <c r="ANO39"/>
     </row>
-    <row r="40" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
         <v>62</v>
       </c>
@@ -43086,44 +42593,44 @@
       <c r="F40" s="35">
         <v>0</v>
       </c>
-      <c r="G40" s="97">
-        <v>0</v>
-      </c>
-      <c r="H40" s="97">
-        <v>0</v>
-      </c>
-      <c r="I40" s="97">
-        <v>0</v>
-      </c>
-      <c r="J40" s="97">
-        <v>0</v>
-      </c>
-      <c r="K40" s="36">
-        <v>0</v>
-      </c>
-      <c r="L40" s="38">
-        <v>0</v>
-      </c>
-      <c r="M40" s="39">
-        <v>0</v>
-      </c>
-      <c r="N40" s="40">
-        <v>0</v>
-      </c>
-      <c r="O40" s="35"/>
-      <c r="Q40" s="38">
-        <v>0</v>
-      </c>
-      <c r="R40" s="35">
-        <v>0</v>
-      </c>
-      <c r="S40" s="38">
-        <v>0</v>
-      </c>
-      <c r="T40" s="41">
-        <v>0</v>
-      </c>
-      <c r="U40" s="42">
+      <c r="G40" s="36">
+        <v>0</v>
+      </c>
+      <c r="H40" s="38">
+        <v>0</v>
+      </c>
+      <c r="I40" s="39">
+        <v>0</v>
+      </c>
+      <c r="J40" s="40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="35"/>
+      <c r="M40" s="38">
+        <v>0</v>
+      </c>
+      <c r="N40" s="35">
+        <v>0</v>
+      </c>
+      <c r="O40" s="38">
+        <v>0</v>
+      </c>
+      <c r="P40" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="42">
+        <v>0</v>
+      </c>
+      <c r="R40" s="36">
+        <v>0</v>
+      </c>
+      <c r="S40" s="36">
+        <v>0</v>
+      </c>
+      <c r="T40" s="36">
+        <v>0</v>
+      </c>
+      <c r="U40" s="36">
         <v>0</v>
       </c>
       <c r="V40" s="36">
@@ -43180,21 +42687,13 @@
       <c r="AM40" s="36">
         <v>0</v>
       </c>
-      <c r="AN40" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP40" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ40" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR40" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN40" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO40"/>
+      <c r="AP40"/>
+      <c r="AQ40"/>
+      <c r="AR40"/>
       <c r="AS40"/>
       <c r="AT40"/>
       <c r="AU40"/>
@@ -44202,12 +43701,8 @@
       <c r="ANI40"/>
       <c r="ANJ40"/>
       <c r="ANK40"/>
-      <c r="ANL40"/>
-      <c r="ANM40"/>
-      <c r="ANN40"/>
-      <c r="ANO40"/>
     </row>
-    <row r="41" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
         <v>63</v>
       </c>
@@ -44226,44 +43721,44 @@
       <c r="F41" s="35">
         <v>0</v>
       </c>
-      <c r="G41" s="97">
-        <v>0</v>
-      </c>
-      <c r="H41" s="97">
-        <v>0</v>
-      </c>
-      <c r="I41" s="97">
-        <v>0</v>
-      </c>
-      <c r="J41" s="97">
-        <v>0</v>
-      </c>
-      <c r="K41" s="36">
-        <v>0</v>
-      </c>
-      <c r="L41" s="38">
-        <v>0</v>
-      </c>
-      <c r="M41" s="39">
-        <v>0</v>
-      </c>
-      <c r="N41" s="40">
-        <v>0</v>
-      </c>
-      <c r="O41" s="35"/>
-      <c r="Q41" s="38">
-        <v>0</v>
-      </c>
-      <c r="R41" s="35">
-        <v>0</v>
-      </c>
-      <c r="S41" s="38">
-        <v>0</v>
-      </c>
-      <c r="T41" s="41">
-        <v>0</v>
-      </c>
-      <c r="U41" s="42">
+      <c r="G41" s="36">
+        <v>0</v>
+      </c>
+      <c r="H41" s="38">
+        <v>0</v>
+      </c>
+      <c r="I41" s="39">
+        <v>0</v>
+      </c>
+      <c r="J41" s="40">
+        <v>0</v>
+      </c>
+      <c r="K41" s="35"/>
+      <c r="M41" s="38">
+        <v>0</v>
+      </c>
+      <c r="N41" s="35">
+        <v>0</v>
+      </c>
+      <c r="O41" s="38">
+        <v>0</v>
+      </c>
+      <c r="P41" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="42">
+        <v>0</v>
+      </c>
+      <c r="R41" s="36">
+        <v>0</v>
+      </c>
+      <c r="S41" s="36">
+        <v>0</v>
+      </c>
+      <c r="T41" s="36">
+        <v>0</v>
+      </c>
+      <c r="U41" s="36">
         <v>0</v>
       </c>
       <c r="V41" s="36">
@@ -44320,21 +43815,13 @@
       <c r="AM41" s="36">
         <v>0</v>
       </c>
-      <c r="AN41" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP41" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ41" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR41" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN41" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO41"/>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+      <c r="AR41"/>
       <c r="AS41"/>
       <c r="AT41"/>
       <c r="AU41"/>
@@ -45342,12 +44829,8 @@
       <c r="ANI41"/>
       <c r="ANJ41"/>
       <c r="ANK41"/>
-      <c r="ANL41"/>
-      <c r="ANM41"/>
-      <c r="ANN41"/>
-      <c r="ANO41"/>
     </row>
-    <row r="42" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="34" t="s">
         <v>64</v>
       </c>
@@ -45366,44 +44849,44 @@
       <c r="F42" s="35">
         <v>0</v>
       </c>
-      <c r="G42" s="97">
-        <v>0</v>
-      </c>
-      <c r="H42" s="97">
-        <v>0</v>
-      </c>
-      <c r="I42" s="97">
-        <v>0</v>
-      </c>
-      <c r="J42" s="97">
-        <v>0</v>
-      </c>
-      <c r="K42" s="36">
+      <c r="G42" s="36">
         <v>11</v>
       </c>
-      <c r="L42" s="38">
-        <v>0</v>
-      </c>
-      <c r="M42" s="39">
+      <c r="H42" s="38">
+        <v>0</v>
+      </c>
+      <c r="I42" s="39">
         <v>70</v>
       </c>
-      <c r="N42" s="40">
-        <v>0</v>
-      </c>
-      <c r="O42" s="35"/>
-      <c r="Q42" s="38">
-        <v>0</v>
-      </c>
-      <c r="R42" s="35">
-        <v>0</v>
-      </c>
-      <c r="S42" s="38">
-        <v>0</v>
-      </c>
-      <c r="T42" s="41">
-        <v>0</v>
-      </c>
-      <c r="U42" s="42">
+      <c r="J42" s="40">
+        <v>0</v>
+      </c>
+      <c r="K42" s="35"/>
+      <c r="M42" s="38">
+        <v>0</v>
+      </c>
+      <c r="N42" s="35">
+        <v>0</v>
+      </c>
+      <c r="O42" s="38">
+        <v>0</v>
+      </c>
+      <c r="P42" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="42">
+        <v>0</v>
+      </c>
+      <c r="R42" s="36">
+        <v>0</v>
+      </c>
+      <c r="S42" s="36">
+        <v>0</v>
+      </c>
+      <c r="T42" s="36">
+        <v>0</v>
+      </c>
+      <c r="U42" s="36">
         <v>0</v>
       </c>
       <c r="V42" s="36">
@@ -45460,21 +44943,13 @@
       <c r="AM42" s="36">
         <v>0</v>
       </c>
-      <c r="AN42" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP42" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR42" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN42" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO42"/>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42"/>
       <c r="AS42"/>
       <c r="AT42"/>
       <c r="AU42"/>
@@ -46482,12 +45957,8 @@
       <c r="ANI42"/>
       <c r="ANJ42"/>
       <c r="ANK42"/>
-      <c r="ANL42"/>
-      <c r="ANM42"/>
-      <c r="ANN42"/>
-      <c r="ANO42"/>
     </row>
-    <row r="43" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
         <v>65</v>
       </c>
@@ -46506,121 +45977,113 @@
       <c r="F43" s="35">
         <v>0</v>
       </c>
-      <c r="G43" s="97">
-        <v>0</v>
-      </c>
-      <c r="H43" s="97">
-        <v>0</v>
-      </c>
-      <c r="I43" s="97">
-        <v>0</v>
-      </c>
-      <c r="J43" s="97">
-        <v>0</v>
-      </c>
-      <c r="K43" s="36">
+      <c r="G43" s="36">
         <v>1390</v>
       </c>
-      <c r="L43" s="38">
+      <c r="H43" s="38">
         <v>112</v>
       </c>
-      <c r="M43" s="39">
+      <c r="I43" s="39">
         <v>49</v>
       </c>
-      <c r="N43" s="40">
+      <c r="J43" s="40">
         <v>10</v>
       </c>
-      <c r="O43" s="35">
+      <c r="K43" s="35">
         <v>0.52</v>
       </c>
-      <c r="P43" s="36">
+      <c r="L43" s="36">
         <v>0.95</v>
       </c>
-      <c r="Q43" s="38">
-        <f>(O43+P43)/2</f>
+      <c r="M43" s="38">
+        <f>(K43+L43)/2</f>
         <v>0.73499999999999999</v>
       </c>
-      <c r="R43" s="35">
+      <c r="N43" s="35">
         <v>87</v>
       </c>
-      <c r="S43" s="38">
+      <c r="O43" s="38">
         <v>2000</v>
       </c>
-      <c r="T43" s="41">
+      <c r="P43" s="41">
         <v>73765.766632248604</v>
       </c>
-      <c r="U43" s="42">
+      <c r="Q43" s="42">
         <v>-554097.261680839</v>
       </c>
+      <c r="R43" s="36">
+        <v>2800000</v>
+      </c>
+      <c r="S43" s="36">
+        <v>2710000</v>
+      </c>
+      <c r="T43" s="36">
+        <v>2920000</v>
+      </c>
+      <c r="U43" s="36">
+        <v>3010000</v>
+      </c>
       <c r="V43" s="36">
-        <v>2800000</v>
+        <v>3100000</v>
       </c>
       <c r="W43" s="36">
-        <v>2710000</v>
+        <v>3019990</v>
       </c>
       <c r="X43" s="36">
-        <v>2920000</v>
+        <v>3099990</v>
       </c>
       <c r="Y43" s="36">
-        <v>3010000</v>
+        <v>3099990</v>
       </c>
       <c r="Z43" s="36">
-        <v>3100000</v>
+        <v>2909990</v>
       </c>
       <c r="AA43" s="36">
-        <v>3019990</v>
+        <v>2949980</v>
       </c>
       <c r="AB43" s="36">
-        <v>3099990</v>
+        <v>3149970</v>
       </c>
       <c r="AC43" s="36">
-        <v>3099990</v>
+        <v>3269960</v>
       </c>
       <c r="AD43" s="36">
-        <v>2909990</v>
+        <v>3469940</v>
       </c>
       <c r="AE43" s="36">
-        <v>2949980</v>
+        <v>3769880</v>
       </c>
       <c r="AF43" s="36">
-        <v>3149970</v>
+        <v>3839810</v>
       </c>
       <c r="AG43" s="36">
-        <v>3269960</v>
+        <v>3859630</v>
       </c>
       <c r="AH43" s="36">
-        <v>3469940</v>
+        <v>4139410</v>
       </c>
       <c r="AI43" s="36">
-        <v>3769880</v>
+        <v>4699350</v>
       </c>
       <c r="AJ43" s="36">
-        <v>3839810</v>
+        <v>5169250</v>
       </c>
       <c r="AK43" s="36">
-        <v>3859630</v>
+        <v>5489190</v>
       </c>
       <c r="AL43" s="36">
-        <v>4139410</v>
+        <v>4868700</v>
       </c>
       <c r="AM43" s="36">
-        <v>4699350</v>
-      </c>
-      <c r="AN43" s="36">
-        <v>5169250</v>
-      </c>
-      <c r="AO43" s="36">
-        <v>5489190</v>
-      </c>
-      <c r="AP43" s="36">
-        <v>4868700</v>
-      </c>
-      <c r="AQ43" s="36">
         <v>4948180</v>
       </c>
-      <c r="AR43" s="38">
+      <c r="AN43" s="38">
         <v>4817650</v>
       </c>
+      <c r="AO43"/>
+      <c r="AP43"/>
+      <c r="AQ43"/>
+      <c r="AR43"/>
       <c r="AS43"/>
       <c r="AT43"/>
       <c r="AU43"/>
@@ -47628,12 +47091,8 @@
       <c r="ANI43"/>
       <c r="ANJ43"/>
       <c r="ANK43"/>
-      <c r="ANL43"/>
-      <c r="ANM43"/>
-      <c r="ANN43"/>
-      <c r="ANO43"/>
     </row>
-    <row r="44" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
         <v>66</v>
       </c>
@@ -47652,44 +47111,44 @@
       <c r="F44" s="35">
         <v>125</v>
       </c>
-      <c r="G44" s="97">
-        <v>0</v>
-      </c>
-      <c r="H44" s="97">
-        <v>0</v>
-      </c>
-      <c r="I44" s="97">
-        <v>0</v>
-      </c>
-      <c r="J44" s="97">
-        <v>0</v>
-      </c>
-      <c r="K44" s="36">
+      <c r="G44" s="36">
         <v>970</v>
       </c>
-      <c r="L44" s="38">
-        <v>0</v>
-      </c>
-      <c r="M44" s="39">
+      <c r="H44" s="38">
+        <v>0</v>
+      </c>
+      <c r="I44" s="39">
         <v>80.5</v>
       </c>
-      <c r="N44" s="40">
-        <v>0</v>
-      </c>
-      <c r="O44" s="35"/>
-      <c r="Q44" s="38">
-        <v>0</v>
-      </c>
-      <c r="R44" s="35">
-        <v>0</v>
-      </c>
-      <c r="S44" s="38">
-        <v>0</v>
-      </c>
-      <c r="T44" s="41">
-        <v>0</v>
-      </c>
-      <c r="U44" s="42">
+      <c r="J44" s="40">
+        <v>0</v>
+      </c>
+      <c r="K44" s="35"/>
+      <c r="M44" s="38">
+        <v>0</v>
+      </c>
+      <c r="N44" s="35">
+        <v>0</v>
+      </c>
+      <c r="O44" s="38">
+        <v>0</v>
+      </c>
+      <c r="P44" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="42">
+        <v>0</v>
+      </c>
+      <c r="R44" s="36">
+        <v>0</v>
+      </c>
+      <c r="S44" s="36">
+        <v>0</v>
+      </c>
+      <c r="T44" s="36">
+        <v>0</v>
+      </c>
+      <c r="U44" s="36">
         <v>0</v>
       </c>
       <c r="V44" s="36">
@@ -47746,21 +47205,13 @@
       <c r="AM44" s="36">
         <v>0</v>
       </c>
-      <c r="AN44" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO44" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP44" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ44" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR44" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN44" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO44"/>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+      <c r="AR44"/>
       <c r="AS44"/>
       <c r="AT44"/>
       <c r="AU44"/>
@@ -48768,12 +48219,8 @@
       <c r="ANI44"/>
       <c r="ANJ44"/>
       <c r="ANK44"/>
-      <c r="ANL44"/>
-      <c r="ANM44"/>
-      <c r="ANN44"/>
-      <c r="ANO44"/>
     </row>
-    <row r="45" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="47" t="s">
         <v>67</v>
       </c>
@@ -48792,44 +48239,44 @@
       <c r="F45" s="35">
         <v>0</v>
       </c>
-      <c r="G45" s="97">
-        <v>0</v>
-      </c>
-      <c r="H45" s="97">
-        <v>0</v>
-      </c>
-      <c r="I45" s="97">
-        <v>0</v>
-      </c>
-      <c r="J45" s="97">
-        <v>0</v>
-      </c>
-      <c r="K45" s="36">
+      <c r="G45" s="36">
         <v>190</v>
       </c>
-      <c r="L45" s="38">
+      <c r="H45" s="38">
         <v>15</v>
       </c>
-      <c r="M45" s="39">
+      <c r="I45" s="39">
         <v>95.4</v>
       </c>
-      <c r="N45" s="40">
-        <v>0</v>
-      </c>
-      <c r="O45" s="35"/>
-      <c r="Q45" s="38">
-        <v>0</v>
-      </c>
-      <c r="R45" s="35">
-        <v>0</v>
-      </c>
-      <c r="S45" s="38">
-        <v>0</v>
-      </c>
-      <c r="T45" s="41">
-        <v>0</v>
-      </c>
-      <c r="U45" s="42">
+      <c r="J45" s="40">
+        <v>0</v>
+      </c>
+      <c r="K45" s="35"/>
+      <c r="M45" s="38">
+        <v>0</v>
+      </c>
+      <c r="N45" s="35">
+        <v>0</v>
+      </c>
+      <c r="O45" s="38">
+        <v>0</v>
+      </c>
+      <c r="P45" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="42">
+        <v>0</v>
+      </c>
+      <c r="R45" s="36">
+        <v>0</v>
+      </c>
+      <c r="S45" s="36">
+        <v>0</v>
+      </c>
+      <c r="T45" s="36">
+        <v>0</v>
+      </c>
+      <c r="U45" s="36">
         <v>0</v>
       </c>
       <c r="V45" s="36">
@@ -48886,21 +48333,13 @@
       <c r="AM45" s="36">
         <v>0</v>
       </c>
-      <c r="AN45" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO45" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP45" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ45" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR45" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN45" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO45"/>
+      <c r="AP45"/>
+      <c r="AQ45"/>
+      <c r="AR45"/>
       <c r="AS45"/>
       <c r="AT45"/>
       <c r="AU45"/>
@@ -49908,12 +49347,8 @@
       <c r="ANI45"/>
       <c r="ANJ45"/>
       <c r="ANK45"/>
-      <c r="ANL45"/>
-      <c r="ANM45"/>
-      <c r="ANN45"/>
-      <c r="ANO45"/>
     </row>
-    <row r="46" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
         <v>68</v>
       </c>
@@ -49932,44 +49367,44 @@
       <c r="F46" s="35">
         <v>0</v>
       </c>
-      <c r="G46" s="97">
-        <v>0</v>
-      </c>
-      <c r="H46" s="97">
-        <v>0</v>
-      </c>
-      <c r="I46" s="97">
-        <v>0</v>
-      </c>
-      <c r="J46" s="97">
-        <v>0</v>
-      </c>
-      <c r="K46" s="36">
-        <v>0</v>
-      </c>
-      <c r="L46" s="38">
-        <v>0</v>
-      </c>
-      <c r="M46" s="39">
+      <c r="G46" s="36">
+        <v>0</v>
+      </c>
+      <c r="H46" s="38">
+        <v>0</v>
+      </c>
+      <c r="I46" s="39">
         <v>1</v>
       </c>
-      <c r="N46" s="40">
-        <v>0</v>
-      </c>
-      <c r="O46" s="35"/>
-      <c r="Q46" s="38">
-        <v>0</v>
-      </c>
-      <c r="R46" s="35">
-        <v>0</v>
-      </c>
-      <c r="S46" s="38">
-        <v>0</v>
-      </c>
-      <c r="T46" s="41">
-        <v>0</v>
-      </c>
-      <c r="U46" s="42">
+      <c r="J46" s="40">
+        <v>0</v>
+      </c>
+      <c r="K46" s="35"/>
+      <c r="M46" s="38">
+        <v>0</v>
+      </c>
+      <c r="N46" s="35">
+        <v>0</v>
+      </c>
+      <c r="O46" s="38">
+        <v>0</v>
+      </c>
+      <c r="P46" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="42">
+        <v>0</v>
+      </c>
+      <c r="R46" s="36">
+        <v>0</v>
+      </c>
+      <c r="S46" s="36">
+        <v>0</v>
+      </c>
+      <c r="T46" s="36">
+        <v>0</v>
+      </c>
+      <c r="U46" s="36">
         <v>0</v>
       </c>
       <c r="V46" s="36">
@@ -50026,21 +49461,13 @@
       <c r="AM46" s="36">
         <v>0</v>
       </c>
-      <c r="AN46" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP46" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR46" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN46" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46"/>
       <c r="AS46"/>
       <c r="AT46"/>
       <c r="AU46"/>
@@ -51048,12 +50475,8 @@
       <c r="ANI46"/>
       <c r="ANJ46"/>
       <c r="ANK46"/>
-      <c r="ANL46"/>
-      <c r="ANM46"/>
-      <c r="ANN46"/>
-      <c r="ANO46"/>
     </row>
-    <row r="47" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="47" t="s">
         <v>69</v>
       </c>
@@ -51072,44 +50495,44 @@
       <c r="F47" s="35">
         <v>0</v>
       </c>
-      <c r="G47" s="97">
-        <v>0</v>
-      </c>
-      <c r="H47" s="97">
-        <v>0</v>
-      </c>
-      <c r="I47" s="97">
-        <v>0</v>
-      </c>
-      <c r="J47" s="97">
-        <v>0</v>
-      </c>
-      <c r="K47" s="36">
-        <v>0</v>
-      </c>
-      <c r="L47" s="38">
-        <v>0</v>
-      </c>
-      <c r="M47" s="39">
+      <c r="G47" s="36">
+        <v>0</v>
+      </c>
+      <c r="H47" s="38">
+        <v>0</v>
+      </c>
+      <c r="I47" s="39">
         <v>16.600000000000001</v>
       </c>
-      <c r="N47" s="40">
-        <v>0</v>
-      </c>
-      <c r="O47" s="35"/>
-      <c r="Q47" s="38">
-        <v>0</v>
-      </c>
-      <c r="R47" s="35">
-        <v>0</v>
-      </c>
-      <c r="S47" s="38">
-        <v>0</v>
-      </c>
-      <c r="T47" s="41">
-        <v>0</v>
-      </c>
-      <c r="U47" s="42">
+      <c r="J47" s="40">
+        <v>0</v>
+      </c>
+      <c r="K47" s="35"/>
+      <c r="M47" s="38">
+        <v>0</v>
+      </c>
+      <c r="N47" s="35">
+        <v>0</v>
+      </c>
+      <c r="O47" s="38">
+        <v>0</v>
+      </c>
+      <c r="P47" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="42">
+        <v>0</v>
+      </c>
+      <c r="R47" s="36">
+        <v>0</v>
+      </c>
+      <c r="S47" s="36">
+        <v>0</v>
+      </c>
+      <c r="T47" s="36">
+        <v>0</v>
+      </c>
+      <c r="U47" s="36">
         <v>0</v>
       </c>
       <c r="V47" s="36">
@@ -51166,21 +50589,13 @@
       <c r="AM47" s="36">
         <v>0</v>
       </c>
-      <c r="AN47" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP47" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ47" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR47" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN47" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO47"/>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47"/>
       <c r="AS47"/>
       <c r="AT47"/>
       <c r="AU47"/>
@@ -52188,12 +51603,8 @@
       <c r="ANI47"/>
       <c r="ANJ47"/>
       <c r="ANK47"/>
-      <c r="ANL47"/>
-      <c r="ANM47"/>
-      <c r="ANN47"/>
-      <c r="ANO47"/>
     </row>
-    <row r="48" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="47" t="s">
         <v>70</v>
       </c>
@@ -52212,44 +51623,44 @@
       <c r="F48" s="35">
         <v>0</v>
       </c>
-      <c r="G48" s="97">
-        <v>0</v>
-      </c>
-      <c r="H48" s="97">
-        <v>0</v>
-      </c>
-      <c r="I48" s="97">
-        <v>0</v>
-      </c>
-      <c r="J48" s="97">
-        <v>0</v>
-      </c>
-      <c r="K48" s="36">
+      <c r="G48" s="36">
         <v>160000</v>
       </c>
-      <c r="L48" s="38">
-        <v>0</v>
-      </c>
-      <c r="M48" s="39">
+      <c r="H48" s="38">
+        <v>0</v>
+      </c>
+      <c r="I48" s="39">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="N48" s="40">
-        <v>0</v>
-      </c>
-      <c r="O48" s="35"/>
-      <c r="Q48" s="38">
-        <v>0</v>
-      </c>
-      <c r="R48" s="35">
-        <v>0</v>
-      </c>
-      <c r="S48" s="38">
-        <v>0</v>
-      </c>
-      <c r="T48" s="41">
-        <v>0</v>
-      </c>
-      <c r="U48" s="42">
+      <c r="J48" s="40">
+        <v>0</v>
+      </c>
+      <c r="K48" s="35"/>
+      <c r="M48" s="38">
+        <v>0</v>
+      </c>
+      <c r="N48" s="35">
+        <v>0</v>
+      </c>
+      <c r="O48" s="38">
+        <v>0</v>
+      </c>
+      <c r="P48" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="42">
+        <v>0</v>
+      </c>
+      <c r="R48" s="36">
+        <v>0</v>
+      </c>
+      <c r="S48" s="36">
+        <v>0</v>
+      </c>
+      <c r="T48" s="36">
+        <v>0</v>
+      </c>
+      <c r="U48" s="36">
         <v>0</v>
       </c>
       <c r="V48" s="36">
@@ -52306,21 +51717,13 @@
       <c r="AM48" s="36">
         <v>0</v>
       </c>
-      <c r="AN48" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO48" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP48" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ48" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR48" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN48" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO48"/>
+      <c r="AP48"/>
+      <c r="AQ48"/>
+      <c r="AR48"/>
       <c r="AS48"/>
       <c r="AT48"/>
       <c r="AU48"/>
@@ -53328,12 +52731,8 @@
       <c r="ANI48"/>
       <c r="ANJ48"/>
       <c r="ANK48"/>
-      <c r="ANL48"/>
-      <c r="ANM48"/>
-      <c r="ANN48"/>
-      <c r="ANO48"/>
     </row>
-    <row r="49" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
         <v>71</v>
       </c>
@@ -53352,44 +52751,44 @@
       <c r="F49" s="35">
         <v>0</v>
       </c>
-      <c r="G49" s="97">
-        <v>0</v>
-      </c>
-      <c r="H49" s="97">
-        <v>0</v>
-      </c>
-      <c r="I49" s="97">
-        <v>0</v>
-      </c>
-      <c r="J49" s="97">
-        <v>0</v>
-      </c>
-      <c r="K49" s="36">
-        <v>0</v>
-      </c>
-      <c r="L49" s="38">
-        <v>0</v>
-      </c>
-      <c r="M49" s="39">
+      <c r="G49" s="36">
+        <v>0</v>
+      </c>
+      <c r="H49" s="38">
+        <v>0</v>
+      </c>
+      <c r="I49" s="39">
         <v>0.1</v>
       </c>
-      <c r="N49" s="40">
-        <v>0</v>
-      </c>
-      <c r="O49" s="35"/>
-      <c r="Q49" s="38">
-        <v>0</v>
-      </c>
-      <c r="R49" s="35">
-        <v>0</v>
-      </c>
-      <c r="S49" s="38">
-        <v>0</v>
-      </c>
-      <c r="T49" s="41">
-        <v>0</v>
-      </c>
-      <c r="U49" s="42">
+      <c r="J49" s="40">
+        <v>0</v>
+      </c>
+      <c r="K49" s="35"/>
+      <c r="M49" s="38">
+        <v>0</v>
+      </c>
+      <c r="N49" s="35">
+        <v>0</v>
+      </c>
+      <c r="O49" s="38">
+        <v>0</v>
+      </c>
+      <c r="P49" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="42">
+        <v>0</v>
+      </c>
+      <c r="R49" s="36">
+        <v>0</v>
+      </c>
+      <c r="S49" s="36">
+        <v>0</v>
+      </c>
+      <c r="T49" s="36">
+        <v>0</v>
+      </c>
+      <c r="U49" s="36">
         <v>0</v>
       </c>
       <c r="V49" s="36">
@@ -53446,21 +52845,13 @@
       <c r="AM49" s="36">
         <v>0</v>
       </c>
-      <c r="AN49" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO49" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP49" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ49" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR49" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN49" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO49"/>
+      <c r="AP49"/>
+      <c r="AQ49"/>
+      <c r="AR49"/>
       <c r="AS49"/>
       <c r="AT49"/>
       <c r="AU49"/>
@@ -54468,12 +53859,8 @@
       <c r="ANI49"/>
       <c r="ANJ49"/>
       <c r="ANK49"/>
-      <c r="ANL49"/>
-      <c r="ANM49"/>
-      <c r="ANN49"/>
-      <c r="ANO49"/>
     </row>
-    <row r="50" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
         <v>72</v>
       </c>
@@ -54492,44 +53879,44 @@
       <c r="F50" s="35">
         <v>0</v>
       </c>
-      <c r="G50" s="97">
-        <v>0</v>
-      </c>
-      <c r="H50" s="97">
-        <v>0</v>
-      </c>
-      <c r="I50" s="97">
-        <v>0</v>
-      </c>
-      <c r="J50" s="97">
-        <v>0</v>
-      </c>
-      <c r="K50" s="36">
-        <v>0</v>
-      </c>
-      <c r="L50" s="38">
-        <v>0</v>
-      </c>
-      <c r="M50" s="39">
+      <c r="G50" s="36">
+        <v>0</v>
+      </c>
+      <c r="H50" s="38">
+        <v>0</v>
+      </c>
+      <c r="I50" s="39">
         <v>2000</v>
       </c>
-      <c r="N50" s="40">
-        <v>0</v>
-      </c>
-      <c r="O50" s="35"/>
-      <c r="Q50" s="38">
-        <v>0</v>
-      </c>
-      <c r="R50" s="35">
-        <v>0</v>
-      </c>
-      <c r="S50" s="38">
-        <v>0</v>
-      </c>
-      <c r="T50" s="41">
-        <v>0</v>
-      </c>
-      <c r="U50" s="42">
+      <c r="J50" s="40">
+        <v>0</v>
+      </c>
+      <c r="K50" s="35"/>
+      <c r="M50" s="38">
+        <v>0</v>
+      </c>
+      <c r="N50" s="35">
+        <v>0</v>
+      </c>
+      <c r="O50" s="38">
+        <v>0</v>
+      </c>
+      <c r="P50" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="42">
+        <v>0</v>
+      </c>
+      <c r="R50" s="36">
+        <v>0</v>
+      </c>
+      <c r="S50" s="36">
+        <v>0</v>
+      </c>
+      <c r="T50" s="36">
+        <v>0</v>
+      </c>
+      <c r="U50" s="36">
         <v>0</v>
       </c>
       <c r="V50" s="36">
@@ -54586,21 +53973,13 @@
       <c r="AM50" s="36">
         <v>0</v>
       </c>
-      <c r="AN50" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO50" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP50" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ50" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR50" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN50" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO50"/>
+      <c r="AP50"/>
+      <c r="AQ50"/>
+      <c r="AR50"/>
       <c r="AS50"/>
       <c r="AT50"/>
       <c r="AU50"/>
@@ -55608,12 +54987,8 @@
       <c r="ANI50"/>
       <c r="ANJ50"/>
       <c r="ANK50"/>
-      <c r="ANL50"/>
-      <c r="ANM50"/>
-      <c r="ANN50"/>
-      <c r="ANO50"/>
     </row>
-    <row r="51" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="47" t="s">
         <v>73</v>
       </c>
@@ -55632,121 +55007,113 @@
       <c r="F51" s="35">
         <v>0</v>
       </c>
-      <c r="G51" s="97">
-        <v>0</v>
-      </c>
-      <c r="H51" s="97">
-        <v>0</v>
-      </c>
-      <c r="I51" s="97">
-        <v>0</v>
-      </c>
-      <c r="J51" s="97">
-        <v>0</v>
-      </c>
-      <c r="K51" s="36">
-        <v>0</v>
-      </c>
-      <c r="L51" s="38">
-        <v>0</v>
-      </c>
-      <c r="M51" s="39">
+      <c r="G51" s="36">
+        <v>0</v>
+      </c>
+      <c r="H51" s="38">
+        <v>0</v>
+      </c>
+      <c r="I51" s="39">
         <v>1580</v>
       </c>
-      <c r="N51" s="40">
-        <v>0</v>
-      </c>
-      <c r="O51" s="35">
+      <c r="J51" s="40">
+        <v>0</v>
+      </c>
+      <c r="K51" s="35">
         <v>0.3</v>
       </c>
-      <c r="P51" s="36">
+      <c r="L51" s="36">
         <v>0.97</v>
       </c>
-      <c r="Q51" s="38">
-        <f>(O51+P51)/2</f>
+      <c r="M51" s="38">
+        <f>(K51+L51)/2</f>
         <v>0.63500000000000001</v>
       </c>
-      <c r="R51" s="35">
-        <v>0.53</v>
-      </c>
-      <c r="S51" s="38">
+      <c r="N51" s="35">
+        <v>0.64</v>
+      </c>
+      <c r="O51" s="38">
         <v>1.3080000000000001</v>
       </c>
-      <c r="T51" s="41">
+      <c r="P51" s="41">
         <v>257.68585968079202</v>
       </c>
-      <c r="U51" s="42">
+      <c r="Q51" s="42">
         <v>4731.2741255115297</v>
       </c>
+      <c r="R51" s="36">
+        <v>13900</v>
+      </c>
+      <c r="S51" s="36">
+        <v>14600</v>
+      </c>
+      <c r="T51" s="36">
+        <v>15200</v>
+      </c>
+      <c r="U51" s="36">
+        <v>16390</v>
+      </c>
       <c r="V51" s="36">
-        <v>13900</v>
+        <v>16390</v>
       </c>
       <c r="W51" s="36">
-        <v>14600</v>
+        <v>17680</v>
       </c>
       <c r="X51" s="36">
-        <v>15200</v>
+        <v>17690</v>
       </c>
       <c r="Y51" s="36">
-        <v>16390</v>
+        <v>18680</v>
       </c>
       <c r="Z51" s="36">
-        <v>16390</v>
+        <v>19970</v>
       </c>
       <c r="AA51" s="36">
-        <v>17680</v>
+        <v>18750</v>
       </c>
       <c r="AB51" s="36">
-        <v>17690</v>
+        <v>19630</v>
       </c>
       <c r="AC51" s="36">
-        <v>18680</v>
+        <v>19220</v>
       </c>
       <c r="AD51" s="36">
-        <v>19970</v>
+        <v>20060</v>
       </c>
       <c r="AE51" s="36">
-        <v>18750</v>
+        <v>20530</v>
       </c>
       <c r="AF51" s="36">
-        <v>19630</v>
+        <v>20870</v>
       </c>
       <c r="AG51" s="36">
-        <v>19220</v>
+        <v>20970</v>
       </c>
       <c r="AH51" s="36">
-        <v>20060</v>
+        <v>21780</v>
       </c>
       <c r="AI51" s="36">
-        <v>20530</v>
+        <v>21860</v>
       </c>
       <c r="AJ51" s="36">
-        <v>20870</v>
+        <v>23830</v>
       </c>
       <c r="AK51" s="36">
-        <v>20970</v>
+        <v>24190</v>
       </c>
       <c r="AL51" s="36">
-        <v>21780</v>
+        <v>23910</v>
       </c>
       <c r="AM51" s="36">
-        <v>21860</v>
-      </c>
-      <c r="AN51" s="36">
-        <v>23830</v>
-      </c>
-      <c r="AO51" s="36">
-        <v>24190</v>
-      </c>
-      <c r="AP51" s="36">
-        <v>23910</v>
-      </c>
-      <c r="AQ51" s="36">
         <v>21060</v>
       </c>
-      <c r="AR51" s="38">
+      <c r="AN51" s="38">
         <v>21790</v>
       </c>
+      <c r="AO51"/>
+      <c r="AP51"/>
+      <c r="AQ51"/>
+      <c r="AR51"/>
       <c r="AS51"/>
       <c r="AT51"/>
       <c r="AU51"/>
@@ -56754,12 +56121,8 @@
       <c r="ANI51"/>
       <c r="ANJ51"/>
       <c r="ANK51"/>
-      <c r="ANL51"/>
-      <c r="ANM51"/>
-      <c r="ANN51"/>
-      <c r="ANO51"/>
     </row>
-    <row r="52" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
         <v>74</v>
       </c>
@@ -56780,44 +56143,44 @@
       <c r="F52" s="35">
         <v>0</v>
       </c>
-      <c r="G52" s="97">
-        <v>0</v>
-      </c>
-      <c r="H52" s="97">
-        <v>0</v>
-      </c>
-      <c r="I52" s="97">
-        <v>0</v>
-      </c>
-      <c r="J52" s="97">
-        <v>0</v>
-      </c>
-      <c r="K52" s="36">
-        <v>0</v>
-      </c>
-      <c r="L52" s="38">
-        <v>0</v>
-      </c>
-      <c r="M52" s="39">
+      <c r="G52" s="36">
+        <v>0</v>
+      </c>
+      <c r="H52" s="38">
+        <v>0</v>
+      </c>
+      <c r="I52" s="39">
         <v>0.45</v>
       </c>
-      <c r="N52" s="40">
-        <v>0</v>
-      </c>
-      <c r="O52" s="35"/>
-      <c r="Q52" s="38">
-        <v>0</v>
-      </c>
-      <c r="R52" s="35">
-        <v>0</v>
-      </c>
-      <c r="S52" s="38">
-        <v>0</v>
-      </c>
-      <c r="T52" s="41">
-        <v>0</v>
-      </c>
-      <c r="U52" s="42">
+      <c r="J52" s="40">
+        <v>0</v>
+      </c>
+      <c r="K52" s="35"/>
+      <c r="M52" s="38">
+        <v>0</v>
+      </c>
+      <c r="N52" s="35">
+        <v>0</v>
+      </c>
+      <c r="O52" s="38">
+        <v>0</v>
+      </c>
+      <c r="P52" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="42">
+        <v>0</v>
+      </c>
+      <c r="R52" s="36">
+        <v>0</v>
+      </c>
+      <c r="S52" s="36">
+        <v>0</v>
+      </c>
+      <c r="T52" s="36">
+        <v>0</v>
+      </c>
+      <c r="U52" s="36">
         <v>0</v>
       </c>
       <c r="V52" s="36">
@@ -56874,21 +56237,13 @@
       <c r="AM52" s="36">
         <v>0</v>
       </c>
-      <c r="AN52" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO52" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP52" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR52" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN52" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO52"/>
+      <c r="AP52"/>
+      <c r="AQ52"/>
+      <c r="AR52"/>
       <c r="AS52"/>
       <c r="AT52"/>
       <c r="AU52"/>
@@ -57896,12 +57251,8 @@
       <c r="ANI52"/>
       <c r="ANJ52"/>
       <c r="ANK52"/>
-      <c r="ANL52"/>
-      <c r="ANM52"/>
-      <c r="ANN52"/>
-      <c r="ANO52"/>
     </row>
-    <row r="53" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
         <v>75</v>
       </c>
@@ -57920,115 +57271,107 @@
       <c r="F53" s="35">
         <v>0</v>
       </c>
-      <c r="G53" s="97">
-        <v>0</v>
-      </c>
-      <c r="H53" s="97">
-        <v>0</v>
-      </c>
-      <c r="I53" s="97">
-        <v>0</v>
-      </c>
-      <c r="J53" s="97">
-        <v>0</v>
-      </c>
-      <c r="K53" s="36">
+      <c r="G53" s="36">
         <v>64</v>
       </c>
-      <c r="L53" s="38">
-        <v>0</v>
-      </c>
-      <c r="M53" s="39">
+      <c r="H53" s="38">
+        <v>0</v>
+      </c>
+      <c r="I53" s="39">
         <v>250</v>
       </c>
-      <c r="N53" s="40">
-        <v>0</v>
-      </c>
-      <c r="O53" s="35"/>
-      <c r="Q53" s="38">
+      <c r="J53" s="40">
+        <v>0</v>
+      </c>
+      <c r="K53" s="35"/>
+      <c r="M53" s="38">
         <v>0.75</v>
       </c>
-      <c r="R53" s="35">
+      <c r="N53" s="35">
         <v>4.8</v>
       </c>
-      <c r="S53" s="38">
+      <c r="O53" s="38">
         <v>76.2</v>
       </c>
-      <c r="T53" s="41">
+      <c r="P53" s="41">
         <v>2274.6209310543099</v>
       </c>
-      <c r="U53" s="42">
+      <c r="Q53" s="42">
         <v>111474.49153260099</v>
       </c>
+      <c r="R53" s="36">
+        <v>184000</v>
+      </c>
+      <c r="S53" s="36">
+        <v>188970</v>
+      </c>
+      <c r="T53" s="36">
+        <v>195960</v>
+      </c>
+      <c r="U53" s="36">
+        <v>210950</v>
+      </c>
       <c r="V53" s="36">
-        <v>184000</v>
+        <v>205900</v>
       </c>
       <c r="W53" s="36">
-        <v>188970</v>
+        <v>197850</v>
       </c>
       <c r="X53" s="36">
-        <v>195960</v>
+        <v>237860</v>
       </c>
       <c r="Y53" s="36">
-        <v>210950</v>
+        <v>221830</v>
       </c>
       <c r="Z53" s="36">
-        <v>205900</v>
+        <v>248720</v>
       </c>
       <c r="AA53" s="36">
-        <v>197850</v>
+        <v>206510</v>
       </c>
       <c r="AB53" s="36">
-        <v>237860</v>
+        <v>263350</v>
       </c>
       <c r="AC53" s="36">
-        <v>221830</v>
+        <v>289200</v>
       </c>
       <c r="AD53" s="36">
-        <v>248720</v>
+        <v>300610</v>
       </c>
       <c r="AE53" s="36">
-        <v>206510</v>
+        <v>317350</v>
       </c>
       <c r="AF53" s="36">
-        <v>263350</v>
+        <v>294830</v>
       </c>
       <c r="AG53" s="36">
-        <v>289200</v>
+        <v>251880</v>
       </c>
       <c r="AH53" s="36">
-        <v>300610</v>
+        <v>252040</v>
       </c>
       <c r="AI53" s="36">
-        <v>317350</v>
+        <v>229800</v>
       </c>
       <c r="AJ53" s="36">
-        <v>294830</v>
+        <v>223630</v>
       </c>
       <c r="AK53" s="36">
-        <v>251880</v>
+        <v>276260</v>
       </c>
       <c r="AL53" s="36">
-        <v>252040</v>
+        <v>257510</v>
       </c>
       <c r="AM53" s="36">
-        <v>229800</v>
-      </c>
-      <c r="AN53" s="36">
-        <v>223630</v>
-      </c>
-      <c r="AO53" s="36">
-        <v>276260</v>
-      </c>
-      <c r="AP53" s="36">
-        <v>257510</v>
-      </c>
-      <c r="AQ53" s="36">
         <v>249220</v>
       </c>
-      <c r="AR53" s="38">
+      <c r="AN53" s="38">
         <v>228660</v>
       </c>
+      <c r="AO53"/>
+      <c r="AP53"/>
+      <c r="AQ53"/>
+      <c r="AR53"/>
       <c r="AS53"/>
       <c r="AT53"/>
       <c r="AU53"/>
@@ -59036,12 +58379,8 @@
       <c r="ANI53"/>
       <c r="ANJ53"/>
       <c r="ANK53"/>
-      <c r="ANL53"/>
-      <c r="ANM53"/>
-      <c r="ANN53"/>
-      <c r="ANO53"/>
     </row>
-    <row r="54" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="47" t="s">
         <v>76</v>
       </c>
@@ -59060,44 +58399,44 @@
       <c r="F54" s="35">
         <v>0</v>
       </c>
-      <c r="G54" s="97">
-        <v>0</v>
-      </c>
-      <c r="H54" s="97">
-        <v>0</v>
-      </c>
-      <c r="I54" s="97">
-        <v>0</v>
-      </c>
-      <c r="J54" s="97">
-        <v>0</v>
-      </c>
-      <c r="K54" s="36">
-        <v>0</v>
-      </c>
-      <c r="L54" s="38">
-        <v>0</v>
-      </c>
-      <c r="M54" s="39">
-        <v>0</v>
-      </c>
-      <c r="N54" s="40">
-        <v>0</v>
-      </c>
-      <c r="O54" s="35"/>
-      <c r="Q54" s="38">
-        <v>0</v>
-      </c>
-      <c r="R54" s="35">
-        <v>0</v>
-      </c>
-      <c r="S54" s="38">
-        <v>0</v>
-      </c>
-      <c r="T54" s="41">
-        <v>0</v>
-      </c>
-      <c r="U54" s="42">
+      <c r="G54" s="36">
+        <v>0</v>
+      </c>
+      <c r="H54" s="38">
+        <v>0</v>
+      </c>
+      <c r="I54" s="39">
+        <v>0</v>
+      </c>
+      <c r="J54" s="40">
+        <v>0</v>
+      </c>
+      <c r="K54" s="35"/>
+      <c r="M54" s="38">
+        <v>0</v>
+      </c>
+      <c r="N54" s="35">
+        <v>0</v>
+      </c>
+      <c r="O54" s="38">
+        <v>0</v>
+      </c>
+      <c r="P54" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="42">
+        <v>0</v>
+      </c>
+      <c r="R54" s="36">
+        <v>0</v>
+      </c>
+      <c r="S54" s="36">
+        <v>0</v>
+      </c>
+      <c r="T54" s="36">
+        <v>0</v>
+      </c>
+      <c r="U54" s="36">
         <v>0</v>
       </c>
       <c r="V54" s="36">
@@ -59154,21 +58493,13 @@
       <c r="AM54" s="36">
         <v>0</v>
       </c>
-      <c r="AN54" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP54" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ54" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR54" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN54" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO54"/>
+      <c r="AP54"/>
+      <c r="AQ54"/>
+      <c r="AR54"/>
       <c r="AS54"/>
       <c r="AT54"/>
       <c r="AU54"/>
@@ -60176,12 +59507,8 @@
       <c r="ANI54"/>
       <c r="ANJ54"/>
       <c r="ANK54"/>
-      <c r="ANL54"/>
-      <c r="ANM54"/>
-      <c r="ANN54"/>
-      <c r="ANO54"/>
     </row>
-    <row r="55" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
         <v>77</v>
       </c>
@@ -60200,44 +59527,44 @@
       <c r="F55" s="35">
         <v>0</v>
       </c>
-      <c r="G55" s="97">
-        <v>0</v>
-      </c>
-      <c r="H55" s="97">
-        <v>0</v>
-      </c>
-      <c r="I55" s="97">
-        <v>0</v>
-      </c>
-      <c r="J55" s="97">
-        <v>0</v>
-      </c>
-      <c r="K55" s="36">
+      <c r="G55" s="36">
         <v>2651</v>
       </c>
-      <c r="L55" s="38">
+      <c r="H55" s="38">
         <v>200</v>
       </c>
-      <c r="M55" s="39">
+      <c r="I55" s="39">
         <v>56.7</v>
       </c>
-      <c r="N55" s="40">
-        <v>0</v>
-      </c>
-      <c r="O55" s="35"/>
-      <c r="Q55" s="38">
-        <v>0</v>
-      </c>
-      <c r="R55" s="35">
-        <v>0</v>
-      </c>
-      <c r="S55" s="38">
-        <v>0</v>
-      </c>
-      <c r="T55" s="41">
-        <v>0</v>
-      </c>
-      <c r="U55" s="42">
+      <c r="J55" s="40">
+        <v>0</v>
+      </c>
+      <c r="K55" s="35"/>
+      <c r="M55" s="38">
+        <v>0</v>
+      </c>
+      <c r="N55" s="35">
+        <v>0</v>
+      </c>
+      <c r="O55" s="38">
+        <v>0</v>
+      </c>
+      <c r="P55" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="42">
+        <v>0</v>
+      </c>
+      <c r="R55" s="36">
+        <v>0</v>
+      </c>
+      <c r="S55" s="36">
+        <v>0</v>
+      </c>
+      <c r="T55" s="36">
+        <v>0</v>
+      </c>
+      <c r="U55" s="36">
         <v>0</v>
       </c>
       <c r="V55" s="36">
@@ -60294,21 +59621,13 @@
       <c r="AM55" s="36">
         <v>0</v>
       </c>
-      <c r="AN55" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP55" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ55" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR55" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN55" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO55"/>
+      <c r="AP55"/>
+      <c r="AQ55"/>
+      <c r="AR55"/>
       <c r="AS55"/>
       <c r="AT55"/>
       <c r="AU55"/>
@@ -61316,12 +60635,8 @@
       <c r="ANI55"/>
       <c r="ANJ55"/>
       <c r="ANK55"/>
-      <c r="ANL55"/>
-      <c r="ANM55"/>
-      <c r="ANN55"/>
-      <c r="ANO55"/>
     </row>
-    <row r="56" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
         <v>78</v>
       </c>
@@ -61340,44 +60655,44 @@
       <c r="F56" s="35">
         <v>0</v>
       </c>
-      <c r="G56" s="97">
-        <v>0</v>
-      </c>
-      <c r="H56" s="97">
-        <v>0</v>
-      </c>
-      <c r="I56" s="97">
-        <v>0</v>
-      </c>
-      <c r="J56" s="97">
-        <v>0</v>
-      </c>
-      <c r="K56" s="36">
+      <c r="G56" s="36">
         <v>2544</v>
       </c>
-      <c r="L56" s="38">
+      <c r="H56" s="38">
         <v>7</v>
       </c>
-      <c r="M56" s="39">
+      <c r="I56" s="39">
         <v>207</v>
       </c>
-      <c r="N56" s="40">
-        <v>0</v>
-      </c>
-      <c r="O56" s="35"/>
-      <c r="Q56" s="38">
-        <v>0</v>
-      </c>
-      <c r="R56" s="35">
-        <v>0</v>
-      </c>
-      <c r="S56" s="38">
-        <v>0</v>
-      </c>
-      <c r="T56" s="41">
-        <v>0</v>
-      </c>
-      <c r="U56" s="42">
+      <c r="J56" s="40">
+        <v>0</v>
+      </c>
+      <c r="K56" s="35"/>
+      <c r="M56" s="38">
+        <v>0</v>
+      </c>
+      <c r="N56" s="35">
+        <v>0</v>
+      </c>
+      <c r="O56" s="38">
+        <v>0</v>
+      </c>
+      <c r="P56" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="42">
+        <v>0</v>
+      </c>
+      <c r="R56" s="36">
+        <v>0</v>
+      </c>
+      <c r="S56" s="36">
+        <v>0</v>
+      </c>
+      <c r="T56" s="36">
+        <v>0</v>
+      </c>
+      <c r="U56" s="36">
         <v>0</v>
       </c>
       <c r="V56" s="36">
@@ -61434,21 +60749,13 @@
       <c r="AM56" s="36">
         <v>0</v>
       </c>
-      <c r="AN56" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO56" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP56" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ56" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN56" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO56"/>
+      <c r="AP56"/>
+      <c r="AQ56"/>
+      <c r="AR56"/>
       <c r="AS56"/>
       <c r="AT56"/>
       <c r="AU56"/>
@@ -62456,12 +61763,8 @@
       <c r="ANI56"/>
       <c r="ANJ56"/>
       <c r="ANK56"/>
-      <c r="ANL56"/>
-      <c r="ANM56"/>
-      <c r="ANN56"/>
-      <c r="ANO56"/>
     </row>
-    <row r="57" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
         <v>79</v>
       </c>
@@ -62480,47 +61783,47 @@
       <c r="F57" s="35">
         <v>0</v>
       </c>
-      <c r="G57" s="97">
-        <v>0</v>
-      </c>
-      <c r="H57" s="97">
-        <v>0</v>
-      </c>
-      <c r="I57" s="97">
-        <v>0</v>
-      </c>
-      <c r="J57" s="97">
-        <v>0</v>
-      </c>
-      <c r="K57" s="36">
-        <v>0</v>
-      </c>
-      <c r="L57" s="38">
-        <v>0</v>
-      </c>
-      <c r="M57" s="39">
+      <c r="G57" s="36">
+        <v>0</v>
+      </c>
+      <c r="H57" s="38">
+        <v>0</v>
+      </c>
+      <c r="I57" s="39">
         <v>57</v>
       </c>
-      <c r="N57" s="40">
-        <v>0</v>
-      </c>
-      <c r="O57" s="35"/>
-      <c r="Q57" s="38">
+      <c r="J57" s="40">
+        <v>0</v>
+      </c>
+      <c r="K57" s="35"/>
+      <c r="M57" s="38">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R57" s="35">
+      <c r="N57" s="35">
         <v>1.108E-2</v>
       </c>
-      <c r="S57" s="38">
+      <c r="O57" s="38">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="T57" s="41">
-        <v>0</v>
-      </c>
-      <c r="U57" s="42">
-        <v>0</v>
-      </c>
-      <c r="V57" s="42">
+      <c r="P57" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="42">
+        <v>0</v>
+      </c>
+      <c r="R57" s="42">
+        <v>0</v>
+      </c>
+      <c r="S57" s="36">
+        <v>0</v>
+      </c>
+      <c r="T57" s="36">
+        <v>0</v>
+      </c>
+      <c r="U57" s="36">
+        <v>0</v>
+      </c>
+      <c r="V57" s="36">
         <v>0</v>
       </c>
       <c r="W57" s="36">
@@ -62574,21 +61877,13 @@
       <c r="AM57" s="36">
         <v>0</v>
       </c>
-      <c r="AN57" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO57" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP57" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR57" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN57" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO57"/>
+      <c r="AP57"/>
+      <c r="AQ57"/>
+      <c r="AR57"/>
       <c r="AS57"/>
       <c r="AT57"/>
       <c r="AU57"/>
@@ -63596,12 +62891,8 @@
       <c r="ANI57"/>
       <c r="ANJ57"/>
       <c r="ANK57"/>
-      <c r="ANL57"/>
-      <c r="ANM57"/>
-      <c r="ANN57"/>
-      <c r="ANO57"/>
     </row>
-    <row r="58" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="47" t="s">
         <v>80</v>
       </c>
@@ -63621,115 +62912,107 @@
       <c r="F58" s="35">
         <v>0</v>
       </c>
-      <c r="G58" s="97">
-        <v>0</v>
-      </c>
-      <c r="H58" s="97">
-        <v>0</v>
-      </c>
-      <c r="I58" s="97">
-        <v>0</v>
-      </c>
-      <c r="J58" s="97">
-        <v>0</v>
-      </c>
-      <c r="K58" s="36">
-        <v>0</v>
-      </c>
-      <c r="L58" s="38">
-        <v>0</v>
-      </c>
-      <c r="M58" s="39">
+      <c r="G58" s="36">
+        <v>0</v>
+      </c>
+      <c r="H58" s="38">
+        <v>0</v>
+      </c>
+      <c r="I58" s="39">
         <v>400</v>
       </c>
-      <c r="N58" s="40">
+      <c r="J58" s="40">
         <v>258</v>
       </c>
-      <c r="O58" s="35"/>
-      <c r="Q58" s="38">
+      <c r="K58" s="35"/>
+      <c r="M58" s="38">
         <v>0.91</v>
       </c>
-      <c r="R58" s="35">
+      <c r="N58" s="35">
         <v>794</v>
       </c>
-      <c r="S58" s="38">
+      <c r="O58" s="38">
         <v>2000</v>
       </c>
-      <c r="T58" s="41">
+      <c r="P58" s="41">
         <v>102968.10545833</v>
       </c>
-      <c r="U58" s="42">
+      <c r="Q58" s="42">
         <v>-448351.45343147498</v>
       </c>
+      <c r="R58" s="36">
+        <v>3600000</v>
+      </c>
+      <c r="S58" s="36">
+        <v>3814000</v>
+      </c>
+      <c r="T58" s="36">
+        <v>4015000</v>
+      </c>
+      <c r="U58" s="36">
+        <v>4055000</v>
+      </c>
       <c r="V58" s="36">
-        <v>3600000</v>
+        <v>4260000</v>
       </c>
       <c r="W58" s="36">
-        <v>3814000</v>
+        <v>4500000</v>
       </c>
       <c r="X58" s="36">
-        <v>4015000</v>
+        <v>4700000</v>
       </c>
       <c r="Y58" s="36">
-        <v>4055000</v>
+        <v>5000000</v>
       </c>
       <c r="Z58" s="36">
-        <v>4260000</v>
+        <v>4800000</v>
       </c>
       <c r="AA58" s="36">
-        <v>4500000</v>
+        <v>5299990</v>
       </c>
       <c r="AB58" s="36">
-        <v>4700000</v>
+        <v>4999990</v>
       </c>
       <c r="AC58" s="36">
-        <v>5000000</v>
+        <v>5199990</v>
       </c>
       <c r="AD58" s="36">
-        <v>4800000</v>
+        <v>5799980</v>
       </c>
       <c r="AE58" s="36">
-        <v>5299990</v>
+        <v>6289960</v>
       </c>
       <c r="AF58" s="36">
-        <v>4999990</v>
+        <v>6389940</v>
       </c>
       <c r="AG58" s="36">
-        <v>5199990</v>
+        <v>5799880</v>
       </c>
       <c r="AH58" s="36">
-        <v>5799980</v>
+        <v>6399810</v>
       </c>
       <c r="AI58" s="36">
-        <v>6289960</v>
+        <v>6699790</v>
       </c>
       <c r="AJ58" s="36">
-        <v>6389940</v>
+        <v>7229760</v>
       </c>
       <c r="AK58" s="36">
-        <v>5799880</v>
+        <v>7399740</v>
       </c>
       <c r="AL58" s="36">
-        <v>6399810</v>
+        <v>6039590</v>
       </c>
       <c r="AM58" s="36">
-        <v>6699790</v>
-      </c>
-      <c r="AN58" s="36">
-        <v>7229760</v>
-      </c>
-      <c r="AO58" s="36">
-        <v>7399740</v>
-      </c>
-      <c r="AP58" s="36">
-        <v>6039590</v>
-      </c>
-      <c r="AQ58" s="36">
         <v>6939440</v>
       </c>
-      <c r="AR58" s="38">
+      <c r="AN58" s="38">
         <v>6599270</v>
       </c>
+      <c r="AO58"/>
+      <c r="AP58"/>
+      <c r="AQ58"/>
+      <c r="AR58"/>
       <c r="AS58"/>
       <c r="AT58"/>
       <c r="AU58"/>
@@ -64737,12 +64020,8 @@
       <c r="ANI58"/>
       <c r="ANJ58"/>
       <c r="ANK58"/>
-      <c r="ANL58"/>
-      <c r="ANM58"/>
-      <c r="ANN58"/>
-      <c r="ANO58"/>
     </row>
-    <row r="59" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="47" t="s">
         <v>81</v>
       </c>
@@ -64761,44 +64040,44 @@
       <c r="F59" s="35">
         <v>0</v>
       </c>
-      <c r="G59" s="97">
-        <v>0</v>
-      </c>
-      <c r="H59" s="97">
-        <v>0</v>
-      </c>
-      <c r="I59" s="97">
-        <v>0</v>
-      </c>
-      <c r="J59" s="97">
-        <v>0</v>
-      </c>
-      <c r="K59" s="36">
-        <v>0</v>
-      </c>
-      <c r="L59" s="38">
-        <v>0</v>
-      </c>
-      <c r="M59" s="39">
+      <c r="G59" s="36">
+        <v>0</v>
+      </c>
+      <c r="H59" s="38">
+        <v>0</v>
+      </c>
+      <c r="I59" s="39">
         <v>60</v>
       </c>
-      <c r="N59" s="40">
-        <v>0</v>
-      </c>
-      <c r="O59" s="35"/>
-      <c r="Q59" s="38">
-        <v>0</v>
-      </c>
-      <c r="R59" s="35">
-        <v>0</v>
-      </c>
-      <c r="S59" s="38">
-        <v>0</v>
-      </c>
-      <c r="T59" s="41">
-        <v>0</v>
-      </c>
-      <c r="U59" s="42">
+      <c r="J59" s="40">
+        <v>0</v>
+      </c>
+      <c r="K59" s="35"/>
+      <c r="M59" s="38">
+        <v>0</v>
+      </c>
+      <c r="N59" s="35">
+        <v>0</v>
+      </c>
+      <c r="O59" s="38">
+        <v>0</v>
+      </c>
+      <c r="P59" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="42">
+        <v>0</v>
+      </c>
+      <c r="R59" s="36">
+        <v>0</v>
+      </c>
+      <c r="S59" s="36">
+        <v>0</v>
+      </c>
+      <c r="T59" s="36">
+        <v>0</v>
+      </c>
+      <c r="U59" s="36">
         <v>0</v>
       </c>
       <c r="V59" s="36">
@@ -64855,21 +64134,13 @@
       <c r="AM59" s="36">
         <v>0</v>
       </c>
-      <c r="AN59" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO59" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP59" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ59" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN59" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO59"/>
+      <c r="AP59"/>
+      <c r="AQ59"/>
+      <c r="AR59"/>
       <c r="AS59"/>
       <c r="AT59"/>
       <c r="AU59"/>
@@ -65877,12 +65148,8 @@
       <c r="ANI59"/>
       <c r="ANJ59"/>
       <c r="ANK59"/>
-      <c r="ANL59"/>
-      <c r="ANM59"/>
-      <c r="ANN59"/>
-      <c r="ANO59"/>
     </row>
-    <row r="60" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="47" t="s">
         <v>82</v>
       </c>
@@ -65902,115 +65169,107 @@
       <c r="F60" s="35">
         <v>0</v>
       </c>
-      <c r="G60" s="97">
-        <v>0</v>
-      </c>
-      <c r="H60" s="97">
-        <v>0</v>
-      </c>
-      <c r="I60" s="97">
-        <v>0</v>
-      </c>
-      <c r="J60" s="97">
-        <v>0</v>
-      </c>
-      <c r="K60" s="36">
-        <v>0</v>
-      </c>
-      <c r="L60" s="38">
-        <v>0</v>
-      </c>
-      <c r="M60" s="39">
+      <c r="G60" s="36">
+        <v>0</v>
+      </c>
+      <c r="H60" s="38">
+        <v>0</v>
+      </c>
+      <c r="I60" s="39">
         <v>3710</v>
       </c>
-      <c r="N60" s="40">
-        <v>0</v>
-      </c>
-      <c r="O60" s="35"/>
-      <c r="Q60" s="38">
+      <c r="J60" s="40">
+        <v>0</v>
+      </c>
+      <c r="K60" s="35"/>
+      <c r="M60" s="38">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="R60" s="35">
+      <c r="N60" s="35">
         <v>15</v>
       </c>
-      <c r="S60" s="38">
+      <c r="O60" s="38">
         <v>63</v>
       </c>
-      <c r="T60" s="41">
+      <c r="P60" s="41">
         <v>1274.74442509663</v>
       </c>
-      <c r="U60" s="42">
+      <c r="Q60" s="42">
         <v>-18947.842061937801</v>
       </c>
+      <c r="R60" s="36">
+        <v>33900</v>
+      </c>
+      <c r="S60" s="36">
+        <v>33700</v>
+      </c>
+      <c r="T60" s="36">
+        <v>35100</v>
+      </c>
+      <c r="U60" s="36">
+        <v>37100</v>
+      </c>
       <c r="V60" s="36">
-        <v>33900</v>
+        <v>41800</v>
       </c>
       <c r="W60" s="36">
-        <v>33700</v>
+        <v>42800</v>
       </c>
       <c r="X60" s="36">
-        <v>35100</v>
+        <v>43000</v>
       </c>
       <c r="Y60" s="36">
-        <v>37100</v>
+        <v>58000</v>
       </c>
       <c r="Z60" s="36">
-        <v>41800</v>
+        <v>60000</v>
       </c>
       <c r="AA60" s="36">
-        <v>42800</v>
+        <v>41000</v>
       </c>
       <c r="AB60" s="36">
-        <v>43000</v>
+        <v>40200</v>
       </c>
       <c r="AC60" s="36">
-        <v>58000</v>
+        <v>58200</v>
       </c>
       <c r="AD60" s="36">
-        <v>60000</v>
+        <v>55700</v>
       </c>
       <c r="AE60" s="36">
-        <v>41000</v>
+        <v>58500</v>
       </c>
       <c r="AF60" s="36">
-        <v>40200</v>
+        <v>55500</v>
       </c>
       <c r="AG60" s="36">
-        <v>58200</v>
+        <v>53490</v>
       </c>
       <c r="AH60" s="36">
-        <v>55700</v>
+        <v>57590</v>
       </c>
       <c r="AI60" s="36">
-        <v>58500</v>
+        <v>62380</v>
       </c>
       <c r="AJ60" s="36">
-        <v>55500</v>
+        <v>73980</v>
       </c>
       <c r="AK60" s="36">
-        <v>53490</v>
+        <v>78980</v>
       </c>
       <c r="AL60" s="36">
-        <v>57590</v>
+        <v>82670</v>
       </c>
       <c r="AM60" s="36">
-        <v>62380</v>
-      </c>
-      <c r="AN60" s="36">
-        <v>73980</v>
-      </c>
-      <c r="AO60" s="36">
-        <v>78980</v>
-      </c>
-      <c r="AP60" s="36">
-        <v>82670</v>
-      </c>
-      <c r="AQ60" s="36">
         <v>77760</v>
       </c>
-      <c r="AR60" s="38">
+      <c r="AN60" s="38">
         <v>75940</v>
       </c>
+      <c r="AO60"/>
+      <c r="AP60"/>
+      <c r="AQ60"/>
+      <c r="AR60"/>
       <c r="AS60"/>
       <c r="AT60"/>
       <c r="AU60"/>
@@ -67018,12 +66277,8 @@
       <c r="ANI60"/>
       <c r="ANJ60"/>
       <c r="ANK60"/>
-      <c r="ANL60"/>
-      <c r="ANM60"/>
-      <c r="ANN60"/>
-      <c r="ANO60"/>
     </row>
-    <row r="61" spans="1:1055" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1051" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
         <v>83</v>
       </c>
@@ -67042,44 +66297,44 @@
       <c r="F61" s="35">
         <v>0</v>
       </c>
-      <c r="G61" s="97">
-        <v>0</v>
-      </c>
-      <c r="H61" s="97">
-        <v>0</v>
-      </c>
-      <c r="I61" s="97">
-        <v>0</v>
-      </c>
-      <c r="J61" s="97">
-        <v>0</v>
-      </c>
-      <c r="K61" s="36">
-        <v>0</v>
-      </c>
-      <c r="L61" s="38">
-        <v>0</v>
-      </c>
-      <c r="M61" s="39">
+      <c r="G61" s="36">
+        <v>0</v>
+      </c>
+      <c r="H61" s="38">
+        <v>0</v>
+      </c>
+      <c r="I61" s="39">
         <v>36</v>
       </c>
-      <c r="N61" s="40">
-        <v>0</v>
-      </c>
-      <c r="O61" s="35"/>
-      <c r="Q61" s="38">
-        <v>0</v>
-      </c>
-      <c r="R61" s="35">
-        <v>0</v>
-      </c>
-      <c r="S61" s="38">
-        <v>0</v>
-      </c>
-      <c r="T61" s="41">
-        <v>0</v>
-      </c>
-      <c r="U61" s="42">
+      <c r="J61" s="40">
+        <v>0</v>
+      </c>
+      <c r="K61" s="35"/>
+      <c r="M61" s="38">
+        <v>0</v>
+      </c>
+      <c r="N61" s="35">
+        <v>0</v>
+      </c>
+      <c r="O61" s="38">
+        <v>0</v>
+      </c>
+      <c r="P61" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="42">
+        <v>0</v>
+      </c>
+      <c r="R61" s="36">
+        <v>0</v>
+      </c>
+      <c r="S61" s="36">
+        <v>0</v>
+      </c>
+      <c r="T61" s="36">
+        <v>0</v>
+      </c>
+      <c r="U61" s="36">
         <v>0</v>
       </c>
       <c r="V61" s="36">
@@ -67136,21 +66391,13 @@
       <c r="AM61" s="36">
         <v>0</v>
       </c>
-      <c r="AN61" s="36">
-        <v>0</v>
-      </c>
-      <c r="AO61" s="36">
-        <v>0</v>
-      </c>
-      <c r="AP61" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ61" s="36">
-        <v>0</v>
-      </c>
-      <c r="AR61" s="38">
-        <v>0</v>
-      </c>
+      <c r="AN61" s="38">
+        <v>0</v>
+      </c>
+      <c r="AO61"/>
+      <c r="AP61"/>
+      <c r="AQ61"/>
+      <c r="AR61"/>
       <c r="AS61"/>
       <c r="AT61"/>
       <c r="AU61"/>
@@ -68158,12 +67405,8 @@
       <c r="ANI61"/>
       <c r="ANJ61"/>
       <c r="ANK61"/>
-      <c r="ANL61"/>
-      <c r="ANM61"/>
-      <c r="ANN61"/>
-      <c r="ANO61"/>
     </row>
-    <row r="62" spans="1:1055" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1051" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="51" t="s">
         <v>84</v>
       </c>
@@ -68183,121 +67426,113 @@
       <c r="F62" s="52">
         <v>0</v>
       </c>
-      <c r="G62" s="97">
-        <v>0</v>
-      </c>
-      <c r="H62" s="97">
-        <v>0</v>
-      </c>
-      <c r="I62" s="97">
-        <v>0</v>
-      </c>
-      <c r="J62" s="97">
-        <v>0</v>
-      </c>
-      <c r="K62" s="53">
+      <c r="G62" s="53">
         <v>200</v>
       </c>
-      <c r="L62" s="55">
-        <v>0</v>
-      </c>
-      <c r="M62" s="56">
+      <c r="H62" s="55">
+        <v>0</v>
+      </c>
+      <c r="I62" s="56">
         <v>72</v>
       </c>
-      <c r="N62" s="57">
+      <c r="J62" s="57">
         <v>9</v>
       </c>
-      <c r="O62" s="52">
+      <c r="K62" s="52">
         <v>0.19</v>
       </c>
-      <c r="P62" s="53">
+      <c r="L62" s="53">
         <v>0.6</v>
       </c>
-      <c r="Q62" s="55">
-        <f>(O62+P62)/2</f>
+      <c r="M62" s="55">
+        <f>(K62+L62)/2</f>
         <v>0.39500000000000002</v>
       </c>
-      <c r="R62" s="52">
+      <c r="N62" s="52">
         <v>230</v>
       </c>
-      <c r="S62" s="55">
+      <c r="O62" s="55">
         <v>1900</v>
       </c>
-      <c r="T62" s="58">
+      <c r="P62" s="58">
         <v>207576.31076444799</v>
       </c>
-      <c r="U62" s="59">
+      <c r="Q62" s="59">
         <v>-1819702.6572439</v>
       </c>
+      <c r="R62" s="53">
+        <v>6810000</v>
+      </c>
+      <c r="S62" s="53">
+        <v>7119990</v>
+      </c>
+      <c r="T62" s="53">
+        <v>7439990</v>
+      </c>
+      <c r="U62" s="53">
+        <v>7459980</v>
+      </c>
       <c r="V62" s="53">
-        <v>6810000</v>
+        <v>7549970</v>
       </c>
       <c r="W62" s="53">
-        <v>7119990</v>
+        <v>8039950</v>
       </c>
       <c r="X62" s="53">
-        <v>7439990</v>
+        <v>8729950</v>
       </c>
       <c r="Y62" s="53">
-        <v>7459980</v>
+        <v>8849940</v>
       </c>
       <c r="Z62" s="53">
-        <v>7549970</v>
+        <v>8359900</v>
       </c>
       <c r="AA62" s="53">
-        <v>8039950</v>
+        <v>9009830</v>
       </c>
       <c r="AB62" s="53">
-        <v>8729950</v>
+        <v>9599770</v>
       </c>
       <c r="AC62" s="53">
-        <v>8849940</v>
+        <v>9799700</v>
       </c>
       <c r="AD62" s="53">
-        <v>8359900</v>
+        <v>9999480</v>
       </c>
       <c r="AE62" s="53">
-        <v>9009830</v>
+        <v>10898960</v>
       </c>
       <c r="AF62" s="53">
-        <v>9599770</v>
+        <v>11598360</v>
       </c>
       <c r="AG62" s="53">
-        <v>9799700</v>
+        <v>11196900</v>
       </c>
       <c r="AH62" s="53">
-        <v>9999480</v>
+        <v>11995070</v>
       </c>
       <c r="AI62" s="53">
-        <v>10898960</v>
+        <v>12794550</v>
       </c>
       <c r="AJ62" s="53">
-        <v>11598360</v>
+        <v>13493710</v>
       </c>
       <c r="AK62" s="53">
-        <v>11196900</v>
+        <v>13393260</v>
       </c>
       <c r="AL62" s="53">
-        <v>11995070</v>
+        <v>13289410</v>
       </c>
       <c r="AM62" s="53">
-        <v>12794550</v>
-      </c>
-      <c r="AN62" s="53">
-        <v>13493710</v>
-      </c>
-      <c r="AO62" s="53">
-        <v>13393260</v>
-      </c>
-      <c r="AP62" s="53">
-        <v>13289410</v>
-      </c>
-      <c r="AQ62" s="53">
         <v>12785320</v>
       </c>
-      <c r="AR62" s="55">
+      <c r="AN62" s="55">
         <v>11881060</v>
       </c>
+      <c r="AO62"/>
+      <c r="AP62"/>
+      <c r="AQ62"/>
+      <c r="AR62"/>
       <c r="AS62"/>
       <c r="AT62"/>
       <c r="AU62"/>
@@ -69305,12 +68540,8 @@
       <c r="ANI62"/>
       <c r="ANJ62"/>
       <c r="ANK62"/>
-      <c r="ANL62"/>
-      <c r="ANM62"/>
-      <c r="ANN62"/>
-      <c r="ANO62"/>
     </row>
-    <row r="63" spans="1:1055" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1051" x14ac:dyDescent="0.25">
       <c r="A63" s="60" t="s">
         <v>85</v>
       </c>
@@ -69322,7 +68553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:1055" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1051" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="64" t="s">
         <v>86</v>
       </c>
@@ -69531,12 +68762,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E97" s="62">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="67" t="s">
         <v>87</v>
       </c>
@@ -69555,10 +68786,10 @@
       <c r="E98" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="M98" s="72"/>
-      <c r="N98" s="73"/>
+      <c r="I98" s="72"/>
+      <c r="J98" s="73"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="47" t="s">
         <v>27</v>
       </c>
@@ -69574,10 +68805,10 @@
       <c r="E99" s="75">
         <v>0</v>
       </c>
-      <c r="M99" s="72"/>
-      <c r="N99" s="73"/>
+      <c r="I99" s="72"/>
+      <c r="J99" s="73"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="47" t="s">
         <v>28</v>
       </c>
@@ -69593,10 +68824,10 @@
       <c r="E100" s="37">
         <v>0.78</v>
       </c>
-      <c r="M100" s="72"/>
-      <c r="N100" s="73"/>
+      <c r="I100" s="72"/>
+      <c r="J100" s="73"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="47" t="s">
         <v>29</v>
       </c>
@@ -69612,10 +68843,10 @@
       <c r="E101" s="37">
         <v>0</v>
       </c>
-      <c r="M101" s="72"/>
-      <c r="N101" s="73"/>
+      <c r="I101" s="72"/>
+      <c r="J101" s="73"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="47" t="s">
         <v>30</v>
       </c>
@@ -69631,10 +68862,10 @@
       <c r="E102" s="37">
         <v>0</v>
       </c>
-      <c r="M102" s="72"/>
-      <c r="N102" s="73"/>
+      <c r="I102" s="72"/>
+      <c r="J102" s="73"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="47" t="s">
         <v>31</v>
       </c>
@@ -69650,10 +68881,10 @@
       <c r="E103" s="37">
         <v>0</v>
       </c>
-      <c r="M103" s="72"/>
-      <c r="N103" s="73"/>
+      <c r="I103" s="72"/>
+      <c r="J103" s="73"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="47" t="s">
         <v>32</v>
       </c>
@@ -69669,10 +68900,10 @@
       <c r="E104" s="37">
         <v>0</v>
       </c>
-      <c r="M104" s="72"/>
-      <c r="N104" s="73"/>
+      <c r="I104" s="72"/>
+      <c r="J104" s="73"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="47" t="s">
         <v>33</v>
       </c>
@@ -69688,10 +68919,10 @@
       <c r="E105" s="37">
         <v>0</v>
       </c>
-      <c r="M105" s="72"/>
-      <c r="N105" s="73"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="73"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="47" t="s">
         <v>34</v>
       </c>
@@ -69707,10 +68938,10 @@
       <c r="E106" s="37">
         <v>0</v>
       </c>
-      <c r="M106" s="72"/>
-      <c r="N106" s="73"/>
+      <c r="I106" s="72"/>
+      <c r="J106" s="73"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
         <v>35</v>
       </c>
@@ -69726,10 +68957,10 @@
       <c r="E107" s="37">
         <v>3450</v>
       </c>
-      <c r="M107" s="72"/>
-      <c r="N107" s="73"/>
+      <c r="I107" s="72"/>
+      <c r="J107" s="73"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
         <v>36</v>
       </c>
@@ -69745,10 +68976,10 @@
       <c r="E108" s="37">
         <v>0</v>
       </c>
-      <c r="M108" s="72"/>
-      <c r="N108" s="73"/>
+      <c r="I108" s="72"/>
+      <c r="J108" s="73"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
         <v>37</v>
       </c>
@@ -69764,10 +68995,10 @@
       <c r="E109" s="37">
         <v>0</v>
       </c>
-      <c r="M109" s="72"/>
-      <c r="N109" s="73"/>
+      <c r="I109" s="72"/>
+      <c r="J109" s="73"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
         <v>38</v>
       </c>
@@ -69783,10 +69014,10 @@
       <c r="E110" s="37">
         <v>0</v>
       </c>
-      <c r="M110" s="72"/>
-      <c r="N110" s="73"/>
+      <c r="I110" s="72"/>
+      <c r="J110" s="73"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="47" t="s">
         <v>39</v>
       </c>
@@ -69802,10 +69033,10 @@
       <c r="E111" s="37">
         <v>0</v>
       </c>
-      <c r="M111" s="72"/>
-      <c r="N111" s="73"/>
+      <c r="I111" s="72"/>
+      <c r="J111" s="73"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="47" t="s">
         <v>40</v>
       </c>
@@ -69821,10 +69052,10 @@
       <c r="E112" s="37">
         <v>0</v>
       </c>
-      <c r="M112" s="72"/>
-      <c r="N112" s="73"/>
+      <c r="I112" s="72"/>
+      <c r="J112" s="73"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="47" t="s">
         <v>89</v>
       </c>
@@ -69840,10 +69071,10 @@
       <c r="E113" s="37">
         <v>0</v>
       </c>
-      <c r="M113" s="72"/>
-      <c r="N113" s="73"/>
+      <c r="I113" s="72"/>
+      <c r="J113" s="73"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="47" t="s">
         <v>42</v>
       </c>
@@ -69859,10 +69090,10 @@
       <c r="E114" s="37">
         <v>140</v>
       </c>
-      <c r="M114" s="72"/>
-      <c r="N114" s="73"/>
+      <c r="I114" s="72"/>
+      <c r="J114" s="73"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="47" t="s">
         <v>43</v>
       </c>
@@ -69878,10 +69109,10 @@
       <c r="E115" s="37">
         <v>0</v>
       </c>
-      <c r="M115" s="72"/>
-      <c r="N115" s="73"/>
+      <c r="I115" s="72"/>
+      <c r="J115" s="73"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="47" t="s">
         <v>44</v>
       </c>
@@ -69897,10 +69128,10 @@
       <c r="E116" s="37">
         <v>0</v>
       </c>
-      <c r="M116" s="72"/>
-      <c r="N116" s="73"/>
+      <c r="I116" s="72"/>
+      <c r="J116" s="73"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="47" t="s">
         <v>45</v>
       </c>
@@ -69916,10 +69147,10 @@
       <c r="E117" s="37">
         <v>0</v>
       </c>
-      <c r="M117" s="72"/>
-      <c r="N117" s="73"/>
+      <c r="I117" s="72"/>
+      <c r="J117" s="73"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="47" t="s">
         <v>46</v>
       </c>
@@ -69935,10 +69166,10 @@
       <c r="E118" s="37">
         <v>0</v>
       </c>
-      <c r="M118" s="72"/>
-      <c r="N118" s="73"/>
+      <c r="I118" s="72"/>
+      <c r="J118" s="73"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="47" t="s">
         <v>47</v>
       </c>
@@ -69954,10 +69185,10 @@
       <c r="E119" s="37">
         <v>0</v>
       </c>
-      <c r="M119" s="72"/>
-      <c r="N119" s="73"/>
+      <c r="I119" s="72"/>
+      <c r="J119" s="73"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="47" t="s">
         <v>48</v>
       </c>
@@ -69973,10 +69204,10 @@
       <c r="E120" s="37">
         <v>0</v>
       </c>
-      <c r="M120" s="72"/>
-      <c r="N120" s="73"/>
+      <c r="I120" s="72"/>
+      <c r="J120" s="73"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="47" t="s">
         <v>49</v>
       </c>
@@ -69992,10 +69223,10 @@
       <c r="E121" s="37">
         <v>11</v>
       </c>
-      <c r="M121" s="72"/>
-      <c r="N121" s="73"/>
+      <c r="I121" s="72"/>
+      <c r="J121" s="73"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="47" t="s">
         <v>50</v>
       </c>
@@ -70011,10 +69242,10 @@
       <c r="E122" s="37">
         <v>0</v>
       </c>
-      <c r="M122" s="72"/>
-      <c r="N122" s="73"/>
+      <c r="I122" s="72"/>
+      <c r="J122" s="73"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="47" t="s">
         <v>51</v>
       </c>
@@ -70030,10 +69261,10 @@
       <c r="E123" s="37">
         <v>0</v>
       </c>
-      <c r="M123" s="72"/>
-      <c r="N123" s="73"/>
+      <c r="I123" s="72"/>
+      <c r="J123" s="73"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="47" t="s">
         <v>52</v>
       </c>
@@ -70049,10 +69280,10 @@
       <c r="E124" s="37">
         <v>0</v>
       </c>
-      <c r="M124" s="72"/>
-      <c r="N124" s="73"/>
+      <c r="I124" s="72"/>
+      <c r="J124" s="73"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="47" t="s">
         <v>53</v>
       </c>
@@ -70068,10 +69299,10 @@
       <c r="E125" s="37">
         <v>3.2</v>
       </c>
-      <c r="M125" s="72"/>
-      <c r="N125" s="73"/>
+      <c r="I125" s="72"/>
+      <c r="J125" s="73"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="47" t="s">
         <v>54</v>
       </c>
@@ -70087,10 +69318,10 @@
       <c r="E126" s="37">
         <v>0</v>
       </c>
-      <c r="M126" s="72"/>
-      <c r="N126" s="73"/>
+      <c r="I126" s="72"/>
+      <c r="J126" s="73"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="47" t="s">
         <v>55</v>
       </c>
@@ -70106,10 +69337,10 @@
       <c r="E127" s="37">
         <v>0</v>
       </c>
-      <c r="M127" s="72"/>
-      <c r="N127" s="73"/>
+      <c r="I127" s="72"/>
+      <c r="J127" s="73"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="47" t="s">
         <v>56</v>
       </c>
@@ -70125,10 +69356,10 @@
       <c r="E128" s="37">
         <v>0</v>
       </c>
-      <c r="M128" s="72"/>
-      <c r="N128" s="73"/>
+      <c r="I128" s="72"/>
+      <c r="J128" s="73"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="47" t="s">
         <v>57</v>
       </c>
@@ -70144,10 +69375,10 @@
       <c r="E129" s="37">
         <v>0</v>
       </c>
-      <c r="M129" s="72"/>
-      <c r="N129" s="73"/>
+      <c r="I129" s="72"/>
+      <c r="J129" s="73"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="47" t="s">
         <v>58</v>
       </c>
@@ -70163,10 +69394,10 @@
       <c r="E130" s="37">
         <v>0</v>
       </c>
-      <c r="M130" s="72"/>
-      <c r="N130" s="73"/>
+      <c r="I130" s="72"/>
+      <c r="J130" s="73"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="47" t="s">
         <v>59</v>
       </c>
@@ -70182,10 +69413,10 @@
       <c r="E131" s="37">
         <v>0</v>
       </c>
-      <c r="M131" s="72"/>
-      <c r="N131" s="73"/>
+      <c r="I131" s="72"/>
+      <c r="J131" s="73"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="47" t="s">
         <v>60</v>
       </c>
@@ -70201,10 +69432,10 @@
       <c r="E132" s="37">
         <v>0</v>
       </c>
-      <c r="M132" s="72"/>
-      <c r="N132" s="73"/>
+      <c r="I132" s="72"/>
+      <c r="J132" s="73"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="47" t="s">
         <v>61</v>
       </c>
@@ -70220,10 +69451,10 @@
       <c r="E133" s="37">
         <v>0</v>
       </c>
-      <c r="M133" s="72"/>
-      <c r="N133" s="73"/>
+      <c r="I133" s="72"/>
+      <c r="J133" s="73"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="47" t="s">
         <v>62</v>
       </c>
@@ -70239,10 +69470,10 @@
       <c r="E134" s="37">
         <v>0</v>
       </c>
-      <c r="M134" s="72"/>
-      <c r="N134" s="73"/>
+      <c r="I134" s="72"/>
+      <c r="J134" s="73"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="47" t="s">
         <v>63</v>
       </c>
@@ -70258,10 +69489,10 @@
       <c r="E135" s="37">
         <v>0</v>
       </c>
-      <c r="M135" s="72"/>
-      <c r="N135" s="73"/>
+      <c r="I135" s="72"/>
+      <c r="J135" s="73"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="47" t="s">
         <v>64</v>
       </c>
@@ -70277,10 +69508,10 @@
       <c r="E136" s="37">
         <v>0</v>
       </c>
-      <c r="M136" s="72"/>
-      <c r="N136" s="73"/>
+      <c r="I136" s="72"/>
+      <c r="J136" s="73"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="47" t="s">
         <v>65</v>
       </c>
@@ -70296,10 +69527,10 @@
       <c r="E137" s="37">
         <v>0</v>
       </c>
-      <c r="M137" s="72"/>
-      <c r="N137" s="73"/>
+      <c r="I137" s="72"/>
+      <c r="J137" s="73"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="47" t="s">
         <v>66</v>
       </c>
@@ -70315,10 +69546,10 @@
       <c r="E138" s="37">
         <v>0</v>
       </c>
-      <c r="M138" s="72"/>
-      <c r="N138" s="73"/>
+      <c r="I138" s="72"/>
+      <c r="J138" s="73"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="47" t="s">
         <v>67</v>
       </c>
@@ -70334,10 +69565,10 @@
       <c r="E139" s="37">
         <v>0</v>
       </c>
-      <c r="M139" s="72"/>
-      <c r="N139" s="73"/>
+      <c r="I139" s="72"/>
+      <c r="J139" s="73"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="47" t="s">
         <v>68</v>
       </c>
@@ -70353,10 +69584,10 @@
       <c r="E140" s="37">
         <v>0</v>
       </c>
-      <c r="M140" s="72"/>
-      <c r="N140" s="73"/>
+      <c r="I140" s="72"/>
+      <c r="J140" s="73"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="47" t="s">
         <v>69</v>
       </c>
@@ -70372,10 +69603,10 @@
       <c r="E141" s="37">
         <v>0</v>
       </c>
-      <c r="M141" s="72"/>
-      <c r="N141" s="73"/>
+      <c r="I141" s="72"/>
+      <c r="J141" s="73"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="47" t="s">
         <v>70</v>
       </c>
@@ -70391,10 +69622,10 @@
       <c r="E142" s="37">
         <v>0</v>
       </c>
-      <c r="M142" s="78"/>
-      <c r="N142" s="73"/>
+      <c r="I142" s="78"/>
+      <c r="J142" s="73"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="34" t="s">
         <v>71</v>
       </c>
@@ -70410,10 +69641,10 @@
       <c r="E143" s="37">
         <v>98</v>
       </c>
-      <c r="M143" s="72"/>
-      <c r="N143" s="73"/>
+      <c r="I143" s="72"/>
+      <c r="J143" s="73"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="34" t="s">
         <v>90</v>
       </c>
@@ -70429,10 +69660,10 @@
       <c r="E144" s="37">
         <v>0</v>
       </c>
-      <c r="M144" s="72"/>
-      <c r="N144" s="73"/>
+      <c r="I144" s="72"/>
+      <c r="J144" s="73"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="47" t="s">
         <v>73</v>
       </c>
@@ -70448,10 +69679,10 @@
       <c r="E145" s="37">
         <v>1.4E-2</v>
       </c>
-      <c r="M145" s="72"/>
-      <c r="N145" s="73"/>
+      <c r="I145" s="72"/>
+      <c r="J145" s="73"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="47" t="s">
         <v>74</v>
       </c>
@@ -70467,10 +69698,10 @@
       <c r="E146" s="37">
         <v>0</v>
       </c>
-      <c r="M146" s="72"/>
-      <c r="N146" s="73"/>
+      <c r="I146" s="72"/>
+      <c r="J146" s="73"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="47" t="s">
         <v>75</v>
       </c>
@@ -70486,10 +69717,10 @@
       <c r="E147" s="37">
         <v>0</v>
       </c>
-      <c r="M147" s="72"/>
-      <c r="N147" s="73"/>
+      <c r="I147" s="72"/>
+      <c r="J147" s="73"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="47" t="s">
         <v>76</v>
       </c>
@@ -70505,10 +69736,10 @@
       <c r="E148" s="37">
         <v>0</v>
       </c>
-      <c r="M148" s="72"/>
-      <c r="N148" s="73"/>
+      <c r="I148" s="72"/>
+      <c r="J148" s="73"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="47" t="s">
         <v>77</v>
       </c>
@@ -70524,10 +69755,10 @@
       <c r="E149" s="37">
         <v>0</v>
       </c>
-      <c r="M149" s="72"/>
-      <c r="N149" s="73"/>
+      <c r="I149" s="72"/>
+      <c r="J149" s="73"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="34" t="s">
         <v>91</v>
       </c>
@@ -70543,10 +69774,10 @@
       <c r="E150" s="37">
         <v>2000</v>
       </c>
-      <c r="M150" s="72"/>
-      <c r="N150" s="73"/>
+      <c r="I150" s="72"/>
+      <c r="J150" s="73"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="34" t="s">
         <v>79</v>
       </c>
@@ -70562,10 +69793,10 @@
       <c r="E151" s="37">
         <v>0</v>
       </c>
-      <c r="M151" s="72"/>
-      <c r="N151" s="73"/>
+      <c r="I151" s="72"/>
+      <c r="J151" s="73"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="34" t="s">
         <v>80</v>
       </c>
@@ -70581,10 +69812,10 @@
       <c r="E152" s="37">
         <v>0</v>
       </c>
-      <c r="M152" s="72"/>
-      <c r="N152" s="73"/>
+      <c r="I152" s="72"/>
+      <c r="J152" s="73"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="34" t="s">
         <v>81</v>
       </c>
@@ -70600,10 +69831,10 @@
       <c r="E153" s="37">
         <v>0</v>
       </c>
-      <c r="M153" s="72"/>
-      <c r="N153" s="73"/>
+      <c r="I153" s="72"/>
+      <c r="J153" s="73"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="34" t="s">
         <v>82</v>
       </c>
@@ -70619,10 +69850,10 @@
       <c r="E154" s="37">
         <v>0</v>
       </c>
-      <c r="M154" s="72"/>
-      <c r="N154" s="73"/>
+      <c r="I154" s="72"/>
+      <c r="J154" s="73"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="34" t="s">
         <v>83</v>
       </c>
@@ -70638,10 +69869,10 @@
       <c r="E155" s="37">
         <v>0</v>
       </c>
-      <c r="M155" s="72"/>
-      <c r="N155" s="73"/>
+      <c r="I155" s="72"/>
+      <c r="J155" s="73"/>
     </row>
-    <row r="156" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79" t="s">
         <v>84</v>
       </c>
@@ -70657,10 +69888,10 @@
       <c r="E156" s="82">
         <v>0</v>
       </c>
-      <c r="M156" s="72"/>
-      <c r="N156" s="73"/>
+      <c r="I156" s="72"/>
+      <c r="J156" s="73"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="83" t="s">
         <v>92</v>
       </c>
@@ -70676,12 +69907,12 @@
       <c r="E157" s="84">
         <v>12000000</v>
       </c>
-      <c r="M157" s="85">
+      <c r="I157" s="85">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="N157" s="73"/>
+      <c r="J157" s="73"/>
     </row>
-    <row r="158" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="86" t="s">
         <v>93</v>
       </c>
@@ -70697,17 +69928,17 @@
       <c r="E158" s="54">
         <v>500000</v>
       </c>
-      <c r="M158" s="88">
+      <c r="I158" s="88">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="N158" s="73"/>
+      <c r="J158" s="73"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="89"/>
       <c r="E159" s="62"/>
-      <c r="N159" s="90"/>
+      <c r="J159" s="90"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="91" t="s">
         <v>94</v>
       </c>
@@ -70724,7 +69955,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="91" t="s">
         <v>95</v>
       </c>
@@ -70746,20 +69977,16 @@
       <c r="F161" s="92">
         <v>0.1</v>
       </c>
-      <c r="G161" s="95"/>
-      <c r="H161" s="95"/>
-      <c r="I161" s="95"/>
-      <c r="J161" s="95"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="94"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
